--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -717,107 +717,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
+          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2025 - 09:30 - 11:30Crackley Wood, Kenilworth - Fri Nov 7Hay Woods - Solihull Fri Dec 5Tile Hill Nature Reserve Mon Dec 82026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: Simplifying Woodland Photography: Unlocking the Secrets to Capturing the Beauty of Nature on a photography walkMy aim is not to instruct you what to shoot, instead, I want to help you develop your own sense of visual awareness, photographic eye and your personal interpretation. I will be happy to help you with the “how to shoot” whatever it is you feel drawn to and wish to express through your creative vision using the camera to construct your intention. The photography walks around these selected woodlands are aimed to promote our senses and connection to trees/woodland/nature - as we walk, observe and take in our environment we may decide to make a photograph, or not.</t>
+          <t>Package Option - 4 Private Photography Classes Face to Face Coventry - 2 hrs each to suit you - Available 9-5 on weekdays. You will be sent a code to book dates</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495550918-139R34YFWLG3Q89CXENT/PRIVATE-PHOTOGRAPHY-LESSONS.png</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
+          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>360</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>360</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SQ7078023, SQ3819844, SQ3142823, SQ1654264, SQ1288994, SQ0063623, SQ6524101</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SQ7078023</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
+          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package Option - 4 Private Photography Classes Face to Face Coventry - 2 hrs each to suit you - Available 9-5 on weekdays. You will be sent a code to book dates</t>
+          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495550918-139R34YFWLG3Q89CXENT/PRIVATE-PHOTOGRAPHY-LESSONS.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>360</v>
+        <v>42</v>
       </c>
       <c r="I7" t="n">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ3248242</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -829,107 +829,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
+          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: 2026Daily From: Fri 23rd Oct to Fri 31st OctHalf-Day morning workshops are 8 am to 11.30 amHalf-Day afternoon workshops are from 12:00 pm to 3:30 pmOne Day workshops are 8 am to 3:30 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Details: Batsford ArboretumDescription: Batsford Arboretum always provides a terrific display of colour, texture and contrasts throughout Autumn. The Batsford Arboretum photography workshops are always very popular and and attract every level of photographer. There really is a complete range and choice for everyone here so it's not to be missed with expert guidance and support.</t>
+          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>250</v>
       </c>
       <c r="I8" t="n">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
+          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SQ0818501</t>
+          <t>SQ4217445</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Monthly Photography Mentoring Sessions - Online - Zoom</t>
+          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Photography mentoring online. Receive a monthly assignment to increase your skills across multiple genres and get expert feedback on your images each month</t>
+          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1559474612221-TBJKYSCMOO6IM7FTXJJI/online-photography-mentoring.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-online-photography-mentoring</t>
+          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>online, photography-tuition, photography-courses</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>1200</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ0754560</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -941,51 +941,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>Monthly Photography Mentoring Sessions - Online - Zoom</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Photography mentoring online. Receive a monthly assignment to increase your skills across multiple genres and get expert feedback on your images each month</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1559474612221-TBJKYSCMOO6IM7FTXJJI/online-photography-mentoring.png</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-online-photography-mentoring</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>online, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
+          <t>SQ1067929</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SQ3248242</t>
+          <t>SQ1067929</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -997,163 +997,163 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr- 01 May</t>
+          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Mon-20-Apr-26Tue-21-Apr-26Wed-22-Apr-26Thu-23-Apr-26Fri-24-Apr-26Sat-25-Apr-26Sun-26-Apr-26Mon-27-Apr-26Tue-28-Apr-26Wed-29-Apr-26Thu-30-Apr-26Fri-01-May-26Book and select either:4hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsJoin our Bluebell Woodland Photography Workshops in Warwickshire to explore beautiful bluebell woods and enhance your photography skills. Led by a professional photographer, you'll capture stunning photos while enjoying easy walks through bluebell trails and receive valuable photography tips for capturing spring blooms in soft woodland light.</t>
+          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWParticipants: Max 4Time: 19:00 - 21:00Multi Course Start Dates: Beginners Photography Course3wks Thursdays - Mar 5 - Mar 19 Coventry3wks Mondays - Mar 9 - Mar 23 Coventry3wks Wednesdays - Apr 1 - Apr 15 Coventry3wks Tuesdays - Apr 7 - Apr 21 Coventry3wks Tuesdays - May 5 - May 19 Coventry3wks Thursdays - May 7 - May 21 Coventry3wks Tuesdays - Jun 2 - Jun 16 Coventry3wks Thursdays - Jun 11- Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 CoventryExperience - Level: Beginner and NoviceThis beginners photography course is aimed at anyone with a digital camera wishing to get off auto exposure mode and learn about key camera settings and composition to make better photos.Equipment Needed:You will need a DSLR or Mirrorless Camera with manual exposure modes.Alan will provide you with a course book covering all the topics for the course</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/bceae6f2-91b8-4012-a00b-7b7b177d346f/Beginners+Photography+Classes.png</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1746549", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Thursdays - Mar 5 - Mar 19 Coventry"}, {"@type": "Offer", "sku": "SQ3510767", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Mondays - Mar 9 - Mar 23 Coventry"}, {"@type": "Offer", "sku": "SQ7826447", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Wednesdays - Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ0670010", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Tuesdays - Apr 7 - Apr 21 Coventry"}, {"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>150</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510, SQ5723283, SQ7533033, SQ4478860</t>
+          <t>SQ1746549, SQ3510767, SQ7826447, SQ0670010, SQ7702763, SQ6898365, SQ8880953, SQ0678506, SQ4322859, SQ5977532</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SQ8599409</t>
+          <t>SQ1746549</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>Intermediates Intentions Photography Project Course</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
+          <t>Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire on this photography course | Coventry | 6-ClassesNO DATES SET FOR 2025 - Check back soon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="I12" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SQ0754560</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>250</v>
+        <v>135.95</v>
       </c>
       <c r="I13" t="n">
-        <v>750</v>
+        <v>459.95</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
+          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SQ4217445</t>
+          <t>SQ0105911</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1165,331 +1165,331 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
+          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWParticipants: Max 4Time: 19:00 - 21:00Multi Course Start Dates: Beginners Photography Course3wks Tuesdays - Jan 6 - Jan 20 Coventry3wks Thursdays - Jan 15- Jan 29 Coventry3wks Wednesdays - Feb 4 - Feb 18 Coventry3wks Mondays - Feb 9 - 23 Feb Coventry3wks Thursdays - Mar 5 - Mar 19 Coventry3wks Mondays - Mar 9 - Mar 23 Coventry3wks Wednesdays - Apr 1 - Apr 15 Coventry3wks Thursdays - Apr 2 - Apr 16 Coventry3wks Tuesdays - May 5 - May 19 Coventry3wks Thursdays - May 7 - May 21 CoventryExperience - Level: Beginner and NoviceThis beginners photography course is aimed at anyone with a digital camera wishing to get off auto exposure mode and learn about key camera settings and composition to make better photos.Equipment Needed:You will need a DSLR or Mirrorless Camera with manual exposure modes.Alan will provide you with a course book covering all the topics for the course</t>
+          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/bceae6f2-91b8-4012-a00b-7b7b177d346f/Beginners+Photography+Classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Tuesdays - Jan 6 - Jan 20 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Thursdays - Jan 15- Jan 29 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Wednesdays - Feb 4 - Feb 18 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Mondays - Feb 9 - Feb 23 Coventry"}, {"@type": "Offer", "sku": "SQ1746549", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Thursdays - Mar 5 - Mar 19 Coventry"}, {"@type": "Offer", "sku": "SQ3510767", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Mondays - Mar 9 - Mar 23 Coventry"}, {"@type": "Offer", "sku": "SQ7826447", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Wednesdays - Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ0670010", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Thursdays - Apr 2 - Apr 16 Coventry"}, {"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "3wks Thursdays - May 7 - May 21 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>150</v>
+        <v>50.57</v>
       </c>
       <c r="I14" t="n">
-        <v>150</v>
+        <v>416.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SQ8880953, SQ0678506, SQ4322859, SQ5977532, SQ1746549, SQ3510767, SQ7826447, SQ0670010, SQ7702763, SQ6898365</t>
+          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SQ8880953</t>
+          <t>SQ4872440</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Intermediates Intentions Photography Project Course</t>
+          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire on this photography course | Coventry | 6-ClassesNO DATES SET FOR 2025 - Check back soon</t>
+          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>400</v>
+        <v>133.85</v>
       </c>
       <c r="I15" t="n">
-        <v>400</v>
+        <v>356.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ6825544</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Landscape Photography DEVON Workshops - Various Dates</t>
+          <t>Beginners Portrait Photography Course - Coventry - 1 Day</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 NightsFri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND FiltersPhotography Workshop Event Details: DevonDescription: Our landscape photography devon workshops are carefully crafted to provide you with an immersive and educational experience. Led by experienced and passionate photographers, these workshops offer a structured learning environment that ensures personal development and skill enhancement. From the moment you join us, you'll be guided through the intricacies of seascape photography, learning new techniques and refining your artistic vision.</t>
+          <t>Beginners Portrait Photography Course - Suitable for any amateur who wants to learn the fundamentals of portrait photography - Coventry - 1-Day Course</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707238641610-VHWSAVN4IPEHPVRGJNQZ/portrait+photography+course.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>775</v>
+        <v>195</v>
       </c>
       <c r="I16" t="n">
-        <v>895</v>
+        <v>195</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SQ3856406, SQ2516659</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SQ3856406</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
+          <t>Online Photography Classes 121 - Zoom - Package Options</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 30th Mar 2026 - 17:30 - 20:00Mon 18th May 2026 - 18:30 - 21:00Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
+          <t>Private online photography classes tailored to your needs - Tuition &amp; support on any aspect of photography - Pay Now - Book dates later.Online photography classes and support are run via Zoom (free to use)Must be used within 12 months of purchase dateIf you want a package (series) of lessons, these package options offer a discount for purchasing multiples. Mon - Fri - 9 am - 5 pm1 x 1hr - £50 - Normal Price for lesson4 x 1hr - 15% Off normal price6 x 1hr - 20% Off normal price8 x 1hr - 25% Off normal price12 x 1hr - 25% Off normal price</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
+          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SQ9554270, SQ5307067, SQ3572999, SQ0796814</t>
+          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SQ9554270</t>
+          <t>SQ1461156</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
+          <t>Photo Print Preparation Service 30-min – File Check &amp; Advice</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 7th Mar 2026 - 10:00 - 13:30Fri 8th May 2026 - 10:00 - 13:30Sat 26th Oct 2026 - 10:00 - 13:30Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
+          <t>Book a 30 min Photo Print Preparation Service. I check crop, aspect ratio and DPI, enlarge, retouch, sharpen and supply print-ready image for you to print</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
+          <t>https://www.alanranger.com/photography-services-near-me/photo-print-preparation-service-30min</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>photography-services</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="I18" t="n">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SQ1416930, SQ0434017, SQ8778402</t>
+          <t>SQ5582230</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SQ1416930</t>
+          <t>SQ5582230</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
+          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: LavenderDescription: Join me in the Cotswolds for a spectacular sight of Lavender. We will shoot into the evening hours and capture some great colour - go abstract or vista; the choice is yours.</t>
+          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2025 - 09:30 - 11:30Crackley Wood, Kenilworth - Fri Nov 7Hay Woods - Solihull Fri Dec 5Tile Hill Nature Reserve Mon Dec 82026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: Simplifying Woodland Photography: Unlocking the Secrets to Capturing the Beauty of Nature on a photography walkMy aim is not to instruct you what to shoot, instead, I want to help you develop your own sense of visual awareness, photographic eye and your personal interpretation. I will be happy to help you with the “how to shoot” whatever it is you feel drawn to and wish to express through your creative vision using the camera to construct your intention. The photography walks around these selected woodlands are aimed to promote our senses and connection to trees/woodland/nature - as we walk, observe and take in our environment we may decide to make a photograph, or not.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714571149035-8ZN5I6UWJRIY2TG52JNT/Lavender+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SQ6748367, SQ7542811</t>
+          <t>SQ7078023, SQ3819844, SQ3142823, SQ1654264, SQ1288994, SQ0063623, SQ6524101</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SQ6748367</t>
+          <t>SQ7078023</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1501,51 +1501,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Poppy Fields Photography Workshops | Worcestershire</t>
+          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: Rolling hills full of poppies takes some beating. Join me for one of the poppy fields photography location shoots from early June to end of June in Worcestershire - These are provisional dates and may change depending on mother nature.</t>
+          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: 2026Daily From: Fri 23rd Oct to Fri 31st OctHalf-Day morning workshops are 8 am to 11.30 amHalf-Day afternoon workshops are from 12:00 pm to 3:30 pmOne Day workshops are 8 am to 3:30 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Details: Batsford ArboretumDescription: Batsford Arboretum always provides a terrific display of colour, texture and contrasts throughout Autumn. The Batsford Arboretum photography workshops are always very popular and and attract every level of photographer. There really is a complete range and choice for everyone here so it's not to be missed with expert guidance and support.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I20" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SQ8740143, SQ7189877</t>
+          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SQ8740143</t>
+          <t>SQ0818501</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1557,51 +1557,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BURNHAM ON SEA Long Exposure Photography Workshop 2 May</t>
+          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr- 01 May</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 2nd May 2026 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: BurnhamDescription: Experience the magic of long exposure photography against the breathtaking backdrop of Burnham on Sea's iconic lighthouse. Join us for an unforgettable workshop where you'll master the art of capturing stunning sunset seascapes. Our expert instructors will guide you through the process, helping you harness the beauty of this picturesque location in Somerset</t>
+          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Mon-20-Apr-26Tue-21-Apr-26Wed-22-Apr-26Thu-23-Apr-26Fri-24-Apr-26Sat-25-Apr-26Sun-26-Apr-26Mon-27-Apr-26Tue-28-Apr-26Wed-29-Apr-26Thu-30-Apr-26Fri-01-May-26Book and select either:4hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsJoin our Bluebell Woodland Photography Workshops in Warwickshire to explore beautiful bluebell woods and enhance your photography skills. Led by a professional photographer, you'll capture stunning photos while enjoying easy walks through bluebell trails and receive valuable photography tips for capturing spring blooms in soft woodland light.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
+          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H21" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I21" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510, SQ5723283, SQ7533033, SQ4478860</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ8599409</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1613,51 +1613,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
+          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 20 Mar - Sun 22 Mar - 3 Days/2 Nights 2026Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Lake DistrictDescription: We will be based in the north lakes and visit some of the top spots in the Lake District for photographs. The Lake District has been a favourite location for photographers for decades. It offers a rich variety of landscapes and the seasonal weather means it can be different every time you visit.The weather creates unique windows to capture, reflections, mist, stormy skies and subtle and strong colours - often all in the space of 1-2 days and sometimes just hours.We will visit approximately 2-3 locations a day in a weekend subject to the wishes of the group, time, weather and other factors: Sign up today for an amazing lake district photography workshop</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 30th Mar 2026 - 17:30 - 20:00Mon 18th May 2026 - 18:30 - 21:00Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0142956", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 20 Mar - Sun 22 Mar - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>975</v>
+        <v>50</v>
       </c>
       <c r="I22" t="n">
-        <v>1075</v>
+        <v>50</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SQ0142956, SQ9100538, SQ5158309, SQ9016326</t>
+          <t>SQ9554270, SQ5307067, SQ3572999, SQ0796814</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SQ0142956</t>
+          <t>SQ9554270</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1669,163 +1669,163 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
+          <t>Landscape Photography DEVON Workshops - Various Dates</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
+          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 NightsFri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND FiltersPhotography Workshop Event Details: DevonDescription: Our landscape photography devon workshops are carefully crafted to provide you with an immersive and educational experience. Led by experienced and passionate photographers, these workshops offer a structured learning environment that ensures personal development and skill enhancement. From the moment you join us, you'll be guided through the intricacies of seascape photography, learning new techniques and refining your artistic vision.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>135.95</v>
+        <v>775</v>
       </c>
       <c r="I23" t="n">
-        <v>459.95</v>
+        <v>895</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
+          <t>SQ3856406, SQ2516659</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SQ0105911</t>
+          <t>SQ3856406</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
+          <t>Poppy Fields Photography Workshops | Worcestershire</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
+          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: Rolling hills full of poppies takes some beating. Join me for one of the poppy fields photography location shoots from early June to end of June in Worcestershire - These are provisional dates and may change depending on mother nature.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>50.57</v>
+        <v>95</v>
       </c>
       <c r="I24" t="n">
-        <v>416.85</v>
+        <v>95</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
+          <t>SQ8740143, SQ7189877</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SQ4872440</t>
+          <t>SQ8740143</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
+          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 16th May 2026 - 09:30 - 16:00Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 7th Mar 2026 - 10:00 - 13:30Fri 8th May 2026 - 10:00 - 13:30Sat 26th Oct 2026 - 10:00 - 13:30Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="I25" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SQ2363666, SQ3794821, SQ8457424, SQ9037810</t>
+          <t>SQ1416930, SQ0434017, SQ8778402</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SQ2363666</t>
+          <t>SQ1416930</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1837,107 +1837,107 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
+          <t>BURNHAM ON SEA Long Exposure Photography Workshop 2 May</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
+          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 2nd May 2026 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: BurnhamDescription: Experience the magic of long exposure photography against the breathtaking backdrop of Burnham on Sea's iconic lighthouse. Join us for an unforgettable workshop where you'll master the art of capturing stunning sunset seascapes. Our expert instructors will guide you through the process, helping you harness the beauty of this picturesque location in Somerset</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>133.85</v>
+        <v>95</v>
       </c>
       <c r="I26" t="n">
-        <v>356.9</v>
+        <v>95</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SQ6825544</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NORTHUMBERLAND Photography Workshops - Feb 26 - Mar 1</t>
+          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 26th Feb 13:00 - Sun 1st Mar, 13:00 2026 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details: NorthumberlandDescription: Northumberland Photography Workshops - One of the highlights of Northumberland's landscape is its impressive collection of over seventy castles, the highest number in any English county. These historic fortresses not only showcase the region's rich heritage but also serve as captivating subjects for your photographs. The iconic Bamburgh Castle, dating back to the 11th century, stands majestically on a rocky outcrop, offering panoramic views of the surrounding coastline. Alnwick Castle, made famous by its appearance in the Harry Potter films, is another must-visit location for photography enthusiasts.Lindisfarne Castle and Dunstanburgh Castle are two other gems that beckon photographers with their unique charm. Lindisfarne Castle, perched on a basalt rock outcrop, creates a striking silhouette against the backdrop of the North Sea. Dunstanburgh Castle, situated atop a grassy cliff edge, is flanked by smooth black boulders on Embleton Beach, creating a dramatic composition that is sure to leave a lasting impression on your photographs.Sign up to Northumberland Photography Workshops - Coastline Photography to take your photography to the next level.</t>
+          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: LavenderDescription: Join me in the Cotswolds for a spectacular sight of Lavender. We will shoot into the evening hours and capture some great colour - go abstract or vista; the choice is yours.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714235981485-EF5PRA0X9C6ZNGQUO265/dunstanburgh+boulders.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>995</v>
+        <v>150</v>
       </c>
       <c r="I27" t="n">
-        <v>995</v>
+        <v>150</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ6748367, SQ7542811</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ6748367</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1949,51 +1949,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ANGLESEY Landscape Photography Workshop -  May 2026</t>
+          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 8th May 15:00 - Sun 10th May 14:00, 2026Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Anglesey PhotographyDescription: A great location for a Landscape Photography Workshop Anglesey is a large island of 220 square miles of mainly farmland, but the coastline is excellent for photography with sandy coves, harbours, and rocky headlands in addition to the lighthouses. We will also explore some other areas, Parys Mountain, once the world's biggest copper mine, which has been used in many science fiction films and TV shows for its Martian-like coloured appearance.</t>
+          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Lake DistrictDescription: We will be based in the north lakes and visit some of the top spots in the Lake District for photographs. The Lake District has been a favourite location for photographers for decades. It offers a rich variety of landscapes and the seasonal weather means it can be different every time you visit.The weather creates unique windows to capture, reflections, mist, stormy skies and subtle and strong colours - often all in the space of 1-2 days and sometimes just hours.We will visit approximately 2-3 locations a day in a weekend subject to the wishes of the group, time, weather and other factors: Sign up today for an amazing lake district photography workshop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>coastal, Landscape, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "795.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "795.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>795</v>
+        <v>975</v>
       </c>
       <c r="I28" t="n">
-        <v>795</v>
+        <v>1125</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ9100538</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2005,51 +2005,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 30 May</t>
+          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: Embark on a captivating journey of long-exposure photography amidst the secluded Welsh valley of Nant Mill. Join us for an immersive workshop where you'll discover the mesmerizing art of capturing river and waterfall scenes in this ancient woodland near Wrexham.</t>
+          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 16th May 2026 - 09:30 - 16:00Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
+          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="I29" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ2363666, SQ3794821, SQ8457424, SQ9037810</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ2363666</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2061,51 +2061,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
+          <t>ANGLESEY Landscape Photography Workshop -  May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: We will be based near Dingle and visit some of the top spots around the Dingle Peninsula, South Kerry (Skellig Ring) and finally Killarney National Park.There is a wide variety of subjects: Mountains, Lakes, Waterfalls, Trees/woodlands, Coastline, Rock Formations to name a few. All set in stunning scenery to wow any visitor and photographer. We will visit several locations in a day, some are short 10-15 min stops (layby shoots) others will require more time to perfectly capturing the perfect moment with tides and light.</t>
+          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 8th May 15:00 - Sun 10th May 14:00, 2026Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Anglesey PhotographyDescription: A great location for a Landscape Photography Workshop Anglesey is a large island of 220 square miles of mainly farmland, but the coastline is excellent for photography with sandy coves, harbours, and rocky headlands in addition to the lighthouses. We will also explore some other areas, Parys Mountain, once the world's biggest copper mine, which has been used in many science fiction films and TV shows for its Martian-like coloured appearance.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>coastal, Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1595</v>
+        <v>875</v>
       </c>
       <c r="I30" t="n">
-        <v>1595</v>
+        <v>875</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2117,22 +2117,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop NORFOLK - Coastal 13 - 15 Feb</t>
+          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 13th, 09:30am - Sun 15th Feb 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: Photography Workshop Norfolk - We will photograph the North Norfolk coastline ranging from Overstand and Cromer sea fronts and groynes to the atmospheric estuaries of Morston Quay and Blakeney Harbour. Beach huts, boats, estuaries, marshland, there is something for everyone on this 3 day North Norfolk photography workshop.Abandoned boats, windmills, nature reserve, sand dunes, coastal erosion, coastal path/estuary, optional seal trip and of course seascapes. The silting has left a fascinating landscape of marshes, sandhills and mud banks, with many creeks and channels twisting and turning their way through. Blakeney village is set on a small hill leading down to the harbour and has pretty flint cottages.</t>
+          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details: NorthumberlandDescription: Northumberland Photography Workshops - One of the highlights of Northumberland's landscape is its impressive collection of over seventy castles, the highest number in any English county. These historic fortresses not only showcase the region's rich heritage but also serve as captivating subjects for your photographs. The iconic Bamburgh Castle, dating back to the 11th century, stands majestically on a rocky outcrop, offering panoramic views of the surrounding coastline. Alnwick Castle, made famous by its appearance in the Harry Potter films, is another must-visit location for photography enthusiasts.Lindisfarne Castle and Dunstanburgh Castle are two other gems that beckon photographers with their unique charm. Lindisfarne Castle, perched on a basalt rock outcrop, creates a striking silhouette against the backdrop of the North Sea. Dunstanburgh Castle, situated atop a grassy cliff edge, is flanked by smooth black boulders on Embleton Beach, creating a dramatic composition that is sure to leave a lasting impression on your photographs.Sign up to Northumberland Photography Workshops - Coastline Photography to take your photography to the next level.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625462292-PCMT7Q118L1X51MPSENJ/Wells+Next+To+Sea+%2302+-+Sep+2022.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714235981485-EF5PRA0X9C6ZNGQUO265/dunstanburgh+boulders.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2142,26 +2142,26 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="I31" t="n">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2173,107 +2173,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Coventry - 1 Day</t>
+          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 30 May</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Suitable for any amateur who wants to learn the fundamentals of portrait photography - Coventry - 1-Day Course</t>
+          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: Embark on a captivating journey of long-exposure photography amidst the secluded Welsh valley of Nant Mill. Join us for an immersive workshop where you'll discover the mesmerizing art of capturing river and waterfall scenes in this ancient woodland near Wrexham.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707238641610-VHWSAVN4IPEHPVRGJNQZ/portrait+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="I32" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUFFOLK Landscape Photography Workshops - 6th-8th Feb</t>
+          <t>Landscape Photography Workshop NORFOLK - Coastal 20 - 22 Nov</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 6th 09:30 - Sun 8th 14:30 Feb 2026 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SuffolkDescription: Suffolk Landscape Photography Workshop - The Suffolk coastline offers a wide variety of views and caters for all styles and ways of interpreting the land and seascapes. There will be a rich mixture of coastal shoreline vista to shoreline architecture including piers, beach huts and iconic sea defence structures.</t>
+          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: Photography Workshop Norfolk - We will photograph the North Norfolk coastline ranging from Overstand and Cromer sea fronts and groynes to the atmospheric estuaries of Morston Quay and Blakeney Harbour. Beach huts, boats, estuaries, marshland, there is something for everyone on this 3 day North Norfolk photography workshop.Abandoned boats, windmills, nature reserve, sand dunes, coastal erosion, coastal path/estuary, optional seal trip and of course seascapes. The silting has left a fascinating landscape of marshes, sandhills and mud banks, with many creeks and channels twisting and turning their way through. Blakeney village is set on a small hill leading down to the harbour and has pretty flint cottages.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714650055069-5DPM44ERXSX234XAGLA9/Southwold+%2304+-+February+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625462292-PCMT7Q118L1X51MPSENJ/Wells+Next+To+Sea+%2302+-+Sep+2022.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>coastal, - weekend residential photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>995</v>
+        <v>1025</v>
       </c>
       <c r="I33" t="n">
-        <v>995</v>
+        <v>1025</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2285,51 +2285,51 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MACRO Photography Workshops Warwickshire - Feb and Mar</t>
+          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sat 8 Nov 10:00 - 12:30Macro Photography - Sun 17 May 10:00 - 12:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
+          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: We will be based near Dingle and visit some of the top spots around the Dingle Peninsula, South Kerry (Skellig Ring) and finally Killarney National Park.There is a wide variety of subjects: Mountains, Lakes, Waterfalls, Trees/woodlands, Coastline, Rock Formations to name a few. All set in stunning scenery to wow any visitor and photographer. We will visit several locations in a day, some are short 10-15 min stops (layby shoots) others will require more time to perfectly capturing the perfect moment with tides and light.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 17 May 10:00 - 12:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>65</v>
+        <v>1595</v>
       </c>
       <c r="I34" t="n">
-        <v>65</v>
+        <v>1595</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SQ8482281, SQ8660736</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SQ8482281</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2341,51 +2341,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
+          <t>MACRO Photography Workshops Warwickshire - Feb and Mar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: North YorkshireDescription: North Yorkshire Landscape Photography - We will be based on the northeast coast of England (North Yorkshire and the Moors) and visit some of the iconic coastlines of Staithes, Runswick, Whitby and more. We will concentrate our workshop time along the impressive coastline and work from sunrise to sunset to ensure we make use of the best light, tides and empty beaches. This is the perfect workshop for practising long exposures and working at sunrise and sunsets to get those iconic views on the coast.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sat 8 Nov 10:00 - 12:30Macro Photography - Sun 17 May 10:00 - 12:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707212716744-VYD7AYV9U6N6VEZ3C4D1/North+Yorkshire+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 17 May 10:00 - 12:30"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>1450</v>
+        <v>65</v>
       </c>
       <c r="I35" t="n">
-        <v>1450</v>
+        <v>65</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ8482281, SQ8660736</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ8482281</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2509,51 +2509,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 30-31 May</t>
+          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 30th - Sun 31st May 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
+          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SuffolkDescription: Suffolk Landscape Photography Workshop - The Suffolk coastline offers a wide variety of views and caters for all styles and ways of interpreting the land and seascapes. There will be a rich mixture of coastal shoreline vista to shoreline architecture including piers, beach huts and iconic sea defence structures.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714650055069-5DPM44ERXSX234XAGLA9/Southwold+%2304+-+February+2024.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>coastal, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>575</v>
+        <v>995</v>
       </c>
       <c r="I38" t="n">
-        <v>575</v>
+        <v>995</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
+          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DorsetDescription: The Dorset Photography Workshop along the coastline is an exciting and great part of the UK to capture seascapes. We will work around Durdle Door and surrounding areas to make coastal images. Not limited to just the classic seascapes we can cover any genre or style of photography, beit B&amp;W or abstract this prehistoric coastline offers lots of variety and scope to suit all interests.</t>
+          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: North YorkshireDescription: North Yorkshire Landscape Photography - We will be based on the northeast coast of England (North Yorkshire and the Moors) and visit some of the iconic coastlines of Staithes, Runswick, Whitby and more. We will concentrate our workshop time along the impressive coastline and work from sunrise to sunset to ensure we make use of the best light, tides and empty beaches. This is the perfect workshop for practising long exposures and working at sunrise and sunsets to get those iconic views on the coast.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707212716744-VYD7AYV9U6N6VEZ3C4D1/North+Yorkshire+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2590,26 +2590,26 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>925</v>
+        <v>1450</v>
       </c>
       <c r="I39" t="n">
-        <v>925</v>
+        <v>1450</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2621,51 +2621,51 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 16 Apr</t>
+          <t>WALES Photography Workshop | Lake Vyrnwy 30-31 May</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Thu 16 Apr 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: Join me on this evening urban architecture photography workshop and learn how to see and design images at night! We will walk around several historic parts of Coventry in this 2.5hr workshop, photographing buildings and ruins - all to practise the art of dealing with tricky light, learning how to focus in the dark, long exposures and hopefully some good skies to help us capture that big space above us.</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 30th - Sun 31st May 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>50</v>
+        <v>575</v>
       </c>
       <c r="I40" t="n">
-        <v>50</v>
+        <v>575</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2677,51 +2677,51 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
+          <t>Landscape Photography SNOWDONIA - Sat 26th - Sun 27th Sep 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Tue 31st Mar 2026 - 18:00 - 20:00Mon 13th Apr 2026 - 18:30 - 20:30Wed 6th May 2026 - 18:30 - 20:30Mon 11th May 2026 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: Join me for this evening Long Exposure Photography Workshop, where we will shoot Kenilworth Castle ruins against the night sky.Kenilworth Castle, formerly one of the strongest fortifications in the country, was reinvented in the Elizabethan era by Robert Dudley as an impressive palace for his queen. Initially built in the 1120s by Geoffrey de Clinton, the Norman keep served as a basis for the structure, and King John later added an external stone wall, as well as a reservoir, to the complex.</t>
+          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SnowdoniaDescription: Snowdonia National Park, located in North Wales, offers a diverse range of landscapes that will inspire and challenge any photographer. Snowdonia has everything from rugged mountains, flowing rivers, serene lakes, and ancient quarries.The park is home to some of the highest mountain ranges in England and Wales, providing a stunning backdrop for your photography journey. The terrain and landscape of Snowdonia, with its waterfalls, are great for long exposure techniques, the quarries and slate mines provide a starker but striking landscape to create images from the historic mining relics in the area, and last but not least, there are majestic lakes with reflections and mountains to practise and be inspired by to create compelling compositions from this rugged and serene landscape.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>595</v>
       </c>
       <c r="I41" t="n">
-        <v>50</v>
+        <v>595</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SQ7119101, SQ3245206, SQ6816264, SQ5325711</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SQ7119101</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2733,51 +2733,51 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Landscape Photography SNOWDONIA - Sat 7th - Sun 8th Mar 2026</t>
+          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 7th - Sun 8th Mar 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SnowdoniaDescription: Snowdonia National Park, located in North Wales, offers a diverse range of landscapes that will inspire and challenge any photographer. Snowdonia has everything from rugged mountains, flowing rivers, serene lakes, and ancient quarries.The park is home to some of the highest mountain ranges in England and Wales, providing a stunning backdrop for your photography journey. The terrain and landscape of Snowdonia, with its waterfalls, are great for long exposure techniques, the quarries and slate mines provide a starker but striking landscape to create images from the historic mining relics in the area, and last but not least, there are majestic lakes with reflections and mountains to practise and be inspired by to create compelling compositions from this rugged and serene landscape.</t>
+          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DorsetDescription: The Dorset Photography Workshop along the coastline is an exciting and great part of the UK to capture seascapes. We will work around Durdle Door and surrounding areas to make coastal images. Not limited to just the classic seascapes we can cover any genre or style of photography, beit B&amp;W or abstract this prehistoric coastline offers lots of variety and scope to suit all interests.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>595</v>
+        <v>925</v>
       </c>
       <c r="I42" t="n">
-        <v>595</v>
+        <v>925</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2789,51 +2789,51 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
+          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 16 Apr</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:2026 DatesSun May 17th 2026 - 15:00 - 17:00Sun Jul 12th 2026 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
+          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Thu 16 Apr 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: Join me on this evening urban architecture photography workshop and learn how to see and design images at night! We will walk around several historic parts of Coventry in this 2.5hr workshop, photographing buildings and ruins - all to practise the art of dealing with tricky light, learning how to focus in the dark, long exposures and hopefully some good skies to help us capture that big space above us.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I43" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SQ0939451, SQ3644687</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SQ0939451</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2845,51 +2845,51 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
+          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 3Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details: GowerDescription: Just a short distance away from Swansea, the Gower Peninsula is a remarkable sight for landscape photography in Wales.Gower is a truly unique environment that boasts heathlands, limestone grasslands, brackish and freshwater marshes, dunes and oak woodlands. It is characterised by a distinct combination of features, including lofty limestone cliffs, sandy beaches, and jagged rocky shores that together form its southern coastline. In the north, the coast is a series of tranquil salt marshes and dune systems. This is a perfect location for landscape photography Wales</t>
+          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Tue 31st Mar 2026 - 18:00 - 20:00Mon 13th Apr 2026 - 18:30 - 20:30Wed 6th May 2026 - 18:30 - 20:30Mon 11th May 2026 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: Join me for this evening Long Exposure Photography Workshop, where we will shoot Kenilworth Castle ruins against the night sky.Kenilworth Castle, formerly one of the strongest fortifications in the country, was reinvented in the Elizabethan era by Robert Dudley as an impressive palace for his queen. Initially built in the 1120s by Geoffrey de Clinton, the Norman keep served as a basis for the structure, and King John later added an external stone wall, as well as a reservoir, to the complex.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>825</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
-        <v>825</v>
+        <v>50</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ7119101, SQ3245206, SQ6816264, SQ5325711</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ7119101</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2901,51 +2901,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
+          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: Fireworks photography workshop Kenilworth. We will be photographing from outside the castle walls so you don't need to by a ticket for the display. Kenilworth castle acts an excellent backdrop for the amazing fireworks display organised by the Round Table every year.</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:2026 DatesSun May 17th 2026 - 15:00 - 17:00Sun Jul 12th 2026 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="I45" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ0939451, SQ3644687</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ0939451</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2957,22 +2957,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EXMOOR Photography Workshop - Sat 23rd - Sun 24th May 2026</t>
+          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 23rd 10:00 - Sun 24th May 15:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
+          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 3Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details: GowerDescription: Just a short distance away from Swansea, the Gower Peninsula is a remarkable sight for landscape photography in Wales.Gower is a truly unique environment that boasts heathlands, limestone grasslands, brackish and freshwater marshes, dunes and oak woodlands. It is characterised by a distinct combination of features, including lofty limestone cliffs, sandy beaches, and jagged rocky shores that together form its southern coastline. In the north, the coast is a series of tranquil salt marshes and dune systems. This is a perfect location for landscape photography Wales</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2982,26 +2982,26 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>575</v>
+        <v>825</v>
       </c>
       <c r="I46" t="n">
-        <v>575</v>
+        <v>825</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3013,51 +3013,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
+          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Sezincote is a Mughal Indian palace set in the Cotswold Hills, created by the nabob Charles Cockerell in 1805.The house is surmounted by a copper dome and minarets, and set in a picturesque water garden with seven pools, waterfalls, a grotto and a temple to Surya, the Hindu Sun God. A curving Orangery frames the Persian Garden of Paradise.</t>
+          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: Fireworks photography workshop Kenilworth. We will be photographing from outside the castle walls so you don't need to by a ticket for the display. Kenilworth castle acts an excellent backdrop for the amazing fireworks display organised by the Round Table every year.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I47" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3069,51 +3069,51 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
+          <t>EXMOOR Photography Workshop - Sat 23rd - Sun 24th May 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: HeathersDescription: Peak District heather WorkshopsSurprise View, perched atop Hathersage, is one of the best viewpoints in the Peak District. It's a perfect spot to admire the sunset and, on a clear night, is a designated 'Dark Skies' stargazing location. To access this special place, head uphill in a northerly direction from the car park and find the strangely shaped Mother Cap stone. Then, marvel at the vivid stars filling the Peak District's dark skies.The Roaches, with Hen Cloud and Ramshaw Rocks, form a gritstone escarpment that marks the Peak's south-western edge. Best viewed from the approach along the Leek road, they stand as a line of silent sentinels guarding the entrance to the Peak District, worn into fantastic shapes by the elements.</t>
+          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 23rd 10:00 - Sun 24th May 15:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707246605883-FVZKLJN54Z455J1Q13CV/peak+district+heather.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>125</v>
+        <v>575</v>
       </c>
       <c r="I48" t="n">
-        <v>200</v>
+        <v>575</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SQ1994489, SQ1389945, SQ5395624</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SQ1994489</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3125,51 +3125,51 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
+          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 19th Apr - SpringSun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: It will be different from other workshops in the format as it will be divided into separate sessions during the day to tackle theory, set-up, shooting, image review, and post-production.A theory session and discussion on woodland photography and its challenges and some answers, followed by practical advice on settings, lenses, equipment, etc.A presentation on developing creative vision and simplification in woodland settingsA 2hr woodland exploration and walk-making compositions and turning theory into practice in the field.Initial image reviews and critiques to shortlist images to editDemonstration, advice and post-production of your woodland images</t>
+          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: HeathersDescription: Peak District heather WorkshopsSurprise View, perched atop Hathersage, is one of the best viewpoints in the Peak District. It's a perfect spot to admire the sunset and, on a clear night, is a designated 'Dark Skies' stargazing location. To access this special place, head uphill in a northerly direction from the car park and find the strangely shaped Mother Cap stone. Then, marvel at the vivid stars filling the Peak District's dark skies.The Roaches, with Hen Cloud and Ramshaw Rocks, form a gritstone escarpment that marks the Peak's south-western edge. Best viewed from the approach along the Leek road, they stand as a line of silent sentinels guarding the entrance to the Peak District, worn into fantastic shapes by the elements.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707246605883-FVZKLJN54Z455J1Q13CV/peak+district+heather.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 19th Apr 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Sun 10 Jan 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
         <v>125</v>
       </c>
       <c r="I49" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SQ0512761, SQ4914997, SQ4894934, SQ2827052</t>
+          <t>SQ1994489, SQ1389945, SQ5395624</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SQ0512761</t>
+          <t>SQ1994489</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3181,51 +3181,51 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DARTMOOR Photography Workshop - Landscapes - 9th - 11th Oct</t>
+          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DartmoorDescription: Dartmoor Photography Workshop - Nestled amidst the stunning landscapes of southwest England, Dartmoor National Park presents a captivating playground for photographers of all levels. This diverse and dynamic environment boasts rugged moors, ancient woodlands, dramatic granite tors, mysterious valleys, and serene rivers – all waiting to be captured and immortalised in your photographs. From sunrise to sunset, each moment offers a spectacle of natural wonders ready to be transformed into breathtaking images.</t>
+          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Sezincote is a Mughal Indian palace set in the Cotswold Hills, created by the nabob Charles Cockerell in 1805.The house is surmounted by a copper dome and minarets, and set in a picturesque water garden with seven pools, waterfalls, a grotto and a temple to Surya, the Hindu Sun God. A curving Orangery frames the Persian Garden of Paradise.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>875</v>
+        <v>55</v>
       </c>
       <c r="I50" t="n">
-        <v>875</v>
+        <v>55</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3237,162 +3237,478 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Online Photography Classes 121 - Zoom - Package Options</t>
+          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Private online photography classes tailored to your needs - Tuition &amp; support on any aspect of photography - Pay Now - Book dates later.Online photography classes and support are run via Zoom (free to use)Must be used within 12 months of purchase dateIf you want a package (series) of lessons, these package options offer a discount for purchasing multiples. Mon - Fri - 9 am - 5 pm1 x 1hr - £50 - Normal Price for lesson4 x 1hr - 15% Off normal price6 x 1hr - 20% Off normal price8 x 1hr - 25% Off normal price12 x 1hr - 25% Off normal price</t>
+          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 19th Apr - SpringSun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: It will be different from other workshops in the format as it will be divided into separate sessions during the day to tackle theory, set-up, shooting, image review, and post-production.A theory session and discussion on woodland photography and its challenges and some answers, followed by practical advice on settings, lenses, equipment, etc.A presentation on developing creative vision and simplification in woodland settingsA 2hr woodland exploration and walk-making compositions and turning theory into practice in the field.Initial image reviews and critiques to shortlist images to editDemonstration, advice and post-production of your woodland images</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
+          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 19th Apr 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 10 Jan 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="I51" t="n">
-        <v>450</v>
+        <v>125</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
+          <t>SQ0512761, SQ4914997, SQ4894934, SQ2827052</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SQ1461156</t>
+          <t>SQ0512761</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Photo Print Preparation Service 30-min – File Check &amp; Advice</t>
+          <t>DARTMOOR Photography Workshop - Landscapes - 9th - 11th Oct</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Book a 30 min Photo Print Preparation Service. I check crop, aspect ratio and DPI, enlarge, retouch, sharpen and supply print-ready image for you to print</t>
+          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DartmoorDescription: Dartmoor Photography Workshop - Nestled amidst the stunning landscapes of southwest England, Dartmoor National Park presents a captivating playground for photographers of all levels. This diverse and dynamic environment boasts rugged moors, ancient woodlands, dramatic granite tors, mysterious valleys, and serene rivers – all waiting to be captured and immortalised in your photographs. From sunrise to sunset, each moment offers a spectacle of natural wonders ready to be transformed into breathtaking images.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photo-print-preparation-service-30min</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>29</v>
+        <v>875</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>875</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Premium Photography Academy Membership Subscription</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Premium Photography Academy Membership with Online Supported LearningSupported learning with tutoring: input, feedback &amp; troubleshootingDirect advice from Alan RangerIncludes everything in Foundation 101 plus:✓ 12 x Power Up Sessions (1 hr, 1-2-1 Zoom with Alan each month)✓ 4×30-min 1:1 coaching Zooms with Alan — targeted problem-solving✓ Image feedback or troubleshooting in every session✓ Exams and Certification Modules✓ eBook of all 60 Foundation Modules✓ 35 x 1 Page Field Checklists (PDF)✓ Free access to all new PDFs, exams, and add-ons released over the next 12 months.Fixed 12-month commitment (no pro-rata or early exit)</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/c9ec1c90-837a-4817-9d61-a6d3999e72eb/premium+photography+academy+membership.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/premium-photography-academy-membership</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops;pocket-guide-series;print, photography-gift-vouchers;photography-presents</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2906305", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-01-13", "priceValidUntil": "2027-01-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="I53" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>SQ2906305</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SQ2906305</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Alan Ranger Academy - Photography Foundation Course eBook</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Alan Ranger Academy - Photography Foundation Course eBook</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/578e5993-00d9-4963-9053-6241bc6c4336/Photography+Course+Sixty+Foundation+Modules-For+Beginners-.jpg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-foundation-course-ebook</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>25</v>
+      </c>
+      <c r="I54" t="n">
+        <v>25</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>15 Camera Settings — Photography Field Checklists PDF Bundle</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>15 Camera Settings — Photography Field Checklists PDF Bundle</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/camera-settings-photography-field-checklists</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>15</v>
+      </c>
+      <c r="I55" t="n">
+        <v>15</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10 Composition PDFs — Photography Field Checklists Bundle</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10 Composition PDFs — Photography Field Checklists Bundle</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/composition-settings-photography-field-checklists</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10 Genre PDFs — Photography Field Checklists Bundle</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10 Genre PDFs — Photography Field Checklists Bundle</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-genre-photography-field-checklists</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "10 Genre PDFs — Photography Field Checklists Bundle"}]</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-35bundle-photography-field-checklists</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" t="n">
+        <v>30</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/99e1a922-9f30-4f2a-a27e-5e7ba52c72de/Digital+Download+Product+1-+Academy.png</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/foundation-digital-pack-plus</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>69</v>
+      </c>
+      <c r="I59" t="n">
+        <v>69</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>product</t>
         </is>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1746549", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Thursdays - Mar 5 - Mar 19 Coventry"}, {"@type": "Offer", "sku": "SQ3510767", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Mondays - Mar 9 - Mar 23 Coventry"}, {"@type": "Offer", "sku": "SQ7826447", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Wednesdays - Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ0670010", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Tuesdays - Apr 7 - Apr 21 Coventry"}, {"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1746549", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Thursdays - Mar 5 - Mar 19 Coventry"}, {"@type": "Offer", "sku": "SQ3510767", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Mondays - Mar 9 - Mar 23 Coventry"}, {"@type": "Offer", "sku": "SQ7826447", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Wednesdays - Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ0670010", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Tuesdays - Apr 7 - Apr 21 Coventry"}, {"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 17 May 10:00 - 12:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 17 May 10:00 - 12:30"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 19th Apr 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Sun 10 Jan 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 19th Apr 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 10 Jan 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3426,7 +3426,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3478,7 +3478,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3530,7 +3530,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3582,7 +3582,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "10 Genre PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "10 Genre PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3634,7 +3634,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3686,7 +3686,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-15", "priceValidUntil": "2027-03-15", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1746549", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Thursdays - Mar 5 - Mar 19 Coventry"}, {"@type": "Offer", "sku": "SQ3510767", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Mondays - Mar 9 - Mar 23 Coventry"}, {"@type": "Offer", "sku": "SQ7826447", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Wednesdays - Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ0670010", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Tuesdays - Apr 7 - Apr 21 Coventry"}, {"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1746549", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Thursdays - Mar 5 - Mar 19 Coventry"}, {"@type": "Offer", "sku": "SQ3510767", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Mondays - Mar 9 - Mar 23 Coventry"}, {"@type": "Offer", "sku": "SQ7826447", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Wednesdays - Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ0670010", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Tuesdays - Apr 7 - Apr 21 Coventry"}, {"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 17 May 10:00 - 12:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 17 May 10:00 - 12:30"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 19th Apr 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Sun 10 Jan 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 19th Apr 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 10 Jan 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3426,7 +3426,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3478,7 +3478,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3530,7 +3530,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3582,7 +3582,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "10 Genre PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "10 Genre PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3634,7 +3634,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3686,7 +3686,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-16", "priceValidUntil": "2027-03-16", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -717,107 +717,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
+          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package Option - 4 Private Photography Classes Face to Face Coventry - 2 hrs each to suit you - Available 9-5 on weekdays. You will be sent a code to book dates</t>
+          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2025 - 09:30 - 11:30Crackley Wood, Kenilworth - Fri Nov 7Hay Woods - Solihull Fri Dec 5Tile Hill Nature Reserve Mon Dec 82026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: Simplifying Woodland Photography: Unlocking the Secrets to Capturing the Beauty of Nature on a photography walkMy aim is not to instruct you what to shoot, instead, I want to help you develop your own sense of visual awareness, photographic eye and your personal interpretation. I will be happy to help you with the “how to shoot” whatever it is you feel drawn to and wish to express through your creative vision using the camera to construct your intention. The photography walks around these selected woodlands are aimed to promote our senses and connection to trees/woodland/nature - as we walk, observe and take in our environment we may decide to make a photograph, or not.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495550918-139R34YFWLG3Q89CXENT/PRIVATE-PHOTOGRAPHY-LESSONS.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
+          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>360</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>360</v>
+        <v>15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ7078023, SQ3819844, SQ3142823, SQ1654264, SQ1288994, SQ0063623, SQ6524101</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ7078023</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Package Option - 4 Private Photography Classes Face to Face Coventry - 2 hrs each to suit you - Available 9-5 on weekdays. You will be sent a code to book dates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495550918-139R34YFWLG3Q89CXENT/PRIVATE-PHOTOGRAPHY-LESSONS.png</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>360</v>
       </c>
       <c r="I7" t="n">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SQ3248242</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -829,107 +829,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
+          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: 2026Daily From: Fri 23rd Oct to Fri 31st OctHalf-Day morning workshops are 8 am to 11.30 amHalf-Day afternoon workshops are from 12:00 pm to 3:30 pmOne Day workshops are 8 am to 3:30 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Details: Batsford ArboretumDescription: Batsford Arboretum always provides a terrific display of colour, texture and contrasts throughout Autumn. The Batsford Arboretum photography workshops are always very popular and and attract every level of photographer. There really is a complete range and choice for everyone here so it's not to be missed with expert guidance and support.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>250</v>
+        <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
+          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SQ4217445</t>
+          <t>SQ0818501</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>Monthly Photography Mentoring Sessions - Online - Zoom</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
+          <t>Photography mentoring online. Receive a monthly assignment to increase your skills across multiple genres and get expert feedback on your images each month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1559474612221-TBJKYSCMOO6IM7FTXJJI/online-photography-mentoring.png</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-online-photography-mentoring</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>online, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1200</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>3000</v>
+        <v>15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
+          <t>SQ1067929</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SQ0754560</t>
+          <t>SQ1067929</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -941,51 +941,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monthly Photography Mentoring Sessions - Online - Zoom</t>
+          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Photography mentoring online. Receive a monthly assignment to increase your skills across multiple genres and get expert feedback on your images each month</t>
+          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1559474612221-TBJKYSCMOO6IM7FTXJJI/online-photography-mentoring.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-online-photography-mentoring</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>online, photography-tuition, photography-courses</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ3248242</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -997,163 +997,163 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
+          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr- 01 May</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWParticipants: Max 4Time: 19:00 - 21:00Multi Course Start Dates: Beginners Photography Course3wks Thursdays - Mar 5 - Mar 19 Coventry3wks Mondays - Mar 9 - Mar 23 Coventry3wks Wednesdays - Apr 1 - Apr 15 Coventry3wks Tuesdays - Apr 7 - Apr 21 Coventry3wks Tuesdays - May 5 - May 19 Coventry3wks Thursdays - May 7 - May 21 Coventry3wks Tuesdays - Jun 2 - Jun 16 Coventry3wks Thursdays - Jun 11- Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 CoventryExperience - Level: Beginner and NoviceThis beginners photography course is aimed at anyone with a digital camera wishing to get off auto exposure mode and learn about key camera settings and composition to make better photos.Equipment Needed:You will need a DSLR or Mirrorless Camera with manual exposure modes.Alan will provide you with a course book covering all the topics for the course</t>
+          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Mon-20-Apr-26Tue-21-Apr-26Wed-22-Apr-26Thu-23-Apr-26Fri-24-Apr-26Sat-25-Apr-26Sun-26-Apr-26Mon-27-Apr-26Tue-28-Apr-26Wed-29-Apr-26Thu-30-Apr-26Fri-01-May-26Book and select either:4hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsJoin our Bluebell Woodland Photography Workshops in Warwickshire to explore beautiful bluebell woods and enhance your photography skills. Led by a professional photographer, you'll capture stunning photos while enjoying easy walks through bluebell trails and receive valuable photography tips for capturing spring blooms in soft woodland light.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/bceae6f2-91b8-4012-a00b-7b7b177d346f/Beginners+Photography+Classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1746549", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Thursdays - Mar 5 - Mar 19 Coventry"}, {"@type": "Offer", "sku": "SQ3510767", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Mondays - Mar 9 - Mar 23 Coventry"}, {"@type": "Offer", "sku": "SQ7826447", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Wednesdays - Apr 1 - Apr 15 Coventry"}, {"@type": "Offer", "sku": "SQ0670010", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Tuesdays - Apr 7 - Apr 21 Coventry"}, {"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H11" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="I11" t="n">
         <v>150</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SQ1746549, SQ3510767, SQ7826447, SQ0670010, SQ7702763, SQ6898365, SQ8880953, SQ0678506, SQ4322859, SQ5977532</t>
+          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510, SQ5723283, SQ7533033, SQ4478860</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SQ1746549</t>
+          <t>SQ8599409</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Intermediates Intentions Photography Project Course</t>
+          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire on this photography course | Coventry | 6-ClassesNO DATES SET FOR 2025 - Check back soon</t>
+          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I12" t="n">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ0754560</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
+          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
+          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
+          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>135.95</v>
+        <v>250</v>
       </c>
       <c r="I13" t="n">
-        <v>459.95</v>
+        <v>750</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
+          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SQ0105911</t>
+          <t>SQ4217445</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1165,331 +1165,331 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
+          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
+          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWParticipants: Max 4Time: 19:00 - 21:00Multi Course Start Dates: Beginners Photography Course3wks Tuesdays - May 5 - May 19 Coventry3wks Thursdays - May 7 - May 21 Coventry3wks Tuesdays - Jun 2 - Jun 16 Coventry3wks Thursdays - Jun 11- Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 CoventryExperience - Level: Beginner and NoviceThis beginners photography course is aimed at anyone with a digital camera wishing to get off auto exposure mode and learn about key camera settings and composition to make better photos.Equipment Needed:You will need a DSLR or Mirrorless Camera with manual exposure modes.Alan will provide you with a course book covering all the topics for the course</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/bceae6f2-91b8-4012-a00b-7b7b177d346f/Beginners+Photography+Classes.png</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>50.57</v>
+        <v>150</v>
       </c>
       <c r="I14" t="n">
-        <v>416.85</v>
+        <v>150</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
+          <t>SQ7702763, SQ6898365, SQ8880953, SQ0678506, SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SQ4872440</t>
+          <t>SQ7702763</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
+          <t>Intermediates Intentions Photography Project Course</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
+          <t>Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire on this photography course | Coventry | 6-ClassesNO DATES SET FOR 2025 - Check back soon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
+          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>133.85</v>
+        <v>400</v>
       </c>
       <c r="I15" t="n">
-        <v>356.9</v>
+        <v>400</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SQ6825544</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Coventry - 1 Day</t>
+          <t>Landscape Photography DEVON Workshops - Various Dates</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Suitable for any amateur who wants to learn the fundamentals of portrait photography - Coventry - 1-Day Course</t>
+          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 NightsFri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND FiltersPhotography Workshop Event Details: DevonDescription: Our landscape photography devon workshops are carefully crafted to provide you with an immersive and educational experience. Led by experienced and passionate photographers, these workshops offer a structured learning environment that ensures personal development and skill enhancement. From the moment you join us, you'll be guided through the intricacies of seascape photography, learning new techniques and refining your artistic vision.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707238641610-VHWSAVN4IPEHPVRGJNQZ/portrait+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>195</v>
+        <v>775</v>
       </c>
       <c r="I16" t="n">
-        <v>195</v>
+        <v>895</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ3856406, SQ2516659</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ3856406</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Online Photography Classes 121 - Zoom - Package Options</t>
+          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Private online photography classes tailored to your needs - Tuition &amp; support on any aspect of photography - Pay Now - Book dates later.Online photography classes and support are run via Zoom (free to use)Must be used within 12 months of purchase dateIf you want a package (series) of lessons, these package options offer a discount for purchasing multiples. Mon - Fri - 9 am - 5 pm1 x 1hr - £50 - Normal Price for lesson4 x 1hr - 15% Off normal price6 x 1hr - 20% Off normal price8 x 1hr - 25% Off normal price12 x 1hr - 25% Off normal price</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 30th Mar 2026 - 17:30 - 20:00Mon 18th May 2026 - 18:30 - 21:00Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>450</v>
+        <v>50</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
+          <t>SQ9554270, SQ5307067, SQ3572999, SQ0796814</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SQ1461156</t>
+          <t>SQ9554270</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Photo Print Preparation Service 30-min – File Check &amp; Advice</t>
+          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Book a 30 min Photo Print Preparation Service. I check crop, aspect ratio and DPI, enlarge, retouch, sharpen and supply print-ready image for you to print</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 7th Mar 2026 - 10:00 - 13:30Fri 8th May 2026 - 10:00 - 13:30Sat 26th Oct 2026 - 10:00 - 13:30Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photo-print-preparation-service-30min</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ1416930, SQ0434017, SQ8778402</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ1416930</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
+          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2025 - 09:30 - 11:30Crackley Wood, Kenilworth - Fri Nov 7Hay Woods - Solihull Fri Dec 5Tile Hill Nature Reserve Mon Dec 82026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: Simplifying Woodland Photography: Unlocking the Secrets to Capturing the Beauty of Nature on a photography walkMy aim is not to instruct you what to shoot, instead, I want to help you develop your own sense of visual awareness, photographic eye and your personal interpretation. I will be happy to help you with the “how to shoot” whatever it is you feel drawn to and wish to express through your creative vision using the camera to construct your intention. The photography walks around these selected woodlands are aimed to promote our senses and connection to trees/woodland/nature - as we walk, observe and take in our environment we may decide to make a photograph, or not.</t>
+          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: LavenderDescription: Join me in the Cotswolds for a spectacular sight of Lavender. We will shoot into the evening hours and capture some great colour - go abstract or vista; the choice is yours.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SQ7078023, SQ3819844, SQ3142823, SQ1654264, SQ1288994, SQ0063623, SQ6524101</t>
+          <t>SQ6748367, SQ7542811</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SQ7078023</t>
+          <t>SQ6748367</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1501,51 +1501,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
+          <t>Poppy Fields Photography Workshops | Worcestershire</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: 2026Daily From: Fri 23rd Oct to Fri 31st OctHalf-Day morning workshops are 8 am to 11.30 amHalf-Day afternoon workshops are from 12:00 pm to 3:30 pmOne Day workshops are 8 am to 3:30 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Details: Batsford ArboretumDescription: Batsford Arboretum always provides a terrific display of colour, texture and contrasts throughout Autumn. The Batsford Arboretum photography workshops are always very popular and and attract every level of photographer. There really is a complete range and choice for everyone here so it's not to be missed with expert guidance and support.</t>
+          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: Rolling hills full of poppies takes some beating. Join me for one of the poppy fields photography location shoots from early June to end of June in Worcestershire - These are provisional dates and may change depending on mother nature.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I20" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
+          <t>SQ8740143, SQ7189877</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SQ0818501</t>
+          <t>SQ8740143</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1557,51 +1557,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr- 01 May</t>
+          <t>BURNHAM ON SEA Long Exposure Photography Workshop 2 May</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Mon-20-Apr-26Tue-21-Apr-26Wed-22-Apr-26Thu-23-Apr-26Fri-24-Apr-26Sat-25-Apr-26Sun-26-Apr-26Mon-27-Apr-26Tue-28-Apr-26Wed-29-Apr-26Thu-30-Apr-26Fri-01-May-26Book and select either:4hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsJoin our Bluebell Woodland Photography Workshops in Warwickshire to explore beautiful bluebell woods and enhance your photography skills. Led by a professional photographer, you'll capture stunning photos while enjoying easy walks through bluebell trails and receive valuable photography tips for capturing spring blooms in soft woodland light.</t>
+          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 2nd May 2026 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: BurnhamDescription: Experience the magic of long exposure photography against the breathtaking backdrop of Burnham on Sea's iconic lighthouse. Join us for an unforgettable workshop where you'll master the art of capturing stunning sunset seascapes. Our expert instructors will guide you through the process, helping you harness the beauty of this picturesque location in Somerset</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
+          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510, SQ5723283, SQ7533033, SQ4478860</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SQ8599409</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1613,51 +1613,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
+          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 30th Mar 2026 - 17:30 - 20:00Mon 18th May 2026 - 18:30 - 21:00Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
+          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Lake DistrictDescription: We will be based in the north lakes and visit some of the top spots in the Lake District for photographs. The Lake District has been a favourite location for photographers for decades. It offers a rich variety of landscapes and the seasonal weather means it can be different every time you visit.The weather creates unique windows to capture, reflections, mist, stormy skies and subtle and strong colours - often all in the space of 1-2 days and sometimes just hours.We will visit approximately 2-3 locations a day in a weekend subject to the wishes of the group, time, weather and other factors: Sign up today for an amazing lake district photography workshop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>50</v>
+        <v>975</v>
       </c>
       <c r="I22" t="n">
-        <v>50</v>
+        <v>1125</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SQ9554270, SQ5307067, SQ3572999, SQ0796814</t>
+          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SQ9554270</t>
+          <t>SQ9100538</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1669,163 +1669,163 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Landscape Photography DEVON Workshops - Various Dates</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 NightsFri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND FiltersPhotography Workshop Event Details: DevonDescription: Our landscape photography devon workshops are carefully crafted to provide you with an immersive and educational experience. Led by experienced and passionate photographers, these workshops offer a structured learning environment that ensures personal development and skill enhancement. From the moment you join us, you'll be guided through the intricacies of seascape photography, learning new techniques and refining your artistic vision.</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>775</v>
+        <v>135.95</v>
       </c>
       <c r="I23" t="n">
-        <v>895</v>
+        <v>459.95</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SQ3856406, SQ2516659</t>
+          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SQ3856406</t>
+          <t>SQ0105911</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Poppy Fields Photography Workshops | Worcestershire</t>
+          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: Rolling hills full of poppies takes some beating. Join me for one of the poppy fields photography location shoots from early June to end of June in Worcestershire - These are provisional dates and may change depending on mother nature.</t>
+          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>95</v>
+        <v>50.57</v>
       </c>
       <c r="I24" t="n">
-        <v>95</v>
+        <v>416.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SQ8740143, SQ7189877</t>
+          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SQ8740143</t>
+          <t>SQ4872440</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
+          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 7th Mar 2026 - 10:00 - 13:30Fri 8th May 2026 - 10:00 - 13:30Sat 26th Oct 2026 - 10:00 - 13:30Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
+          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 16th May 2026 - 09:30 - 16:00Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="I25" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SQ1416930, SQ0434017, SQ8778402</t>
+          <t>SQ2363666, SQ3794821, SQ8457424, SQ9037810</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SQ1416930</t>
+          <t>SQ2363666</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1837,107 +1837,107 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BURNHAM ON SEA Long Exposure Photography Workshop 2 May</t>
+          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 2nd May 2026 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: BurnhamDescription: Experience the magic of long exposure photography against the breathtaking backdrop of Burnham on Sea's iconic lighthouse. Join us for an unforgettable workshop where you'll master the art of capturing stunning sunset seascapes. Our expert instructors will guide you through the process, helping you harness the beauty of this picturesque location in Somerset</t>
+          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
+          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>95</v>
+        <v>133.85</v>
       </c>
       <c r="I26" t="n">
-        <v>95</v>
+        <v>356.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ6825544</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
+          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: LavenderDescription: Join me in the Cotswolds for a spectacular sight of Lavender. We will shoot into the evening hours and capture some great colour - go abstract or vista; the choice is yours.</t>
+          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details: NorthumberlandDescription: Northumberland Photography Workshops - One of the highlights of Northumberland's landscape is its impressive collection of over seventy castles, the highest number in any English county. These historic fortresses not only showcase the region's rich heritage but also serve as captivating subjects for your photographs. The iconic Bamburgh Castle, dating back to the 11th century, stands majestically on a rocky outcrop, offering panoramic views of the surrounding coastline. Alnwick Castle, made famous by its appearance in the Harry Potter films, is another must-visit location for photography enthusiasts.Lindisfarne Castle and Dunstanburgh Castle are two other gems that beckon photographers with their unique charm. Lindisfarne Castle, perched on a basalt rock outcrop, creates a striking silhouette against the backdrop of the North Sea. Dunstanburgh Castle, situated atop a grassy cliff edge, is flanked by smooth black boulders on Embleton Beach, creating a dramatic composition that is sure to leave a lasting impression on your photographs.Sign up to Northumberland Photography Workshops - Coastline Photography to take your photography to the next level.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714235981485-EF5PRA0X9C6ZNGQUO265/dunstanburgh+boulders.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>150</v>
+        <v>995</v>
       </c>
       <c r="I27" t="n">
-        <v>150</v>
+        <v>995</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SQ6748367, SQ7542811</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SQ6748367</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1949,51 +1949,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
+          <t>ANGLESEY Landscape Photography Workshop -  May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Lake DistrictDescription: We will be based in the north lakes and visit some of the top spots in the Lake District for photographs. The Lake District has been a favourite location for photographers for decades. It offers a rich variety of landscapes and the seasonal weather means it can be different every time you visit.The weather creates unique windows to capture, reflections, mist, stormy skies and subtle and strong colours - often all in the space of 1-2 days and sometimes just hours.We will visit approximately 2-3 locations a day in a weekend subject to the wishes of the group, time, weather and other factors: Sign up today for an amazing lake district photography workshop</t>
+          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 8th May 15:00 - Sun 10th May 14:00, 2026Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Anglesey PhotographyDescription: A great location for a Landscape Photography Workshop Anglesey is a large island of 220 square miles of mainly farmland, but the coastline is excellent for photography with sandy coves, harbours, and rocky headlands in addition to the lighthouses. We will also explore some other areas, Parys Mountain, once the world's biggest copper mine, which has been used in many science fiction films and TV shows for its Martian-like coloured appearance.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>coastal, Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>975</v>
+        <v>875</v>
       </c>
       <c r="I28" t="n">
-        <v>1125</v>
+        <v>875</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SQ9100538</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2005,51 +2005,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
+          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 30 May</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 16th May 2026 - 09:30 - 16:00Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
+          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: Embark on a captivating journey of long-exposure photography amidst the secluded Welsh valley of Nant Mill. Join us for an immersive workshop where you'll discover the mesmerizing art of capturing river and waterfall scenes in this ancient woodland near Wrexham.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="I29" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SQ2363666, SQ3794821, SQ8457424, SQ9037810</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SQ2363666</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2061,51 +2061,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ANGLESEY Landscape Photography Workshop -  May 2026</t>
+          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 8th May 15:00 - Sun 10th May 14:00, 2026Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Anglesey PhotographyDescription: A great location for a Landscape Photography Workshop Anglesey is a large island of 220 square miles of mainly farmland, but the coastline is excellent for photography with sandy coves, harbours, and rocky headlands in addition to the lighthouses. We will also explore some other areas, Parys Mountain, once the world's biggest copper mine, which has been used in many science fiction films and TV shows for its Martian-like coloured appearance.</t>
+          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: We will be based near Dingle and visit some of the top spots around the Dingle Peninsula, South Kerry (Skellig Ring) and finally Killarney National Park.There is a wide variety of subjects: Mountains, Lakes, Waterfalls, Trees/woodlands, Coastline, Rock Formations to name a few. All set in stunning scenery to wow any visitor and photographer. We will visit several locations in a day, some are short 10-15 min stops (layby shoots) others will require more time to perfectly capturing the perfect moment with tides and light.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>coastal, Landscape, - weekend residential photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>875</v>
+        <v>1595</v>
       </c>
       <c r="I30" t="n">
-        <v>875</v>
+        <v>1595</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2117,22 +2117,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
+          <t>Landscape Photography Workshop NORFOLK - Coastal 20 - 22 Nov</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details: NorthumberlandDescription: Northumberland Photography Workshops - One of the highlights of Northumberland's landscape is its impressive collection of over seventy castles, the highest number in any English county. These historic fortresses not only showcase the region's rich heritage but also serve as captivating subjects for your photographs. The iconic Bamburgh Castle, dating back to the 11th century, stands majestically on a rocky outcrop, offering panoramic views of the surrounding coastline. Alnwick Castle, made famous by its appearance in the Harry Potter films, is another must-visit location for photography enthusiasts.Lindisfarne Castle and Dunstanburgh Castle are two other gems that beckon photographers with their unique charm. Lindisfarne Castle, perched on a basalt rock outcrop, creates a striking silhouette against the backdrop of the North Sea. Dunstanburgh Castle, situated atop a grassy cliff edge, is flanked by smooth black boulders on Embleton Beach, creating a dramatic composition that is sure to leave a lasting impression on your photographs.Sign up to Northumberland Photography Workshops - Coastline Photography to take your photography to the next level.</t>
+          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: Photography Workshop Norfolk - We will photograph the North Norfolk coastline ranging from Overstand and Cromer sea fronts and groynes to the atmospheric estuaries of Morston Quay and Blakeney Harbour. Beach huts, boats, estuaries, marshland, there is something for everyone on this 3 day North Norfolk photography workshop.Abandoned boats, windmills, nature reserve, sand dunes, coastal erosion, coastal path/estuary, optional seal trip and of course seascapes. The silting has left a fascinating landscape of marshes, sandhills and mud banks, with many creeks and channels twisting and turning their way through. Blakeney village is set on a small hill leading down to the harbour and has pretty flint cottages.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714235981485-EF5PRA0X9C6ZNGQUO265/dunstanburgh+boulders.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625462292-PCMT7Q118L1X51MPSENJ/Wells+Next+To+Sea+%2302+-+Sep+2022.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2142,26 +2142,26 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>995</v>
+        <v>1025</v>
       </c>
       <c r="I31" t="n">
-        <v>995</v>
+        <v>1025</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2173,107 +2173,107 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 30 May</t>
+          <t>Beginners Portrait Photography Course - Coventry - 1 Day</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: Embark on a captivating journey of long-exposure photography amidst the secluded Welsh valley of Nant Mill. Join us for an immersive workshop where you'll discover the mesmerizing art of capturing river and waterfall scenes in this ancient woodland near Wrexham.</t>
+          <t>Beginners Portrait Photography Course - Suitable for any amateur who wants to learn the fundamentals of portrait photography - Coventry - 1-Day Course</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707238641610-VHWSAVN4IPEHPVRGJNQZ/portrait+photography+course.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="I32" t="n">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop NORFOLK - Coastal 20 - 22 Nov</t>
+          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: Photography Workshop Norfolk - We will photograph the North Norfolk coastline ranging from Overstand and Cromer sea fronts and groynes to the atmospheric estuaries of Morston Quay and Blakeney Harbour. Beach huts, boats, estuaries, marshland, there is something for everyone on this 3 day North Norfolk photography workshop.Abandoned boats, windmills, nature reserve, sand dunes, coastal erosion, coastal path/estuary, optional seal trip and of course seascapes. The silting has left a fascinating landscape of marshes, sandhills and mud banks, with many creeks and channels twisting and turning their way through. Blakeney village is set on a small hill leading down to the harbour and has pretty flint cottages.</t>
+          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SuffolkDescription: Suffolk Landscape Photography Workshop - The Suffolk coastline offers a wide variety of views and caters for all styles and ways of interpreting the land and seascapes. There will be a rich mixture of coastal shoreline vista to shoreline architecture including piers, beach huts and iconic sea defence structures.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625462292-PCMT7Q118L1X51MPSENJ/Wells+Next+To+Sea+%2302+-+Sep+2022.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714650055069-5DPM44ERXSX234XAGLA9/Southwold+%2304+-+February+2024.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>coastal, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1025</v>
+        <v>995</v>
       </c>
       <c r="I33" t="n">
-        <v>1025</v>
+        <v>995</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2285,51 +2285,51 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
+          <t>MACRO Photography Workshops Warwickshire - Feb and Mar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: We will be based near Dingle and visit some of the top spots around the Dingle Peninsula, South Kerry (Skellig Ring) and finally Killarney National Park.There is a wide variety of subjects: Mountains, Lakes, Waterfalls, Trees/woodlands, Coastline, Rock Formations to name a few. All set in stunning scenery to wow any visitor and photographer. We will visit several locations in a day, some are short 10-15 min stops (layby shoots) others will require more time to perfectly capturing the perfect moment with tides and light.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sat 8 Nov 10:00 - 12:30Macro Photography - Sun 17 May 10:00 - 12:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 17 May 10:00 - 12:30"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>1595</v>
+        <v>65</v>
       </c>
       <c r="I34" t="n">
-        <v>1595</v>
+        <v>65</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ8482281, SQ8660736</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ8482281</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2341,51 +2341,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MACRO Photography Workshops Warwickshire - Feb and Mar</t>
+          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sat 8 Nov 10:00 - 12:30Macro Photography - Sun 17 May 10:00 - 12:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
+          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: North YorkshireDescription: North Yorkshire Landscape Photography - We will be based on the northeast coast of England (North Yorkshire and the Moors) and visit some of the iconic coastlines of Staithes, Runswick, Whitby and more. We will concentrate our workshop time along the impressive coastline and work from sunrise to sunset to ensure we make use of the best light, tides and empty beaches. This is the perfect workshop for practising long exposures and working at sunrise and sunsets to get those iconic views on the coast.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707212716744-VYD7AYV9U6N6VEZ3C4D1/North+Yorkshire+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 17 May 10:00 - 12:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>65</v>
+        <v>1450</v>
       </c>
       <c r="I35" t="n">
-        <v>65</v>
+        <v>1450</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SQ8482281, SQ8660736</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SQ8482281</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2509,51 +2509,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
+          <t>WALES Photography Workshop | Lake Vyrnwy 30-31 May</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SuffolkDescription: Suffolk Landscape Photography Workshop - The Suffolk coastline offers a wide variety of views and caters for all styles and ways of interpreting the land and seascapes. There will be a rich mixture of coastal shoreline vista to shoreline architecture including piers, beach huts and iconic sea defence structures.</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 30th - Sun 31st May 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714650055069-5DPM44ERXSX234XAGLA9/Southwold+%2304+-+February+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>coastal, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>995</v>
+        <v>575</v>
       </c>
       <c r="I38" t="n">
-        <v>995</v>
+        <v>575</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2565,22 +2565,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
+          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: North YorkshireDescription: North Yorkshire Landscape Photography - We will be based on the northeast coast of England (North Yorkshire and the Moors) and visit some of the iconic coastlines of Staithes, Runswick, Whitby and more. We will concentrate our workshop time along the impressive coastline and work from sunrise to sunset to ensure we make use of the best light, tides and empty beaches. This is the perfect workshop for practising long exposures and working at sunrise and sunsets to get those iconic views on the coast.</t>
+          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DorsetDescription: The Dorset Photography Workshop along the coastline is an exciting and great part of the UK to capture seascapes. We will work around Durdle Door and surrounding areas to make coastal images. Not limited to just the classic seascapes we can cover any genre or style of photography, beit B&amp;W or abstract this prehistoric coastline offers lots of variety and scope to suit all interests.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707212716744-VYD7AYV9U6N6VEZ3C4D1/North+Yorkshire+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2590,26 +2590,26 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1450</v>
+        <v>925</v>
       </c>
       <c r="I39" t="n">
-        <v>1450</v>
+        <v>925</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2621,51 +2621,51 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 30-31 May</t>
+          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 30th - Sun 31st May 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
+          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: Join me on this evening urban architecture photography workshop and learn how to see and design images at night! We will walk around several historic parts of Coventry in this 2.5hr workshop, photographing buildings and ruins - all to practise the art of dealing with tricky light, learning how to focus in the dark, long exposures and hopefully some good skies to help us capture that big space above us.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>575</v>
+        <v>50</v>
       </c>
       <c r="I40" t="n">
-        <v>575</v>
+        <v>50</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2677,51 +2677,51 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Landscape Photography SNOWDONIA - Sat 26th - Sun 27th Sep 2026</t>
+          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SnowdoniaDescription: Snowdonia National Park, located in North Wales, offers a diverse range of landscapes that will inspire and challenge any photographer. Snowdonia has everything from rugged mountains, flowing rivers, serene lakes, and ancient quarries.The park is home to some of the highest mountain ranges in England and Wales, providing a stunning backdrop for your photography journey. The terrain and landscape of Snowdonia, with its waterfalls, are great for long exposure techniques, the quarries and slate mines provide a starker but striking landscape to create images from the historic mining relics in the area, and last but not least, there are majestic lakes with reflections and mountains to practise and be inspired by to create compelling compositions from this rugged and serene landscape.</t>
+          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Tue 31st Mar 2026 - 18:00 - 20:00Mon 13th Apr 2026 - 18:30 - 20:30Wed 6th May 2026 - 18:30 - 20:30Mon 11th May 2026 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: Join me for this evening Long Exposure Photography Workshop, where we will shoot Kenilworth Castle ruins against the night sky.Kenilworth Castle, formerly one of the strongest fortifications in the country, was reinvented in the Elizabethan era by Robert Dudley as an impressive palace for his queen. Initially built in the 1120s by Geoffrey de Clinton, the Norman keep served as a basis for the structure, and King John later added an external stone wall, as well as a reservoir, to the complex.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>595</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
-        <v>595</v>
+        <v>50</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ7119101, SQ3245206, SQ6816264, SQ5325711</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ7119101</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2733,51 +2733,51 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
+          <t>Landscape Photography SNOWDONIA - Sat 26 - Sun 27 Sep 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DorsetDescription: The Dorset Photography Workshop along the coastline is an exciting and great part of the UK to capture seascapes. We will work around Durdle Door and surrounding areas to make coastal images. Not limited to just the classic seascapes we can cover any genre or style of photography, beit B&amp;W or abstract this prehistoric coastline offers lots of variety and scope to suit all interests.</t>
+          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SnowdoniaDescription: Snowdonia National Park, located in North Wales, offers a diverse range of landscapes that will inspire and challenge any photographer. Snowdonia has everything from rugged mountains, flowing rivers, serene lakes, and ancient quarries.The park is home to some of the highest mountain ranges in England and Wales, providing a stunning backdrop for your photography journey. The terrain and landscape of Snowdonia, with its waterfalls, are great for long exposure techniques, the quarries and slate mines provide a starker but striking landscape to create images from the historic mining relics in the area, and last but not least, there are majestic lakes with reflections and mountains to practise and be inspired by to create compelling compositions from this rugged and serene landscape.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>925</v>
+        <v>595</v>
       </c>
       <c r="I42" t="n">
-        <v>925</v>
+        <v>595</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2789,51 +2789,51 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 16 Apr</t>
+          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Thu 16 Apr 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: Join me on this evening urban architecture photography workshop and learn how to see and design images at night! We will walk around several historic parts of Coventry in this 2.5hr workshop, photographing buildings and ruins - all to practise the art of dealing with tricky light, learning how to focus in the dark, long exposures and hopefully some good skies to help us capture that big space above us.</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:2026 DatesSun May 17th 2026 - 15:00 - 17:00Sun Jul 12th 2026 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ0939451, SQ3644687</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ0939451</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2845,51 +2845,51 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
+          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Tue 31st Mar 2026 - 18:00 - 20:00Mon 13th Apr 2026 - 18:30 - 20:30Wed 6th May 2026 - 18:30 - 20:30Mon 11th May 2026 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: Join me for this evening Long Exposure Photography Workshop, where we will shoot Kenilworth Castle ruins against the night sky.Kenilworth Castle, formerly one of the strongest fortifications in the country, was reinvented in the Elizabethan era by Robert Dudley as an impressive palace for his queen. Initially built in the 1120s by Geoffrey de Clinton, the Norman keep served as a basis for the structure, and King John later added an external stone wall, as well as a reservoir, to the complex.</t>
+          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 3Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details: GowerDescription: Just a short distance away from Swansea, the Gower Peninsula is a remarkable sight for landscape photography in Wales.Gower is a truly unique environment that boasts heathlands, limestone grasslands, brackish and freshwater marshes, dunes and oak woodlands. It is characterised by a distinct combination of features, including lofty limestone cliffs, sandy beaches, and jagged rocky shores that together form its southern coastline. In the north, the coast is a series of tranquil salt marshes and dune systems. This is a perfect location for landscape photography Wales</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>825</v>
       </c>
       <c r="I44" t="n">
-        <v>50</v>
+        <v>825</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SQ7119101, SQ3245206, SQ6816264, SQ5325711</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SQ7119101</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2901,51 +2901,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
+          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:2026 DatesSun May 17th 2026 - 15:00 - 17:00Sun Jul 12th 2026 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
+          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: Fireworks photography workshop Kenilworth. We will be photographing from outside the castle walls so you don't need to by a ticket for the display. Kenilworth castle acts an excellent backdrop for the amazing fireworks display organised by the Round Table every year.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="I45" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SQ0939451, SQ3644687</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SQ0939451</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2957,22 +2957,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
+          <t>EXMOOR Photography Workshop - Sat 23rd - Sun 24th May 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 3Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details: GowerDescription: Just a short distance away from Swansea, the Gower Peninsula is a remarkable sight for landscape photography in Wales.Gower is a truly unique environment that boasts heathlands, limestone grasslands, brackish and freshwater marshes, dunes and oak woodlands. It is characterised by a distinct combination of features, including lofty limestone cliffs, sandy beaches, and jagged rocky shores that together form its southern coastline. In the north, the coast is a series of tranquil salt marshes and dune systems. This is a perfect location for landscape photography Wales</t>
+          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 23rd 10:00 - Sun 24th May 15:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2982,26 +2982,26 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>825</v>
+        <v>575</v>
       </c>
       <c r="I46" t="n">
-        <v>825</v>
+        <v>575</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3013,51 +3013,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
+          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: Fireworks photography workshop Kenilworth. We will be photographing from outside the castle walls so you don't need to by a ticket for the display. Kenilworth castle acts an excellent backdrop for the amazing fireworks display organised by the Round Table every year.</t>
+          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Sezincote is a Mughal Indian palace set in the Cotswold Hills, created by the nabob Charles Cockerell in 1805.The house is surmounted by a copper dome and minarets, and set in a picturesque water garden with seven pools, waterfalls, a grotto and a temple to Surya, the Hindu Sun God. A curving Orangery frames the Persian Garden of Paradise.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="I47" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3069,51 +3069,51 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EXMOOR Photography Workshop - Sat 23rd - Sun 24th May 2026</t>
+          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 23rd 10:00 - Sun 24th May 15:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
+          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: HeathersDescription: Peak District heather WorkshopsSurprise View, perched atop Hathersage, is one of the best viewpoints in the Peak District. It's a perfect spot to admire the sunset and, on a clear night, is a designated 'Dark Skies' stargazing location. To access this special place, head uphill in a northerly direction from the car park and find the strangely shaped Mother Cap stone. Then, marvel at the vivid stars filling the Peak District's dark skies.The Roaches, with Hen Cloud and Ramshaw Rocks, form a gritstone escarpment that marks the Peak's south-western edge. Best viewed from the approach along the Leek road, they stand as a line of silent sentinels guarding the entrance to the Peak District, worn into fantastic shapes by the elements.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707246605883-FVZKLJN54Z455J1Q13CV/peak+district+heather.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>575</v>
+        <v>125</v>
       </c>
       <c r="I48" t="n">
-        <v>575</v>
+        <v>200</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ1994489, SQ1389945, SQ5395624</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ1994489</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3125,51 +3125,51 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
+          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: HeathersDescription: Peak District heather WorkshopsSurprise View, perched atop Hathersage, is one of the best viewpoints in the Peak District. It's a perfect spot to admire the sunset and, on a clear night, is a designated 'Dark Skies' stargazing location. To access this special place, head uphill in a northerly direction from the car park and find the strangely shaped Mother Cap stone. Then, marvel at the vivid stars filling the Peak District's dark skies.The Roaches, with Hen Cloud and Ramshaw Rocks, form a gritstone escarpment that marks the Peak's south-western edge. Best viewed from the approach along the Leek road, they stand as a line of silent sentinels guarding the entrance to the Peak District, worn into fantastic shapes by the elements.</t>
+          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: It will be different from other workshops in the format as it will be divided into separate sessions during the day to tackle theory, set-up, shooting, image review, and post-production.A theory session and discussion on woodland photography and its challenges and some answers, followed by practical advice on settings, lenses, equipment, etc.A presentation on developing creative vision and simplification in woodland settingsA 2hr woodland exploration and walk-making compositions and turning theory into practice in the field.Initial image reviews and critiques to shortlist images to editDemonstration, advice and post-production of your woodland images</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707246605883-FVZKLJN54Z455J1Q13CV/peak+district+heather.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
+          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
         <v>125</v>
       </c>
       <c r="I49" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SQ1994489, SQ1389945, SQ5395624</t>
+          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SQ1994489</t>
+          <t>SQ4914997</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3181,51 +3181,51 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
+          <t>DARTMOOR Photography Workshop - Landscapes - 9th - 11th Oct</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Sezincote is a Mughal Indian palace set in the Cotswold Hills, created by the nabob Charles Cockerell in 1805.The house is surmounted by a copper dome and minarets, and set in a picturesque water garden with seven pools, waterfalls, a grotto and a temple to Surya, the Hindu Sun God. A curving Orangery frames the Persian Garden of Paradise.</t>
+          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DartmoorDescription: Dartmoor Photography Workshop - Nestled amidst the stunning landscapes of southwest England, Dartmoor National Park presents a captivating playground for photographers of all levels. This diverse and dynamic environment boasts rugged moors, ancient woodlands, dramatic granite tors, mysterious valleys, and serene rivers – all waiting to be captured and immortalised in your photographs. From sunrise to sunset, each moment offers a spectacle of natural wonders ready to be transformed into breathtaking images.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>55</v>
+        <v>875</v>
       </c>
       <c r="I50" t="n">
-        <v>55</v>
+        <v>875</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3237,112 +3237,112 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
+          <t>Online Photography Classes 121 - Zoom - Package Options</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 19th Apr - SpringSun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: It will be different from other workshops in the format as it will be divided into separate sessions during the day to tackle theory, set-up, shooting, image review, and post-production.A theory session and discussion on woodland photography and its challenges and some answers, followed by practical advice on settings, lenses, equipment, etc.A presentation on developing creative vision and simplification in woodland settingsA 2hr woodland exploration and walk-making compositions and turning theory into practice in the field.Initial image reviews and critiques to shortlist images to editDemonstration, advice and post-production of your woodland images</t>
+          <t>Private online photography classes tailored to your needs - Tuition &amp; support on any aspect of photography - Pay Now - Book dates later.Online photography classes and support are run via Zoom (free to use)Must be used within 12 months of purchase dateIf you want a package (series) of lessons, these package options offer a discount for purchasing multiples. Mon - Fri - 9 am - 5 pm1 x 1hr - £50 - Normal Price for lesson4 x 1hr - 15% Off normal price6 x 1hr - 20% Off normal price8 x 1hr - 25% Off normal price12 x 1hr - 25% Off normal price</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 19th Apr 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Sun 10 Jan 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="I51" t="n">
-        <v>125</v>
+        <v>450</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SQ0512761, SQ4914997, SQ4894934, SQ2827052</t>
+          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SQ0512761</t>
+          <t>SQ1461156</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DARTMOOR Photography Workshop - Landscapes - 9th - 11th Oct</t>
+          <t>Photo Print Preparation Service 30-min – File Check &amp; Advice</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DartmoorDescription: Dartmoor Photography Workshop - Nestled amidst the stunning landscapes of southwest England, Dartmoor National Park presents a captivating playground for photographers of all levels. This diverse and dynamic environment boasts rugged moors, ancient woodlands, dramatic granite tors, mysterious valleys, and serene rivers – all waiting to be captured and immortalised in your photographs. From sunrise to sunset, each moment offers a spectacle of natural wonders ready to be transformed into breathtaking images.</t>
+          <t>Book a 30 min Photo Print Preparation Service. I check crop, aspect ratio and DPI, enlarge, retouch, sharpen and supply print-ready image for you to print</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/photo-print-preparation-service-30min</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>photography-services</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>875</v>
+        <v>29</v>
       </c>
       <c r="I52" t="n">
-        <v>875</v>
+        <v>29</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ5582230</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ5582230</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3426,7 +3426,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3478,7 +3478,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3530,7 +3530,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3561,12 +3561,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10 Genre PDFs — Photography Field Checklists Bundle</t>
+          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10 Genre PDFs — Photography Field Checklists Bundle</t>
+          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-genre-photography-field-checklists</t>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-35bundle-photography-field-checklists</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "10 Genre PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-</t>
+          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>SUP-10-GENRE-PDFS-PHOTOGRAPHY-FIELD-</t>
+          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3613,102 +3613,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
+          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
+          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/99e1a922-9f30-4f2a-a27e-5e7ba52c72de/Digital+Download+Product+1-+Academy.png</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-35bundle-photography-field-checklists</t>
+          <t>https://www.alanranger.com/photography-services-near-me/foundation-digital-pack-plus</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="I58" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
+          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
+          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/99e1a922-9f30-4f2a-a27e-5e7ba52c72de/Digital+Download+Product+1-+Academy.png</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/foundation-digital-pack-plus</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-03-17", "priceValidUntil": "2027-03-17", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>69</v>
-      </c>
-      <c r="I59" t="n">
-        <v>69</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
         <is>
           <t>product</t>
         </is>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -493,372 +493,372 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Professional Black and White Photography Course | Coventry</t>
+          <t>MACRO Photography Workshops Warwickshire - Feb and Mar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Enter the date of the event on Customer Information Notes Field when you go through the checkout process. Black and White Photography Course for beginners</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sat 8 Nov 10:00 - 12:30Macro Photography - Sun 17 May 10:00 - 12:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/b8c2a6b2-9a51-492d-a6c0-b685f5e16cc2/Beginners+Photography+Classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/black-and-white-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>photography-courses</t>
+          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 17 May 10:00 - 12:30"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="I2" t="n">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SQ9709344</t>
+          <t>SQ8482281, SQ8660736</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SQ9709344</t>
+          <t>SQ8482281</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
+          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventrySummaryLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 3 Weekly 2hr Evening Classes - All evening classes are from 19:00 to 21:00Participants: Max 3Lightroom Courses Event Details: Editing CourseCoventry 3 wks - Wed 4 Mar - 18 Mar 2026Coventry 3 wks - Wed 13 May - 27 May 2026Coventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Experience - Level: BeginnersThe beginners Lightroom photo editing classes are aimed at anyone wishing to learn photo editing and photo management with a workflow and consistencyEquipment Needed:You will need a laptop with Adobe Lightroom Classic subscription and the App installedAlan will provide you with training Lightroom Library with images and use that to explain and then demonstrate the various tools</t>
+          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
+          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photo editing, lightroom</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="I3" t="n">
-        <v>150</v>
+        <v>3000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SQ6876661, SQ0415856, SQ7526725, SQ6831161</t>
+          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SQ6876661</t>
+          <t>SQ0754560</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
+          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select six online Zoom sessions within twelve months at intervals to suit youRPS Courses - Mentoring for DistinctionsParticipants: Via Zoom online in a group of max 3, or on 1-2-1 basis.Equipment Needed: Zoom AppDropbox App used for updated portfolios and imagesTerms: Sessions must be taken within 12 months of booking the course or forfeited, but there are options to extend the timeline and retain unused classes or add additional classes.Method:Technical and creative critique with suggestions for improvementAdvice on image selection and panel layoutMore Details about the RPS Mentoring Course*Note: Your tutor, Alan Ranger, holds both the RPS's Licentiate and Associate Distinctions, but the RPS does not accredit this Course. This is not an approved course or endorsed by the RPS as an organisation. Alan’s advice is private, unofficial and based on his experience and understanding of the elements required to reach the standard that may result in being awarded a distinction without any guarantee.</t>
+          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: 2026Daily From: Fri 23rd Oct to Fri 31st OctHalf-Day morning workshops are 8 am to 11.30 amHalf-Day afternoon workshops are from 12:00 pm to 3:30 pmOne Day workshops are 8 am to 3:30 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Details: Batsford ArboretumDescription: Batsford Arboretum always provides a terrific display of colour, texture and contrasts throughout Autumn. The Batsford Arboretum photography workshops are always very popular and and attract every level of photographer. There really is a complete range and choice for everyone here so it's not to be missed with expert guidance and support.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
+          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="I4" t="n">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SQ3499847, SQ5925235, SQ1898169, SQ7296901, SQ4136369</t>
+          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SQ3499847</t>
+          <t>SQ0818501</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
+          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
+          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWParticipants: Max 4Time: 19:00 - 21:00Multi Course Start Dates: Beginners Photography Course3wks Tuesdays - May 5 - May 19 Coventry3wks Thursdays - May 7 - May 21 Coventry3wks Tuesdays - Jun 2 - Jun 16 Coventry3wks Thursdays - Jun 11- Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 CoventryExperience - Level: Beginner and NoviceThis beginners photography course is aimed at anyone with a digital camera wishing to get off auto exposure mode and learn about key camera settings and composition to make better photos.Equipment Needed:You will need a DSLR or Mirrorless Camera with manual exposure modes.Alan will provide you with a course book covering all the topics for the course</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/bceae6f2-91b8-4012-a00b-7b7b177d346f/Beginners+Photography+Classes.png</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ7702763, SQ6898365, SQ8880953, SQ0678506, SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ7702763</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
+          <t>Beginners Portrait Photography Course - Coventry - 1 Day</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2025 - 09:30 - 11:30Crackley Wood, Kenilworth - Fri Nov 7Hay Woods - Solihull Fri Dec 5Tile Hill Nature Reserve Mon Dec 82026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: Simplifying Woodland Photography: Unlocking the Secrets to Capturing the Beauty of Nature on a photography walkMy aim is not to instruct you what to shoot, instead, I want to help you develop your own sense of visual awareness, photographic eye and your personal interpretation. I will be happy to help you with the “how to shoot” whatever it is you feel drawn to and wish to express through your creative vision using the camera to construct your intention. The photography walks around these selected woodlands are aimed to promote our senses and connection to trees/woodland/nature - as we walk, observe and take in our environment we may decide to make a photograph, or not.</t>
+          <t>Beginners Portrait Photography Course - Suitable for any amateur who wants to learn the fundamentals of portrait photography - Coventry - 1-Day Course</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707238641610-VHWSAVN4IPEHPVRGJNQZ/portrait+photography+course.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
+          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SQ7078023, SQ3819844, SQ3142823, SQ1654264, SQ1288994, SQ0063623, SQ6524101</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SQ7078023</t>
+          <t>SQ2592535</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
+          <t>Professional Black and White Photography Course | Coventry</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package Option - 4 Private Photography Classes Face to Face Coventry - 2 hrs each to suit you - Available 9-5 on weekdays. You will be sent a code to book dates</t>
+          <t>Enter the date of the event on Customer Information Notes Field when you go through the checkout process. Black and White Photography Course for beginners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495550918-139R34YFWLG3Q89CXENT/PRIVATE-PHOTOGRAPHY-LESSONS.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/b8c2a6b2-9a51-492d-a6c0-b685f5e16cc2/Beginners+Photography+Classes.png</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
+          <t>https://www.alanranger.com/photography-services-near-me/black-and-white-photography-course</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
+          <t>photography-courses</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>360</v>
+        <v>165</v>
       </c>
       <c r="I7" t="n">
-        <v>360</v>
+        <v>165</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ9709344</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ9709344</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BATSFORD Arboretum Autumn Photography Workshops 23 - 31 Oct</t>
+          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr- 30 Apr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: 2026Daily From: Fri 23rd Oct to Fri 31st OctHalf-Day morning workshops are 8 am to 11.30 amHalf-Day afternoon workshops are from 12:00 pm to 3:30 pmOne Day workshops are 8 am to 3:30 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Details: Batsford ArboretumDescription: Batsford Arboretum always provides a terrific display of colour, texture and contrasts throughout Autumn. The Batsford Arboretum photography workshops are always very popular and and attract every level of photographer. There really is a complete range and choice for everyone here so it's not to be missed with expert guidance and support.</t>
+          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-27Book and select either:4hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsJoin our Bluebell Woodland Photography Workshops in Warwickshire to explore beautiful bluebell woods and enhance your photography skills. Led by a professional photographer, you'll capture stunning photos while enjoying easy walks through bluebell trails and receive valuable photography tips for capturing spring blooms in soft woodland light.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715155253660-I9BNV2CJV5TPWB56WH93/Batsford+Autumn+7.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/batsford-arboretum-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, - one day photo workshops, Landscape, Woodlands, autumn</t>
+          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
         <v>99</v>
@@ -868,12 +868,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SQ0818501, SQ7647904, SQ9436105, SQ1204772, SQ9290465, SQ7375084, SQ0264308, SQ9938663, SQ0693365, SQ3442432, SQ8197555, SQ9853668, SQ0732756, SQ6382131, SQ4533936, SQ4668363, SQ5203247, SQ1249736</t>
+          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SQ0818501</t>
+          <t>SQ8599409</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -885,51 +885,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Monthly Photography Mentoring Sessions - Online - Zoom</t>
+          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Photography mentoring online. Receive a monthly assignment to increase your skills across multiple genres and get expert feedback on your images each month</t>
+          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1559474612221-TBJKYSCMOO6IM7FTXJJI/online-photography-mentoring.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-online-photography-mentoring</t>
+          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>online, photography-tuition, photography-courses</t>
+          <t>photography-services</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -941,107 +941,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>Christmas Photography Seasonal Workshops | Warwickshire</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2024 DatesMonday 16 December 2024 - 18:30 - 21:00 - Stratford Upon Avon Evening ShootSunday, 29 December 2024 - 1 day Christmas Photo Walk08:45 15:15Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details: Christmas PhotowalkDescription: Christmas photography Workshops - Will you need to escape the heat and fuss of Christmas festivities and start walking off some of the overindulgences of Christmas? Join me for the informal christmas photography photo walk and discover just how much there is to photograph as you walk around the countryside.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1573822266360-1I7REB8B91RNZXW2PNKP/christmas-sparkle-photography-workshop.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/christmas-photography-workshops</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Urban</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
+          <t>SQ8119747, SQ6178610</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SQ3248242</t>
+          <t>SQ8119747</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr- 01 May</t>
+          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Mon-20-Apr-26Tue-21-Apr-26Wed-22-Apr-26Thu-23-Apr-26Fri-24-Apr-26Sat-25-Apr-26Sun-26-Apr-26Mon-27-Apr-26Tue-28-Apr-26Wed-29-Apr-26Thu-30-Apr-26Fri-01-May-26Book and select either:4hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsJoin our Bluebell Woodland Photography Workshops in Warwickshire to explore beautiful bluebell woods and enhance your photography skills. Led by a professional photographer, you'll capture stunning photos while enjoying easy walks through bluebell trails and receive valuable photography tips for capturing spring blooms in soft woodland light.</t>
+          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details: NorthumberlandDescription: Northumberland Photography Workshops - One of the highlights of Northumberland's landscape is its impressive collection of over seventy castles, the highest number in any English county. These historic fortresses not only showcase the region's rich heritage but also serve as captivating subjects for your photographs. The iconic Bamburgh Castle, dating back to the 11th century, stands majestically on a rocky outcrop, offering panoramic views of the surrounding coastline. Alnwick Castle, made famous by its appearance in the Harry Potter films, is another must-visit location for photography enthusiasts.Lindisfarne Castle and Dunstanburgh Castle are two other gems that beckon photographers with their unique charm. Lindisfarne Castle, perched on a basalt rock outcrop, creates a striking silhouette against the backdrop of the North Sea. Dunstanburgh Castle, situated atop a grassy cliff edge, is flanked by smooth black boulders on Embleton Beach, creating a dramatic composition that is sure to leave a lasting impression on your photographs.Sign up to Northumberland Photography Workshops - Coastline Photography to take your photography to the next level.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714235981485-EF5PRA0X9C6ZNGQUO265/dunstanburgh+boulders.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5723283", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 01 May Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7533033", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 01 May Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4478860", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 01 May Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>99</v>
+        <v>995</v>
       </c>
       <c r="I11" t="n">
-        <v>150</v>
+        <v>995</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510, SQ5723283, SQ7533033, SQ4478860</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SQ8599409</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1053,331 +1053,331 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Annual Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>DARTMOOR Photography Workshop - Landscapes - 9th - 11th Oct</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Make a one-off payment by bank transfer or through this to get 20% discount on events booked for 12 Months | Tailored Pick N Mix photography training plan</t>
+          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DartmoorDescription: Dartmoor Photography Workshop - Nestled amidst the stunning landscapes of southwest England, Dartmoor National Park presents a captivating playground for photographers of all levels. This diverse and dynamic environment boasts rugged moors, ancient woodlands, dramatic granite tors, mysterious valleys, and serene rivers – all waiting to be captured and immortalised in your photographs. From sunrise to sunset, each moment offers a spectacle of natural wonders ready to be transformed into breathtaking images.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4c6bb1a6-8752-4aea-a250-484fb1acdf75/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/annual-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1200</v>
+        <v>875</v>
       </c>
       <c r="I12" t="n">
-        <v>3000</v>
+        <v>875</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SQ0754560, SQ7502565, SQ1485137, SQ7001156, SQ2612014</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SQ0754560</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
+          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DorsetDescription: The Dorset Photography Workshop along the coastline is an exciting and great part of the UK to capture seascapes. We will work around Durdle Door and surrounding areas to make coastal images. Not limited to just the classic seascapes we can cover any genre or style of photography, beit B&amp;W or abstract this prehistoric coastline offers lots of variety and scope to suit all interests.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>250</v>
+        <v>925</v>
       </c>
       <c r="I13" t="n">
-        <v>750</v>
+        <v>925</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SQ4217445</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Beginners Photography Course | 3 Weekly Evening Classes</t>
+          <t>EXMOOR Photography Workshop - Sat 23rd - Sun 24th May 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWParticipants: Max 4Time: 19:00 - 21:00Multi Course Start Dates: Beginners Photography Course3wks Tuesdays - May 5 - May 19 Coventry3wks Thursdays - May 7 - May 21 Coventry3wks Tuesdays - Jun 2 - Jun 16 Coventry3wks Thursdays - Jun 11- Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 CoventryExperience - Level: Beginner and NoviceThis beginners photography course is aimed at anyone with a digital camera wishing to get off auto exposure mode and learn about key camera settings and composition to make better photos.Equipment Needed:You will need a DSLR or Mirrorless Camera with manual exposure modes.Alan will provide you with a course book covering all the topics for the course</t>
+          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 23rd 10:00 - Sun 24th May 15:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/bceae6f2-91b8-4012-a00b-7b7b177d346f/Beginners+Photography+Classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>150</v>
+        <v>575</v>
       </c>
       <c r="I14" t="n">
-        <v>150</v>
+        <v>575</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SQ7702763, SQ6898365, SQ8880953, SQ0678506, SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SQ7702763</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Intermediates Intentions Photography Project Course</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire on this photography course | Coventry | 6-ClassesNO DATES SET FOR 2025 - Check back soon</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>400</v>
+        <v>135.95</v>
       </c>
       <c r="I15" t="n">
-        <v>400</v>
+        <v>459.95</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ0105911</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Landscape Photography DEVON Workshops - Various Dates</t>
+          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 NightsFri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND FiltersPhotography Workshop Event Details: DevonDescription: Our landscape photography devon workshops are carefully crafted to provide you with an immersive and educational experience. Led by experienced and passionate photographers, these workshops offer a structured learning environment that ensures personal development and skill enhancement. From the moment you join us, you'll be guided through the intricacies of seascape photography, learning new techniques and refining your artistic vision.</t>
+          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>775</v>
+        <v>50.57</v>
       </c>
       <c r="I16" t="n">
-        <v>895</v>
+        <v>416.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SQ3856406, SQ2516659</t>
+          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SQ3856406</t>
+          <t>SQ4872440</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
+          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 30th Mar 2026 - 17:30 - 20:00Mon 18th May 2026 - 18:30 - 21:00Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
+          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: Fireworks photography workshop Kenilworth. We will be photographing from outside the castle walls so you don't need to by a ticket for the display. Kenilworth castle acts an excellent backdrop for the amazing fireworks display organised by the Round Table every year.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SQ9554270, SQ5307067, SQ3572999, SQ0796814</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SQ9554270</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1389,163 +1389,163 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
+          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 7th Mar 2026 - 10:00 - 13:30Fri 8th May 2026 - 10:00 - 13:30Sat 26th Oct 2026 - 10:00 - 13:30Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
+          <t>Package Option - 4 Private Photography Classes Face to Face Coventry - 2 hrs each to suit you - Available 9-5 on weekdays. You will be sent a code to book dates</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495550918-139R34YFWLG3Q89CXENT/PRIVATE-PHOTOGRAPHY-LESSONS.png</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
+          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1416930", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 7th Mar 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ0434017", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 8th May 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>125</v>
+        <v>360</v>
       </c>
       <c r="I18" t="n">
-        <v>125</v>
+        <v>360</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SQ1416930, SQ0434017, SQ8778402</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SQ1416930</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
+          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: LavenderDescription: Join me in the Cotswolds for a spectacular sight of Lavender. We will shoot into the evening hours and capture some great colour - go abstract or vista; the choice is yours.</t>
+          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
+          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>150</v>
+        <v>133.85</v>
       </c>
       <c r="I19" t="n">
-        <v>150</v>
+        <v>356.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SQ6748367, SQ7542811</t>
+          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SQ6748367</t>
+          <t>SQ6825544</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Poppy Fields Photography Workshops | Worcestershire</t>
+          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: Rolling hills full of poppies takes some beating. Join me for one of the poppy fields photography location shoots from early June to end of June in Worcestershire - These are provisional dates and may change depending on mother nature.</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:2026 DatesSun May 17th 2026 - 15:00 - 17:00Sun Jul 12th 2026 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SQ8740143, SQ7189877</t>
+          <t>SQ0939451, SQ3644687</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SQ8740143</t>
+          <t>SQ0939451</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1557,107 +1557,107 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BURNHAM ON SEA Long Exposure Photography Workshop 2 May</t>
+          <t>Intermediates Intentions Photography Project Course</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 2nd May 2026 - 18:30 - 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: BurnhamDescription: Experience the magic of long exposure photography against the breathtaking backdrop of Burnham on Sea's iconic lighthouse. Join us for an unforgettable workshop where you'll master the art of capturing stunning sunset seascapes. Our expert instructors will guide you through the process, helping you harness the beauty of this picturesque location in Somerset</t>
+          <t>Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire on this photography course | Coventry | 6-ClassesNO DATES SET FOR 2025 - Check back soon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
+          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="I21" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
+          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Lake DistrictDescription: We will be based in the north lakes and visit some of the top spots in the Lake District for photographs. The Lake District has been a favourite location for photographers for decades. It offers a rich variety of landscapes and the seasonal weather means it can be different every time you visit.The weather creates unique windows to capture, reflections, mist, stormy skies and subtle and strong colours - often all in the space of 1-2 days and sometimes just hours.We will visit approximately 2-3 locations a day in a weekend subject to the wishes of the group, time, weather and other factors: Sign up today for an amazing lake district photography workshop</t>
+          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: We will be based near Dingle and visit some of the top spots around the Dingle Peninsula, South Kerry (Skellig Ring) and finally Killarney National Park.There is a wide variety of subjects: Mountains, Lakes, Waterfalls, Trees/woodlands, Coastline, Rock Formations to name a few. All set in stunning scenery to wow any visitor and photographer. We will visit several locations in a day, some are short 10-15 min stops (layby shoots) others will require more time to perfectly capturing the perfect moment with tides and light.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>975</v>
+        <v>1595</v>
       </c>
       <c r="I22" t="n">
-        <v>1125</v>
+        <v>1595</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SQ9100538</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1669,163 +1669,163 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
+          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
+          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Lake DistrictDescription: We will be based in the north lakes and visit some of the top spots in the Lake District for photographs. The Lake District has been a favourite location for photographers for decades. It offers a rich variety of landscapes and the seasonal weather means it can be different every time you visit.The weather creates unique windows to capture, reflections, mist, stormy skies and subtle and strong colours - often all in the space of 1-2 days and sometimes just hours.We will visit approximately 2-3 locations a day in a weekend subject to the wishes of the group, time, weather and other factors: Sign up today for an amazing lake district photography workshop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>135.95</v>
+        <v>975</v>
       </c>
       <c r="I23" t="n">
-        <v>459.95</v>
+        <v>1125</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
+          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SQ0105911</t>
+          <t>SQ9100538</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
+          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
+          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 16th May 2026 - 09:30 - 16:00Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>50.57</v>
+        <v>150</v>
       </c>
       <c r="I24" t="n">
-        <v>416.85</v>
+        <v>150</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
+          <t>SQ2363666, SQ3794821, SQ8457424, SQ9037810</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SQ4872440</t>
+          <t>SQ2363666</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
+          <t>Landscape Photography DEVON Workshops - Various Dates</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 16th May 2026 - 09:30 - 16:00Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
+          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 NightsFri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND FiltersPhotography Workshop Event Details: DevonDescription: Our landscape photography devon workshops are carefully crafted to provide you with an immersive and educational experience. Led by experienced and passionate photographers, these workshops offer a structured learning environment that ensures personal development and skill enhancement. From the moment you join us, you'll be guided through the intricacies of seascape photography, learning new techniques and refining your artistic vision.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>150</v>
+        <v>775</v>
       </c>
       <c r="I25" t="n">
-        <v>150</v>
+        <v>895</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SQ2363666, SQ3794821, SQ8457424, SQ9037810</t>
+          <t>SQ3856406, SQ2516659</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SQ2363666</t>
+          <t>SQ3856406</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1837,78 +1837,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
+          <t>Landscape Photography SNOWDONIA - Sat 26 - Sun 27 Sep 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
+          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SnowdoniaDescription: Snowdonia National Park, located in North Wales, offers a diverse range of landscapes that will inspire and challenge any photographer. Snowdonia has everything from rugged mountains, flowing rivers, serene lakes, and ancient quarries.The park is home to some of the highest mountain ranges in England and Wales, providing a stunning backdrop for your photography journey. The terrain and landscape of Snowdonia, with its waterfalls, are great for long exposure techniques, the quarries and slate mines provide a starker but striking landscape to create images from the historic mining relics in the area, and last but not least, there are majestic lakes with reflections and mountains to practise and be inspired by to create compelling compositions from this rugged and serene landscape.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>133.85</v>
+        <v>595</v>
       </c>
       <c r="I26" t="n">
-        <v>356.9</v>
+        <v>595</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SQ6825544</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
+          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details: NorthumberlandDescription: Northumberland Photography Workshops - One of the highlights of Northumberland's landscape is its impressive collection of over seventy castles, the highest number in any English county. These historic fortresses not only showcase the region's rich heritage but also serve as captivating subjects for your photographs. The iconic Bamburgh Castle, dating back to the 11th century, stands majestically on a rocky outcrop, offering panoramic views of the surrounding coastline. Alnwick Castle, made famous by its appearance in the Harry Potter films, is another must-visit location for photography enthusiasts.Lindisfarne Castle and Dunstanburgh Castle are two other gems that beckon photographers with their unique charm. Lindisfarne Castle, perched on a basalt rock outcrop, creates a striking silhouette against the backdrop of the North Sea. Dunstanburgh Castle, situated atop a grassy cliff edge, is flanked by smooth black boulders on Embleton Beach, creating a dramatic composition that is sure to leave a lasting impression on your photographs.Sign up to Northumberland Photography Workshops - Coastline Photography to take your photography to the next level.</t>
+          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 3Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details: GowerDescription: Just a short distance away from Swansea, the Gower Peninsula is a remarkable sight for landscape photography in Wales.Gower is a truly unique environment that boasts heathlands, limestone grasslands, brackish and freshwater marshes, dunes and oak woodlands. It is characterised by a distinct combination of features, including lofty limestone cliffs, sandy beaches, and jagged rocky shores that together form its southern coastline. In the north, the coast is a series of tranquil salt marshes and dune systems. This is a perfect location for landscape photography Wales</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714235981485-EF5PRA0X9C6ZNGQUO265/dunstanburgh+boulders.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1918,26 +1918,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>995</v>
+        <v>825</v>
       </c>
       <c r="I27" t="n">
-        <v>995</v>
+        <v>825</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1949,51 +1949,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ANGLESEY Landscape Photography Workshop -  May 2026</t>
+          <t>Landscape Photography Workshop NORFOLK - Coastal 20 - 22 Nov</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 8th May 15:00 - Sun 10th May 14:00, 2026Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Anglesey PhotographyDescription: A great location for a Landscape Photography Workshop Anglesey is a large island of 220 square miles of mainly farmland, but the coastline is excellent for photography with sandy coves, harbours, and rocky headlands in addition to the lighthouses. We will also explore some other areas, Parys Mountain, once the world's biggest copper mine, which has been used in many science fiction films and TV shows for its Martian-like coloured appearance.</t>
+          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: Photography Workshop Norfolk - We will photograph the North Norfolk coastline ranging from Overstand and Cromer sea fronts and groynes to the atmospheric estuaries of Morston Quay and Blakeney Harbour. Beach huts, boats, estuaries, marshland, there is something for everyone on this 3 day North Norfolk photography workshop.Abandoned boats, windmills, nature reserve, sand dunes, coastal erosion, coastal path/estuary, optional seal trip and of course seascapes. The silting has left a fascinating landscape of marshes, sandhills and mud banks, with many creeks and channels twisting and turning their way through. Blakeney village is set on a small hill leading down to the harbour and has pretty flint cottages.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625462292-PCMT7Q118L1X51MPSENJ/Wells+Next+To+Sea+%2302+-+Sep+2022.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>coastal, Landscape, - weekend residential photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>875</v>
+        <v>1025</v>
       </c>
       <c r="I28" t="n">
-        <v>875</v>
+        <v>1025</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2005,51 +2005,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 30 May</t>
+          <t>ANGLESEY Landscape Photography Workshop -  May 2027</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: Embark on a captivating journey of long-exposure photography amidst the secluded Welsh valley of Nant Mill. Join us for an immersive workshop where you'll discover the mesmerizing art of capturing river and waterfall scenes in this ancient woodland near Wrexham.</t>
+          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Anglesey PhotographyDescription: A great location for a Landscape Photography Workshop Anglesey is a large island of 220 square miles of mainly farmland, but the coastline is excellent for photography with sandy coves, harbours, and rocky headlands in addition to the lighthouses. We will also explore some other areas, Parys Mountain, once the world's biggest copper mine, which has been used in many science fiction films and TV shows for its Martian-like coloured appearance.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
+          <t>coastal, Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>125</v>
+        <v>975</v>
       </c>
       <c r="I29" t="n">
-        <v>125</v>
+        <v>975</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2061,51 +2061,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
+          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 30 May</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: We will be based near Dingle and visit some of the top spots around the Dingle Peninsula, South Kerry (Skellig Ring) and finally Killarney National Park.There is a wide variety of subjects: Mountains, Lakes, Waterfalls, Trees/woodlands, Coastline, Rock Formations to name a few. All set in stunning scenery to wow any visitor and photographer. We will visit several locations in a day, some are short 10-15 min stops (layby shoots) others will require more time to perfectly capturing the perfect moment with tides and light.</t>
+          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: Embark on a captivating journey of long-exposure photography amidst the secluded Welsh valley of Nant Mill. Join us for an immersive workshop where you'll discover the mesmerizing art of capturing river and waterfall scenes in this ancient woodland near Wrexham.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1595</v>
+        <v>125</v>
       </c>
       <c r="I30" t="n">
-        <v>1595</v>
+        <v>125</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2117,163 +2117,163 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop NORFOLK - Coastal 20 - 22 Nov</t>
+          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: Photography Workshop Norfolk - We will photograph the North Norfolk coastline ranging from Overstand and Cromer sea fronts and groynes to the atmospheric estuaries of Morston Quay and Blakeney Harbour. Beach huts, boats, estuaries, marshland, there is something for everyone on this 3 day North Norfolk photography workshop.Abandoned boats, windmills, nature reserve, sand dunes, coastal erosion, coastal path/estuary, optional seal trip and of course seascapes. The silting has left a fascinating landscape of marshes, sandhills and mud banks, with many creeks and channels twisting and turning their way through. Blakeney village is set on a small hill leading down to the harbour and has pretty flint cottages.</t>
+          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventrySummaryLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 3 Weekly 2hr Evening Classes - All evening classes are from 19:00 to 21:00Participants: Max 3Lightroom Courses Event Details: Editing CourseCoventry 3 wks - Wed 4 Mar - 18 Mar 2026Coventry 3 wks - Wed 13 May - 27 May 2026Coventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Experience - Level: BeginnersThe beginners Lightroom photo editing classes are aimed at anyone wishing to learn photo editing and photo management with a workflow and consistencyEquipment Needed:You will need a laptop with Adobe Lightroom Classic subscription and the App installedAlan will provide you with training Lightroom Library with images and use that to explain and then demonstrate the various tools</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625462292-PCMT7Q118L1X51MPSENJ/Wells+Next+To+Sea+%2302+-+Sep+2022.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
+          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses, photo editing, lightroom</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>1025</v>
+        <v>150</v>
       </c>
       <c r="I31" t="n">
-        <v>1025</v>
+        <v>150</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ6876661, SQ0415856, SQ7526725, SQ6831161</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ6876661</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Coventry - 1 Day</t>
+          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Suitable for any amateur who wants to learn the fundamentals of portrait photography - Coventry - 1-Day Course</t>
+          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 11 May 2026 - 18:30 - 20:30Tue 1 Sep 2026 - 18:00 - 20:00Wed 23 Sep 2026 - 17:45 - 19:45Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: Join me for this evening Long Exposure Photography Workshop, where we will shoot Kenilworth Castle ruins against the night sky.Kenilworth Castle, formerly one of the strongest fortifications in the country, was reinvented in the Elizabethan era by Robert Dudley as an impressive palace for his queen. Initially built in the 1120s by Geoffrey de Clinton, the Norman keep served as a basis for the structure, and King John later added an external stone wall, as well as a reservoir, to the complex.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707238641610-VHWSAVN4IPEHPVRGJNQZ/portrait+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/beginners-portrait-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ5325711, SQ9140400, SQ8220723, SQ0932604, SQ1178418</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SQ2592535</t>
+          <t>SQ5325711</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
+          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SuffolkDescription: Suffolk Landscape Photography Workshop - The Suffolk coastline offers a wide variety of views and caters for all styles and ways of interpreting the land and seascapes. There will be a rich mixture of coastal shoreline vista to shoreline architecture including piers, beach huts and iconic sea defence structures.</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714650055069-5DPM44ERXSX234XAGLA9/Southwold+%2304+-+February+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>coastal, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>995</v>
+        <v>125</v>
       </c>
       <c r="I33" t="n">
-        <v>995</v>
+        <v>125</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ8778402, SQ6636860</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ8778402</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2285,51 +2285,51 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MACRO Photography Workshops Warwickshire - Feb and Mar</t>
+          <t>BURNHAM ON SEA Long Exposure Photography Workshop 1 Aug</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sat 8 Nov 10:00 - 12:30Macro Photography - Sun 17 May 10:00 - 12:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
+          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 1st Aug 2026 - 18:45 - 21:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: BurnhamDescription: Experience the magic of long exposure photography against the breathtaking backdrop of Burnham on Sea's iconic lighthouse. Join us for an unforgettable workshop where you'll master the art of capturing stunning sunset seascapes. Our expert instructors will guide you through the process, helping you harness the beauty of this picturesque location in Somerset</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/25c550a3-a242-4303-a11b-367dd7055dbe/Abstract%2Band%2BMacro%2BPhotography%2BWorkshops%2B%25282%2529.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/abstract-and-macro-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Macro &amp; Abstract</t>
+          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 17 May 10:00 - 12:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="I34" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SQ8482281, SQ8660736</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SQ8482281</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2341,163 +2341,163 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
+          <t>Monthly Photography Mentoring Sessions - Online - Zoom</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: North YorkshireDescription: North Yorkshire Landscape Photography - We will be based on the northeast coast of England (North Yorkshire and the Moors) and visit some of the iconic coastlines of Staithes, Runswick, Whitby and more. We will concentrate our workshop time along the impressive coastline and work from sunrise to sunset to ensure we make use of the best light, tides and empty beaches. This is the perfect workshop for practising long exposures and working at sunrise and sunsets to get those iconic views on the coast.</t>
+          <t>Photography mentoring online. Receive a monthly assignment to increase your skills across multiple genres and get expert feedback on your images each month</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707212716744-VYD7AYV9U6N6VEZ3C4D1/North+Yorkshire+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1559474612221-TBJKYSCMOO6IM7FTXJJI/online-photography-mentoring.png</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-online-photography-mentoring</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>online, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1450</v>
+        <v>15</v>
       </c>
       <c r="I35" t="n">
-        <v>1450</v>
+        <v>15</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ1067929</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ1067929</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Christmas Photography Seasonal Workshops | Warwickshire</t>
+          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2024 DatesMonday 16 December 2024 - 18:30 - 21:00 - Stratford Upon Avon Evening ShootSunday, 29 December 2024 - 1 day Christmas Photo Walk08:45 15:15Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details: Christmas PhotowalkDescription: Christmas photography Workshops - Will you need to escape the heat and fuss of Christmas festivities and start walking off some of the overindulgences of Christmas? Join me for the informal christmas photography photo walk and discover just how much there is to photograph as you walk around the countryside.</t>
+          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1573822266360-1I7REB8B91RNZXW2PNKP/christmas-sparkle-photography-workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/christmas-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Urban</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I36" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SQ8119747, SQ6178610</t>
+          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SQ8119747</t>
+          <t>SQ3248242</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Landscape YORKSHIRE DALES Photography Workshop - 10 - 12 Apr</t>
+          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 10th - Sun 12th Apr 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Yorkshire DalesDescription: Yorkshire Dales photography workshop - An exciting 3-day residential photography workshop visiting some gorgeous spots around the Yorkshire Dales. Includes early morning shoots and a variety of moody and dramatic scenes for you to practice, learn and hone your photographic skills.</t>
+          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: North YorkshireDescription: North Yorkshire Landscape Photography - We will be based on the northeast coast of England (North Yorkshire and the Moors) and visit some of the iconic coastlines of Staithes, Runswick, Whitby and more. We will concentrate our workshop time along the impressive coastline and work from sunrise to sunset to ensure we make use of the best light, tides and empty beaches. This is the perfect workshop for practising long exposures and working at sunrise and sunsets to get those iconic views on the coast.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707212716744-VYD7AYV9U6N6VEZ3C4D1/North+Yorkshire+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "825.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>825</v>
+        <v>1450</v>
       </c>
       <c r="I37" t="n">
-        <v>825</v>
+        <v>1450</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2509,51 +2509,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 30-31 May</t>
+          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 30th - Sun 31st May 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
+          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: HeathersDescription: Peak District heather WorkshopsSurprise View, perched atop Hathersage, is one of the best viewpoints in the Peak District. It's a perfect spot to admire the sunset and, on a clear night, is a designated 'Dark Skies' stargazing location. To access this special place, head uphill in a northerly direction from the car park and find the strangely shaped Mother Cap stone. Then, marvel at the vivid stars filling the Peak District's dark skies.The Roaches, with Hen Cloud and Ramshaw Rocks, form a gritstone escarpment that marks the Peak's south-western edge. Best viewed from the approach along the Leek road, they stand as a line of silent sentinels guarding the entrance to the Peak District, worn into fantastic shapes by the elements.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707246605883-FVZKLJN54Z455J1Q13CV/peak+district+heather.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>575</v>
+        <v>125</v>
       </c>
       <c r="I38" t="n">
-        <v>575</v>
+        <v>200</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ1994489, SQ1389945, SQ5395624</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ1994489</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2565,92 +2565,92 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
+          <t>Photo Print Preparation Service 30-min – File Check &amp; Advice</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DorsetDescription: The Dorset Photography Workshop along the coastline is an exciting and great part of the UK to capture seascapes. We will work around Durdle Door and surrounding areas to make coastal images. Not limited to just the classic seascapes we can cover any genre or style of photography, beit B&amp;W or abstract this prehistoric coastline offers lots of variety and scope to suit all interests.</t>
+          <t>Book a 30 min Photo Print Preparation Service. I check crop, aspect ratio and DPI, enlarge, retouch, sharpen and supply print-ready image for you to print</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/photo-print-preparation-service-30min</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>photography-services</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>925</v>
+        <v>29</v>
       </c>
       <c r="I39" t="n">
-        <v>925</v>
+        <v>29</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ5582230</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ5582230</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
+          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: Join me on this evening urban architecture photography workshop and learn how to see and design images at night! We will walk around several historic parts of Coventry in this 2.5hr workshop, photographing buildings and ruins - all to practise the art of dealing with tricky light, learning how to focus in the dark, long exposures and hopefully some good skies to help us capture that big space above us.</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 30th Mar 2026 - 17:30 - 20:00Mon 18th May 2026 - 18:30 - 21:00Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
         <v>50</v>
@@ -2660,12 +2660,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ9554270, SQ5307067, SQ3572999, SQ0796814</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ9554270</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2677,51 +2677,51 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
+          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Tue 31st Mar 2026 - 18:00 - 20:00Mon 13th Apr 2026 - 18:30 - 20:30Wed 6th May 2026 - 18:30 - 20:30Mon 11th May 2026 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: Join me for this evening Long Exposure Photography Workshop, where we will shoot Kenilworth Castle ruins against the night sky.Kenilworth Castle, formerly one of the strongest fortifications in the country, was reinvented in the Elizabethan era by Robert Dudley as an impressive palace for his queen. Initially built in the 1120s by Geoffrey de Clinton, the Norman keep served as a basis for the structure, and King John later added an external stone wall, as well as a reservoir, to the complex.</t>
+          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: LavenderDescription: Join me in the Cotswolds for a spectacular sight of Lavender. We will shoot into the evening hours and capture some great colour - go abstract or vista; the choice is yours.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7119101", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Tue 31st Mar 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3245206", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 13th Apr 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6816264", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Wed 6th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Mon 11th May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I41" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SQ7119101, SQ3245206, SQ6816264, SQ5325711</t>
+          <t>SQ6748367, SQ7542811</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SQ7119101</t>
+          <t>SQ6748367</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2733,51 +2733,51 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Landscape Photography SNOWDONIA - Sat 26 - Sun 27 Sep 2026</t>
+          <t>Poppy Fields Photography Workshops | Worcestershire</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SnowdoniaDescription: Snowdonia National Park, located in North Wales, offers a diverse range of landscapes that will inspire and challenge any photographer. Snowdonia has everything from rugged mountains, flowing rivers, serene lakes, and ancient quarries.The park is home to some of the highest mountain ranges in England and Wales, providing a stunning backdrop for your photography journey. The terrain and landscape of Snowdonia, with its waterfalls, are great for long exposure techniques, the quarries and slate mines provide a starker but striking landscape to create images from the historic mining relics in the area, and last but not least, there are majestic lakes with reflections and mountains to practise and be inspired by to create compelling compositions from this rugged and serene landscape.</t>
+          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: Rolling hills full of poppies takes some beating. Join me for one of the poppy fields photography location shoots from early June to end of June in Worcestershire - These are provisional dates and may change depending on mother nature.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>595</v>
+        <v>95</v>
       </c>
       <c r="I42" t="n">
-        <v>595</v>
+        <v>95</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ8740143, SQ7189877</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ8740143</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2789,219 +2789,219 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
+          <t>Online Photography Classes 121 - Zoom - Package Options</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:2026 DatesSun May 17th 2026 - 15:00 - 17:00Sun Jul 12th 2026 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
+          <t>Private online photography classes tailored to your needs - Tuition &amp; support on any aspect of photography - Pay Now - Book dates later.Online photography classes and support are run via Zoom (free to use)Must be used within 12 months of purchase dateIf you want a package (series) of lessons, these package options offer a discount for purchasing multiples. Mon - Fri - 9 am - 5 pm1 x 1hr - £50 - Normal Price for lesson4 x 1hr - 15% Off normal price6 x 1hr - 20% Off normal price8 x 1hr - 25% Off normal price12 x 1hr - 25% Off normal price</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H43" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I43" t="n">
-        <v>35</v>
+        <v>450</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SQ0939451, SQ3644687</t>
+          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SQ0939451</t>
+          <t>SQ1461156</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
+          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 3Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details: GowerDescription: Just a short distance away from Swansea, the Gower Peninsula is a remarkable sight for landscape photography in Wales.Gower is a truly unique environment that boasts heathlands, limestone grasslands, brackish and freshwater marshes, dunes and oak woodlands. It is characterised by a distinct combination of features, including lofty limestone cliffs, sandy beaches, and jagged rocky shores that together form its southern coastline. In the north, the coast is a series of tranquil salt marshes and dune systems. This is a perfect location for landscape photography Wales</t>
+          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
-        <v>825</v>
+        <v>250</v>
       </c>
       <c r="I44" t="n">
-        <v>825</v>
+        <v>750</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ4217445</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
+          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: Fireworks photography workshop Kenilworth. We will be photographing from outside the castle walls so you don't need to by a ticket for the display. Kenilworth castle acts an excellent backdrop for the amazing fireworks display organised by the Round Table every year.</t>
+          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select six online Zoom sessions within twelve months at intervals to suit youRPS Courses - Mentoring for DistinctionsParticipants: Via Zoom online in a group of max 3, or on 1-2-1 basis.Equipment Needed: Zoom AppDropbox App used for updated portfolios and imagesTerms: Sessions must be taken within 12 months of booking the course or forfeited, but there are options to extend the timeline and retain unused classes or add additional classes.Method:Technical and creative critique with suggestions for improvementAdvice on image selection and panel layoutMore Details about the RPS Mentoring Course*Note: Your tutor, Alan Ranger, holds both the RPS's Licentiate and Associate Distinctions, but the RPS does not accredit this Course. This is not an approved course or endorsed by the RPS as an organisation. Alan’s advice is private, unofficial and based on his experience and understanding of the elements required to reach the standard that may result in being awarded a distinction without any guarantee.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
+          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
         <v>75</v>
       </c>
       <c r="I45" t="n">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ3499847, SQ5925235, SQ1898169, SQ7296901, SQ4136369</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ3499847</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EXMOOR Photography Workshop - Sat 23rd - Sun 24th May 2026</t>
+          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 23rd 10:00 - Sun 24th May 15:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
+          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: It will be different from other workshops in the format as it will be divided into separate sessions during the day to tackle theory, set-up, shooting, image review, and post-production.A theory session and discussion on woodland photography and its challenges and some answers, followed by practical advice on settings, lenses, equipment, etc.A presentation on developing creative vision and simplification in woodland settingsA 2hr woodland exploration and walk-making compositions and turning theory into practice in the field.Initial image reviews and critiques to shortlist images to editDemonstration, advice and post-production of your woodland images</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>575</v>
+        <v>150</v>
       </c>
       <c r="I46" t="n">
-        <v>575</v>
+        <v>150</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ4914997</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3069,51 +3069,51 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
+          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: HeathersDescription: Peak District heather WorkshopsSurprise View, perched atop Hathersage, is one of the best viewpoints in the Peak District. It's a perfect spot to admire the sunset and, on a clear night, is a designated 'Dark Skies' stargazing location. To access this special place, head uphill in a northerly direction from the car park and find the strangely shaped Mother Cap stone. Then, marvel at the vivid stars filling the Peak District's dark skies.The Roaches, with Hen Cloud and Ramshaw Rocks, form a gritstone escarpment that marks the Peak's south-western edge. Best viewed from the approach along the Leek road, they stand as a line of silent sentinels guarding the entrance to the Peak District, worn into fantastic shapes by the elements.</t>
+          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SuffolkDescription: Suffolk Landscape Photography Workshop - The Suffolk coastline offers a wide variety of views and caters for all styles and ways of interpreting the land and seascapes. There will be a rich mixture of coastal shoreline vista to shoreline architecture including piers, beach huts and iconic sea defence structures.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707246605883-FVZKLJN54Z455J1Q13CV/peak+district+heather.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714650055069-5DPM44ERXSX234XAGLA9/Southwold+%2304+-+February+2024.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
+          <t>coastal, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>125</v>
+        <v>995</v>
       </c>
       <c r="I48" t="n">
-        <v>200</v>
+        <v>995</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SQ1994489, SQ1389945, SQ5395624</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SQ1994489</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3125,51 +3125,51 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
+          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: It will be different from other workshops in the format as it will be divided into separate sessions during the day to tackle theory, set-up, shooting, image review, and post-production.A theory session and discussion on woodland photography and its challenges and some answers, followed by practical advice on settings, lenses, equipment, etc.A presentation on developing creative vision and simplification in woodland settingsA 2hr woodland exploration and walk-making compositions and turning theory into practice in the field.Initial image reviews and critiques to shortlist images to editDemonstration, advice and post-production of your woodland images</t>
+          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: Join me on this evening urban architecture photography workshop and learn how to see and design images at night! We will walk around several historic parts of Coventry in this 2.5hr workshop, photographing buildings and ruins - all to practise the art of dealing with tricky light, learning how to focus in the dark, long exposures and hopefully some good skies to help us capture that big space above us.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SQ4914997</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3181,22 +3181,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DARTMOOR Photography Workshop - Landscapes - 9th - 11th Oct</t>
+          <t>WALES Photography Workshop | Lake Vyrnwy 30-31 May</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DartmoorDescription: Dartmoor Photography Workshop - Nestled amidst the stunning landscapes of southwest England, Dartmoor National Park presents a captivating playground for photographers of all levels. This diverse and dynamic environment boasts rugged moors, ancient woodlands, dramatic granite tors, mysterious valleys, and serene rivers – all waiting to be captured and immortalised in your photographs. From sunrise to sunset, each moment offers a spectacle of natural wonders ready to be transformed into breathtaking images.</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 30th - Sun 31st May 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>875</v>
+        <v>575</v>
       </c>
       <c r="I50" t="n">
-        <v>875</v>
+        <v>575</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3237,112 +3237,112 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Online Photography Classes 121 - Zoom - Package Options</t>
+          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Private online photography classes tailored to your needs - Tuition &amp; support on any aspect of photography - Pay Now - Book dates later.Online photography classes and support are run via Zoom (free to use)Must be used within 12 months of purchase dateIf you want a package (series) of lessons, these package options offer a discount for purchasing multiples. Mon - Fri - 9 am - 5 pm1 x 1hr - £50 - Normal Price for lesson4 x 1hr - 15% Off normal price6 x 1hr - 20% Off normal price8 x 1hr - 25% Off normal price12 x 1hr - 25% Off normal price</t>
+          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2025 - 09:30 - 11:30Crackley Wood, Kenilworth - Fri Nov 7Hay Woods - Solihull Fri Dec 5Tile Hill Nature Reserve Mon Dec 82026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: Simplifying Woodland Photography: Unlocking the Secrets to Capturing the Beauty of Nature on a photography walkMy aim is not to instruct you what to shoot, instead, I want to help you develop your own sense of visual awareness, photographic eye and your personal interpretation. I will be happy to help you with the “how to shoot” whatever it is you feel drawn to and wish to express through your creative vision using the camera to construct your intention. The photography walks around these selected woodlands are aimed to promote our senses and connection to trees/woodland/nature - as we walk, observe and take in our environment we may decide to make a photograph, or not.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
+          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I51" t="n">
-        <v>450</v>
+        <v>15</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
+          <t>SQ7078023, SQ3819844, SQ3142823, SQ1654264, SQ1288994, SQ0063623, SQ6524101</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SQ1461156</t>
+          <t>SQ7078023</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Photo Print Preparation Service 30-min – File Check &amp; Advice</t>
+          <t>Landscape YORKSHIRE DALES Photography Workshop - 16 - 18 Apr</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Book a 30 min Photo Print Preparation Service. I check crop, aspect ratio and DPI, enlarge, retouch, sharpen and supply print-ready image for you to print</t>
+          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Yorkshire DalesDescription: Yorkshire Dales photography workshop - An exciting 3-day residential photography workshop visiting some gorgeous spots around the Yorkshire Dales. Includes early morning shoots and a variety of moody and dramatic scenes for you to practice, learn and hone your photographic skills.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photo-print-preparation-service-30min</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>29</v>
+        <v>895</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>895</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3426,7 +3426,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3478,7 +3478,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3530,7 +3530,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3582,7 +3582,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3634,7 +3634,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-04-22", "priceValidUntil": "2027-04-22", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 17 May 10:00 - 12:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 17 May 10:00 - 12:30"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3426,7 +3426,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3478,7 +3478,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3530,7 +3530,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3582,7 +3582,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3634,7 +3634,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-11", "priceValidUntil": "2027-05-11", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -493,12 +493,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MACRO Photography Workshops Warwickshire - Feb and Mar</t>
+          <t>MACRO Photography Workshops Warwickshire - Various</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sat 8 Nov 10:00 - 12:30Macro Photography - Sun 17 May 10:00 - 12:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Tue July 7th - 6:30pm - 8:30pmMacro Photography - Tue Sep 8th - 6:00pm - 8:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 8 Nov 10:00 - 12:30"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 17 May 10:00 - 12:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue Jul 7th - 6:30pm - 8:30pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8660736", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue Sep 8th - 6:00pm - 8:00pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1165,12 +1165,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXMOOR Photography Workshop - Sat 23rd - Sun 24th May 2026</t>
+          <t>EXMOOR Photography Workshop - Sat 18 - Sun 19 Jul 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 23rd 10:00 - Sun 24th May 15:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
+          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 18 10:30 - Sun 19 July 14:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:2026 DatesSun May 17th 2026 - 15:00 - 17:00Sun Jul 12th 2026 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates: DatesSun Jul 12th 2026 - 15:00 - 17:00Sun May 23rd 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1526,26 +1526,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun May 17 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "35.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun Jul 12 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun Jul 12 2026 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SQ0939451, SQ3644687</t>
+          <t>SQ3644687, SQ0939451</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SQ0939451</t>
+          <t>SQ3644687</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 16th May 2026 - 09:30 - 16:00Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
+          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Sat 22nd May 2027 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sat 16th May 2026 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SQ2363666, SQ3794821, SQ8457424, SQ9037810</t>
+          <t>SQ3794821, SQ8457424, SQ9037810, SQ2363666</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SQ2363666</t>
+          <t>SQ3794821</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Landscape</t>
+          <t>Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2254,11 +2254,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
         <v>125</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ8778402, SQ6636860</t>
+          <t>SQ8778402, SQ9080164, SQ6636860</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Mon 30th Mar 2026 - 17:30 - 20:00Mon 18th May 2026 - 18:30 - 21:00Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 30th Mar 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 18th May 2026 - 18:30 - 21:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SQ9554270, SQ5307067, SQ3572999, SQ0796814</t>
+          <t>SQ3572999, SQ0796814, SQ9554270, SQ5307067</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SQ9554270</t>
+          <t>SQ3572999</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3181,12 +3181,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 30-31 May</t>
+          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 30th - Sun 31st May 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "priceSpecification": {"price": "575.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>575</v>
+        <v>695</v>
       </c>
       <c r="I50" t="n">
-        <v>575</v>
+        <v>695</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops;pocket-guide-series;print, photography-gift-vouchers;photography-presents</t>
+          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops, photography-gift-vouchers;photography-presents</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3426,7 +3426,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3478,7 +3478,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3530,7 +3530,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3582,7 +3582,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3634,7 +3634,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-13", "priceValidUntil": "2027-05-13", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Tue July 7th - 6:30pm - 8:30pmMacro Photography - Tue Sep 8th - 6:00pm - 8:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: Join me at a Warwickshire location for this macro photography workshop: We will work around the area in search of macro and abstract shapes, form, colour, tone and patterns.There are beautiful trees with loads of interesting trunks - in addition, all around the area is water, stone and nature’s imprint creating some great textures, shapes, patterns and colours for us to explore and practise and learn macro photography.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Tue July 7th - 6:30pm - 8:30pmMacro Photography - Tue Sep 8th - 6:00pm - 8:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue Jul 7th - 6:30pm - 8:30pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8660736", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue Sep 8th - 6:00pm - 8:00pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue Jul 7th - 6:30pm - 8:30pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8660736", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue Sep 8th - 6:00pm - 8:00pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -610,7 +610,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: 2026Daily From: Fri 23rd Oct to Fri 31st OctHalf-Day morning workshops are 8 am to 11.30 amHalf-Day afternoon workshops are from 12:00 pm to 3:30 pmOne Day workshops are 8 am to 3:30 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Details: Batsford ArboretumDescription: Batsford Arboretum always provides a terrific display of colour, texture and contrasts throughout Autumn. The Batsford Arboretum photography workshops are always very popular and and attract every level of photographer. There really is a complete range and choice for everyone here so it's not to be missed with expert guidance and support.</t>
+          <t>Batsford Arboretum Photography Workshops in autumn. Enjoy the colour and expert photographic guidance | Half or One Day Sessions | Any Level and CameraSummaryLocation: Batsford Arboretum - GloucestershireDates: Fri 23 Oct – Sat 31 Oct 2026Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless CameraPhotography Workshop Event Batsford ArboretumDescription: For nearly fifteen years I've returned to Batsford Arboretum each autumn, and in that time I've come to know every corner of it — which spot works at which hour, where the light falls and the angles that turn one of Britain's finest tree collections into a photograph rather than a snapshot. This workshop is built on that knowledge. Open to all levels and any camera, it's a chance to photograph Batsford's autumn colour with someone who can put you in the right place at the right time, so you can spend your energy on the thing that actually matters: seeing.Because that's where this workshop really lives. We'll cover the technical setup — exposure, depth of field, the settings that give you control — but that's only the floor. The real work is learning to look: to compose with intention and move beyond the cliché shot everyone else comes home with, to find the close-up, the macro detail and the quiet abstract as readily as the wide vista, and above all to read light, texture and colour as a harmony rather than chasing the over-saturated "look how vivid this is" image. Colour handled with restraint and relationship will always outlast colour shouted.With small numbers and genuine one-to-one attention throughout, you'll have the time and space to slow down and work properly — and you can choose a half-day morning or afternoon session, or a full day in the colour. You'll leave not just with a set of strong autumn images, but with a way of seeing — light, texture and composition — that changes how you photograph colour, woodland and the natural world wherever you go next.Good to know: the workshop price includes entrance to the Arboretum. On the early morning session we have exclusive access before the gardens open to the public — the quiet best light of the day, with the place to ourselves. A grab-and-go breakfast is available from around 9:30am, and the café and outdoor snack bar are open through the day for lunch and refreshments, with toilets on site by the reception area.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -666,12 +666,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWParticipants: Max 4Time: 19:00 - 21:00Multi Course Start Dates: Beginners Photography Course3wks Tuesdays - May 5 - May 19 Coventry3wks Thursdays - May 7 - May 21 Coventry3wks Tuesdays - Jun 2 - Jun 16 Coventry3wks Thursdays - Jun 11- Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 CoventryExperience - Level: Beginner and NoviceThis beginners photography course is aimed at anyone with a digital camera wishing to get off auto exposure mode and learn about key camera settings and composition to make better photos.Equipment Needed:You will need a DSLR or Mirrorless Camera with manual exposure modes.Alan will provide you with a course book covering all the topics for the course</t>
+          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 4Start Dates: Beginners Photography Course3wks Thursdays - Jun 11 - Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 CoventryLevel: Beginner and NoviceDescription:A practical three-week evening course that takes you from Auto to confident manual control, built around your own camera.Week 1 is about getting off Auto for good — the exposure modes, then aperture, shutter speed and ISO, and how they work together as the exposure triangle, with practical assignments to put it into practice.Week 2 goes deeper into getting the exposure right: manual exposure, metering, reading the histogram, exposure compensation, stops and dynamic range, and bracketing — followed by a review of your assignment work.Week 3 moves on to focusing and depth of field, white balance, JPEG vs RAW, and the foundations of composition, finishing with a final assignment review.With a maximum of four people, you get genuine attention and plenty of room to ask questions, and you'll leave with a printed course book covering every topic to revisit at home. Beginner and novice friendly — just bring a DSLR or mirrorless camera with manual modes.What You'll Learn: How to get off Auto and use manual exposure, aperture, shutter speed and ISO; how focus works; and the foundations of composition to make stronger, more deliberate photos.Includes: A printed course book covering every topic, so you can revisit it all afterwards.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/bceae6f2-91b8-4012-a00b-7b7b177d346f/Beginners+Photography+Classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e7a77ef5-4a16-4466-9e54-7d29287e9a95/photography+training.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -686,11 +686,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7702763", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Wednesdays - May 5 - May 19 Coventry"}, {"@type": "Offer", "sku": "SQ6898365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Thursdays - May 7 - May 21 Coventry"}, {"@type": "Offer", "sku": "SQ8880953", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Tuesdays - Jun 2 - Jun 16 Coventry"}, {"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
         <v>150</v>
@@ -700,12 +700,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SQ7702763, SQ6898365, SQ8880953, SQ0678506, SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762</t>
+          <t>SQ0678506, SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SQ7702763</t>
+          <t>SQ0678506</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Suitable for any amateur who wants to learn the fundamentals of portrait photography - Coventry - 1-Day Course</t>
+          <t>Beginners Portrait Photography Course Location: 17A Spon Street, Coventry, CV1 3BA (Pay &amp; Display, or Skydome Multi-Storey, 15 Croft Rd, CV1 3LD)Duration: 1-day course, 9am–5pm (approx 1hr lunch)Participants: Max 4Start Dates: Portrait Photography CourseSaturday 11 Oct 2025 - CoventryLevel: BeginnerDescription: A 1-day portrait photography course suitable for any amateur who wants to learn the fundamentals — lighting, exposure, camera settings and composition.Equipment: A DSLR or mirrorless camera with manual exposure modes, and a good understanding of the basics of exposure, aperture, shutter speed and ISO. Ideally a zoom lens (50mm+) or a 50mm prime.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -778,12 +778,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Enter the date of the event on Customer Information Notes Field when you go through the checkout process. Black and White Photography Course for beginners</t>
+          <t>Black and White Photography CourseLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 2 × 2.5hr evening classesParticipants: Max 4Start Dates: Black &amp; White CourseCoventry 2 wks - Mon 3 Sep - 10 Sep 2025Level: Beginner to IntermediateDescription: A two-week course to help beginners and intermediates recognise the visual building blocks of strong black &amp; white images, capture the best data in camera, and convert to mono on the computer.Equipment: A DSLR or mirrorless camera with manual exposure modes. (confirm any editing software requirement)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/b8c2a6b2-9a51-492d-a6c0-b685f5e16cc2/Beginners+Photography+Classes.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1721724334692-7KPD0E90A6E4YZMAR324/black+and+white+photography+course+.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-27Book and select either:4hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsJoin our Bluebell Woodland Photography Workshops in Warwickshire to explore beautiful bluebell woods and enhance your photography skills. Led by a professional photographer, you'll capture stunning photos while enjoying easy walks through bluebell trails and receive valuable photography tips for capturing spring blooms in soft woodland light.</t>
+          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-274hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsDescription: This Bluebell Woodlands photography workshop gives you exclusive access to a private Warwickshire bluebell wood near Stratford-upon-Avon, open to all levels and any camera. For a few short weeks each spring the woodland floor turns into a sea of blue — and unlike the well-known public bluebell spots, this one is yours to photograph without the crowds, so you can slow right down and work the scene properly in soft woodland light, rather than grabbing the same shot everyone else takes.You choose how you shoot it. Pick a four-hour half-day session — sunrise (5:45am–9:45am) for soft, warm early light, or mid-morning (10:30am–2:30pm) for brighter colour — or book the full day (5:45am–2:30pm) to shoot both, with a brunch break in between (9:45–10:30, not included). Whichever you choose, the technical craft is the floor we build on — composition, depth of field, the settings that hold a carpet of blue in focus — but the real work is learning to see. Woodland is a beautifully chaotic subject, so we'll work on simplifying it into a frame with order and intention, on finding the intimate, close-up detail as readily as the wide woodland view, and on reading the soft spring light and the blue-and-green as a quiet harmony rather than chasing a loud, over-saturated bluebell cliché.It's a small group of no more than six, taught personally and pitched at exactly your level, with easy walks along the bluebell trails and one-to-one guidance throughout. Because bluebells wait for no one, dates flex to the flowering — you'll pick a first-choice date and I'll confirm the peak display nearer the time. You'll come away with a portfolio of atmospheric spring woodland images that feel like the place — and a calmer, more intentional way of seeing colour, light and detail that you can take anywhere.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -946,7 +946,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2024 DatesMonday 16 December 2024 - 18:30 - 21:00 - Stratford Upon Avon Evening ShootSunday, 29 December 2024 - 1 day Christmas Photo Walk08:45 15:15Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details: Christmas PhotowalkDescription: Christmas photography Workshops - Will you need to escape the heat and fuss of Christmas festivities and start walking off some of the overindulgences of Christmas? Join me for the informal christmas photography photo walk and discover just how much there is to photograph as you walk around the countryside.</t>
+          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details: Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 16 Dec 18:30 - 21:00 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 29 Dec 08:45 - 15:30 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details: NorthumberlandDescription: Northumberland Photography Workshops - One of the highlights of Northumberland's landscape is its impressive collection of over seventy castles, the highest number in any English county. These historic fortresses not only showcase the region's rich heritage but also serve as captivating subjects for your photographs. The iconic Bamburgh Castle, dating back to the 11th century, stands majestically on a rocky outcrop, offering panoramic views of the surrounding coastline. Alnwick Castle, made famous by its appearance in the Harry Potter films, is another must-visit location for photography enthusiasts.Lindisfarne Castle and Dunstanburgh Castle are two other gems that beckon photographers with their unique charm. Lindisfarne Castle, perched on a basalt rock outcrop, creates a striking silhouette against the backdrop of the North Sea. Dunstanburgh Castle, situated atop a grassy cliff edge, is flanked by smooth black boulders on Embleton Beach, creating a dramatic composition that is sure to leave a lasting impression on your photographs.Sign up to Northumberland Photography Workshops - Coastline Photography to take your photography to the next level.</t>
+          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details NorthumberlandDescription: This is a 4-day, 3-night residential Northumberland photography workshop along one of the most dramatic coastlines in Britain, open to all levels from beginner to advanced. Northumberland has more castles than any English county — over seventy — and on this coast the great ones meet the sea: Bamburgh rising from its rocky outcrop, Lindisfarne silhouetted against the North Sea, Dunstanburgh ringed by the black boulders of Embleton Beach. It's a coastline made for photographers who want history, drama and big coastal light in one trip.Based on the Northumberland coast, we spend four days chasing the best conditions across its finest locations — Bamburgh, Dunstanburgh, Lindisfarne, Beadnell, Craster and more — and because it's the east coast, you can shoot both sunrise and sunset from the same stretch of shore. The focus is on three things that define great coastal photography here: composing castles and shoreline into a strong frame, mastering long exposure to turn tide and sky into mood, and working the magical light of sunrise and sunset over the Farne Islands and empty beaches. Throughout, the emphasis isn't just on the famous castle view but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition, planned each day around the tides, the light and the forecast, with a detailed location itinerary sent a few days ahead. Across four days you'll shoot empty beaches at first light, iconic castles and long-exposure seascapes — and come away with a portfolio of dramatic Northumbrian coastal images and a real command of long-exposure and coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714235981485-EF5PRA0X9C6ZNGQUO265/dunstanburgh+boulders.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/eb76126f-7580-40f0-ac80-39b29897cdc7/Northumberland+-+March+2025+-+%2302.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>995</v>
+        <v>1095</v>
       </c>
       <c r="I11" t="n">
-        <v>995</v>
+        <v>1095</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DartmoorDescription: Dartmoor Photography Workshop - Nestled amidst the stunning landscapes of southwest England, Dartmoor National Park presents a captivating playground for photographers of all levels. This diverse and dynamic environment boasts rugged moors, ancient woodlands, dramatic granite tors, mysterious valleys, and serene rivers – all waiting to be captured and immortalised in your photographs. From sunrise to sunset, each moment offers a spectacle of natural wonders ready to be transformed into breathtaking images.</t>
+          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DartmoorDescription: This is a 3-day, 2-night residential landscape photography workshop based around Dartmoor National Park in South Devon, open to all levels from beginner to advanced. Dartmoor is one of England's most atmospheric wild landscapes — a vast sweep of rugged open moor, dramatic granite tors, ancient stunted woodland and serene rivers running through hidden valleys — and across a weekend you'll learn to read and photograph this dramatic terrain in its ever-changing light.Over three days we range across the moor and its woodlands, working a variety of locations as the conditions dictate — from the sculptural granite tors and big moorland vistas to the mossy, otherworldly ancient woods and tumbling rivers. The focus is on three things that make a strong landscape image here: composing order from a wild, expansive scene, controlling exposure and depth of field across big tonal ranges, and timing your shoot to the moods of Dartmoor light, with optional sunrise and sunset shoots and evening picture reviews. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and weather as a harmony rather than chasing the obvious shot. Be prepared for some longer walks over rougher ground — this is a more demanding workshop that takes you to the moor's most rewarding spots.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation, breakfast and evening meals are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of dramatic Dartmoor landscapes — moors, tors and ancient woodland — and the field craft to capture wild country anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DorsetDescription: The Dorset Photography Workshop along the coastline is an exciting and great part of the UK to capture seascapes. We will work around Durdle Door and surrounding areas to make coastal images. Not limited to just the classic seascapes we can cover any genre or style of photography, beit B&amp;W or abstract this prehistoric coastline offers lots of variety and scope to suit all interests.</t>
+          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DorsetDescription: This is a 3-day, 2-night residential landscape photography workshop along the Jurassic Coast of Dorset, open to all levels from beginner to advanced. Dorset's Purbeck coastline is one of the UK's great seascape locations — a prehistoric, World Heritage shore of sculpted arches, sea stacks and folded cliffs, with the iconic Durdle Door and Lulworth Cove at its heart — and across a weekend you'll learn to photograph it in its best light.Based on the Purbeck coast, we work the area's finest locations — from Durdle Door, Man O'War and Lulworth Cove to Kimmeridge, Dancing Ledge, Mupe Bay and the ghost village of Tyneham. The focus is on three things that make a strong coastal image: composing rock, sea and sky into a balanced frame, using long exposure to turn the moving water into mood, and timing your shoot to the light and the tide. It's never prescriptive though — this varied coastline lends itself to any style, so whether you're drawn to classic seascapes, black and white or abstract, there's scope to follow your own creative vision; throughout, the emphasis is on learning to see, composing with intention and reading light and tone as a harmony rather than chasing the obvious shot. There are optional sunrise and sunset shoots and evenings for relaxed picture reviews.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. B&amp;B accommodation and an evening meal are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Jurassic Coast images and a real command of seascape and long-exposure technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 18 10:30 - Sun 19 July 14:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details: LynmouthDescription: Lynmouth and the surrounding area in Exmoor - North Devon, provide beautiful little secluded bays to shoot rock formations, seascapes and whatever your creative vision allows. We visit many small bays and coves during the weekend and some impressive rock formations in the "valley of rocks" nearby.</t>
+          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 18 10:30 - Sun 19 July 14:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details LynmouthDescription: This is a 2-day, 1-night residential seascape photography workshop based at Lynmouth on the dramatic Exmoor coast of North Devon, open to all levels from beginner to advanced. Lynmouth is a photographer's paradise — where the East and West Lyn rivers meet the sea beneath towering cliffs, fringed by secluded bays, weathered rock formations and the quaint harbour village with its iconic Rhenish Tower. It's a compact, richly varied coastline that rewards a focused weekend of shooting.Over two days we work the area's finest coastal locations — from the secluded bays and rock formations around Lynmouth and the sweeping Valley of Rocks to Watersmeet, Heddon's Mouth and Porlock Weir. The focus is on three things that make a strong seascape: composing rock, water and sky into a balanced frame, using long exposure to turn the moving sea into mood, and timing your shoot to the light and the tide. Throughout, the emphasis isn't just on the grand view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. The days follow the conditions — full days on location with tuition, an optional sunset shoot, and an optional sunrise, with evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a portfolio of dramatic Exmoor seascapes and the field craft to read light and tide on any coast. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: Fireworks photography workshop Kenilworth. We will be photographing from outside the castle walls so you don't need to by a ticket for the display. Kenilworth castle acts an excellent backdrop for the amazing fireworks display organised by the Round Table every year.</t>
+          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: This Fireworks Photography Workshop is a one-off evening capturing one of the most exciting subjects in photography — a full fireworks display bursting over the floodlit ruins of Kenilworth Castle. Open to all levels and any camera, it's built around the Round Table's spectacular annual display, and the magical, fleeting moment when long exposure turns streaking light and exploding colour into a single dramatic image with the castle as its backdrop.Fireworks look chaotic but reward a calm, technical approach, and that's exactly what we'll work on. The focus is on three things that make the difference between a lucky snap and a controlled image: setting up for long exposure — shutter, aperture and the timing that lets you build a burst on the sensor — composing the frame so the castle and the sky work together rather than fighting, and reading the rhythm of the display to know when to open and close the shutter. You'll learn to anticipate rather than react, and to keep shooting cleanly when the sky is at its busiest.It's a small group of no more than four, taught personally and right beside you in the dark, so you get real one-to-one guidance exactly when the action is happening. Better still, we photograph from outside the castle walls, so there's no admission ticket to buy for the display. You'll come away with a set of dramatic fireworks images over a historic castle — and the long-exposure and timing skills to photograph fireworks, light trails and night scenes anywhere. (Please note this is an annual event with the date set by the organisers, so timing is confirmed each year nearer the display.)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package Option - 4 Private Photography Classes Face to Face Coventry - 2 hrs each to suit you - Available 9-5 on weekdays. You will be sent a code to book dates</t>
+          <t>4 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 4 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates: DatesSun Jul 12th 2026 - 15:00 - 17:00Sun May 23rd 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Elevate Your Garden Photography Skills With Garden Photography WorkshopsImmerse yourself in the art of macro and abstract garden photography with our enriching workshops. Discover the nuances of camera settings, lens utilisation, and composition techniques tailored for capturing the captivating beauty of gardens.What to Expect:Dive into the intricacies of capturing stunning macro and abstract garden photography imagesLearn about specialised equipment and lens utilisation for breathtaking garden photographyEngage in hands-on assignments and receive personalised guidanceUnwind with afternoon tea as part of the enriching garden photography workshop experience</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates: DatesSun Jul 12th 2026 - 15:00 - 17:00Sun May 23rd 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun Jul 12 2026 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun Jul 12 2026 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire on this photography course | Coventry | 6-ClassesNO DATES SET FOR 2025 - Check back soon</t>
+          <t>Six-month photography project and showcase your images in a public exhibition in WarwickshireLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 6-month project, 6 classesParticipants: Max 4Level: IntermediateDescription: Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire — a course designed to develop your intentions, vision and a coherent body of work.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: We will be based near Dingle and visit some of the top spots around the Dingle Peninsula, South Kerry (Skellig Ring) and finally Killarney National Park.There is a wide variety of subjects: Mountains, Lakes, Waterfalls, Trees/woodlands, Coastline, Rock Formations to name a few. All set in stunning scenery to wow any visitor and photographer. We will visit several locations in a day, some are short 10-15 min stops (layby shoots) others will require more time to perfectly capturing the perfect moment with tides and light.</t>
+          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: This is a 5-day, 4-night residential photography workshop in the south-west of Ireland — the longest and most immersive trip I run, based around Dingle and exploring some of the most beautiful country in Europe. Open to all levels and any camera, it takes in three extraordinary areas of County Kerry: the wild, sea-battered Dingle Peninsula, the dramatic coastline of South Kerry along the Skellig Ring, and the mountains, lakes and ancient woodland of Killarney National Park.The variety here is the gift and the challenge — mountains, lakes, waterfalls, woodland, coastline and rock formations, often within a single day — and five days gives us the time to do it justice. We'll cover the technical control you need, but the real focus is on learning to see: composing order and intention out of these vast, busy scenes, working close-up and intimate detail as readily as the grand vista, and reading light, weather and tide as a harmony rather than chasing the obvious postcard shot. Some stops are quick laybys to catch a fleeting moment; others we'll work slowly, waiting for the light and water to come good.With a maximum of just four photographers and five full days on the ground, this is genuinely personal tuition with the time to slow down and work properly — Alan plans each day around the season, the forecast and the tides, and sends a detailed itinerary ahead. You'll come away not just with a portfolio from one of Europe's great landscapes, but with a stronger way of seeing — light, composition and restraint — that will change how you photograph wherever you go next. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Lake DistrictDescription: We will be based in the north lakes and visit some of the top spots in the Lake District for photographs. The Lake District has been a favourite location for photographers for decades. It offers a rich variety of landscapes and the seasonal weather means it can be different every time you visit.The weather creates unique windows to capture, reflections, mist, stormy skies and subtle and strong colours - often all in the space of 1-2 days and sometimes just hours.We will visit approximately 2-3 locations a day in a weekend subject to the wishes of the group, time, weather and other factors: Sign up today for an amazing lake district photography workshop</t>
+          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Lake DistrictDescription: This is a 3-day, 2-night residential Lake District photography workshop, based in the north lakes and open to all levels from beginner to advanced. The Lake District has been a favourite of landscape photographers for decades, and for good reason: nowhere else in England packs in such variety — mountains, tarns, ancient woodland, waterfalls and reflective lakes — and the changeable Cumbrian weather means it's never the same place twice. Misty mornings, atmospheric light, stormy skies and quiet reflections can all arrive within a single weekend.Over three days we shoot the iconic scenes at their best, basing ourselves in the north lakes and working two to three carefully chosen locations a day — from Derwent Water, Castlerigg and Ashness Bridge to the tarns and valleys of Langdale, Coniston and Buttermere. The rhythm follows the light: optional sunrise shoots, full days on location with tuition in the field, and optional sunset sessions, with evenings for relaxed picture reviews over a meal. Throughout, the emphasis isn't just on being at the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot. You'll come away with a portfolio of dramatic Lakeland images and the field craft to read light and weather anywhere.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the group, the season and the forecast, sends a detailed location itinerary a few days ahead, and adapts on the ground to chase the best conditions. Accommodation and breakfast are included, so you can switch off from the logistics and focus entirely on your photography for three days. Extra night B&amp;B available for Thursday — contact me for details and booking separately.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Sat 22nd May 2027 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: Spring and Autumn WorkshopsPadley Gorge is a deep but narrow valley in the Peak District, Derbyshire, between the village of Grindleford and the A6187 road. The gorge is wooded with a stream, the Burbage Brook, at the bottom. Padley provides numerous opportunities to refine your composition in many aspects. You can opt for close-up sketches of woodland growth, rocks and water or tackle a wider vista showing the river and work on long exposures, water abstracts and much more.Bolehill Quarry - Created hundreds of millions of years ago by the power of natural forces, the last few centuries have seen the rugged landscape surrounding Padley Gorge sculpted by man who long ago quarried these gritstone Edges for stone and tunnelled deep beneath the moors to drive a railway line through the hills. Now an area of outstanding natural beauty, this walk takes in the breathtaking heights of Millstone Edge and majestic silver birch woodlands. It's a great location for any level of photographer to hone their skills and techniques.</t>
+          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Sat 22nd May 2027 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: This Peak District photography workshop is a full day in the heart of Derbyshire's Hope Valley, open to all levels from beginner to advanced. It's built around two of the area's most rewarding and contrasting locations — the wooded, water-filled drama of Padley Gorge in the morning and the rugged, sculptural landscape of Bolehill Quarry in the afternoon — so in a single day you photograph two completely different faces of the Peak District, and learn to read each one rather than just point a camera at it.The morning at Padley Gorge — a deep, tree-lined valley with the Burbage Brook tumbling through it — is all about slowing down and seeing: simplifying a busy woodland scene into intimate close-ups of rock, moss and water, finding the quiet order in the chaos, and using long exposure to draw movement out of the brook. The afternoon at Bolehill Quarry opens out to the heights of Millstone Edge and silver birch woodland, where the work shifts to composing the bigger landscape. Across both, the technical craft is the floor we build on — exposure, depth of field, the settings that give you control — but the real lesson is learning to see: composing with intention, working close-up detail as readily as the wide vista, and reading light, texture and colour as a harmony rather than chasing the loud, obvious shot.We meet at the Grindleford Railway Café, where you can grab an optional pre-shoot breakfast before we head into the gorge. Lunch is back at the café halfway through — buy on the day or bring your own — before a short drive over to Bolehill for the afternoon session. Taught personally in a small group, this is hands-on, on-location tuition pitched at exactly your level, with Alan beside you in the field throughout; a detailed itinerary is sent a few days ahead, adjusted for the season and forecast, so you'll come away with a varied portfolio of Peak District images and a sharper, more intentional way of seeing landscape anywhere.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 NightsFri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND FiltersPhotography Workshop Event Details: DevonDescription: Our landscape photography devon workshops are carefully crafted to provide you with an immersive and educational experience. Led by experienced and passionate photographers, these workshops offer a structured learning environment that ensures personal development and skill enhancement. From the moment you join us, you'll be guided through the intricacies of seascape photography, learning new techniques and refining your artistic vision.</t>
+          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsThu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND Filters (tripod and filters can be provided)Photography Workshop Event Details DevonDescription: This is a multi-day residential landscape photography workshop based at Hartland Quay on the dramatic North Devon coast, open to all levels from beginner to advanced. Hartland Quay is one of the UK's most spectacular seascape locations — long slithers of rock formations running out into a fierce Atlantic tide — and it's the perfect base for learning seascape photography on a coastline that rewards drama, patience and timing.Across the workshop you'll photograph the classic Hartland Quay views and range out along some of the finest coast in the South West — from Bude and Clovelly to Welcombe Bay, Saunton Sands and Woolacombe. The focus is on the craft of seascape photography: composing a strong coastal frame, mastering long exposure to turn moving water and sky into mood, and timing your shoot to the light and the tide. But the technical side is only the floor — the real work is learning to see, composing with intention and reading light and tide as a harmony rather than chasing the obvious shot, working the intimate detail as readily as the grand vista. Each day follows that rhythm — optional sunrise and sunset shoots when the light is best, full days in the field with tuition, and evening photo reviews and editing sessions to sharpen your eye.With a maximum of just four photographers, this is genuinely personal tuition, and because the whole coast is tide- and light-dependent, Alan plans each day around the forecast and sends a detailed location itinerary a few days ahead. Tripods and ND filters can be lent if you don't yet own them, accommodation and breakfast are included, and you'll come away with a portfolio of dramatic Devon seascapes and a real command of long-exposure coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3856406", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Thu 19th 12:30 - Sun 22nd 12:30 Feb 2026 - 4 Days/3 Nights"}, {"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}, {"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 Nights"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1816,16 +1816,16 @@
         <v>775</v>
       </c>
       <c r="I25" t="n">
-        <v>895</v>
+        <v>950</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SQ3856406, SQ2516659</t>
+          <t>SQ2516659, SQ3856406</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SQ3856406</t>
+          <t>SQ2516659</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SnowdoniaDescription: Snowdonia National Park, located in North Wales, offers a diverse range of landscapes that will inspire and challenge any photographer. Snowdonia has everything from rugged mountains, flowing rivers, serene lakes, and ancient quarries.The park is home to some of the highest mountain ranges in England and Wales, providing a stunning backdrop for your photography journey. The terrain and landscape of Snowdonia, with its waterfalls, are great for long exposure techniques, the quarries and slate mines provide a starker but striking landscape to create images from the historic mining relics in the area, and last but not least, there are majestic lakes with reflections and mountains to practise and be inspired by to create compelling compositions from this rugged and serene landscape.</t>
+          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SnowdoniaDescription: This is a 2-day, 1-night residential landscape photography workshop in Snowdonia National Park, North Wales — open to all levels from beginner to advanced. Home to the highest mountain ranges in England and Wales, Snowdonia is a landscape that will both inspire and challenge any photographer: rugged peaks and flowing rivers, serene lakes and ancient slate quarries, all within a compact corner of Wales that you'll learn to read and photograph in its ever-changing light.What makes Snowdonia so rewarding is its variety, and over two days we work three very different faces of it: the waterfalls and rivers that are perfect for long exposure, turning moving water to silk; the starker, striking world of the historic slate quarries and mining relics, where industry and mountain meet; and the majestic lakes, where still water mirrors the peaks for compelling, reflective compositions. Across all of it the focus stays on the same craft — composing order from a vast scene, controlling exposure across big tonal ranges, and timing your shoot to the light and weather that shift the mood from rugged to serene and back. And throughout, the emphasis isn't just on the grand vista but on learning to see it — working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers and transport between locations included, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Likely locations include the reflective waters of Llynnau Mymbyr beneath the Snowdon massif, the Capel Curig pinnacles, Swallow Falls and the hidden lake of Llyn Craftnant. Accommodation and breakfast are included, so all you have to think about is your photography — and you'll leave with a varied portfolio that captures both the drama and the stillness of this remarkable landscape. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 3Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details: GowerDescription: Just a short distance away from Swansea, the Gower Peninsula is a remarkable sight for landscape photography in Wales.Gower is a truly unique environment that boasts heathlands, limestone grasslands, brackish and freshwater marshes, dunes and oak woodlands. It is characterised by a distinct combination of features, including lofty limestone cliffs, sandy beaches, and jagged rocky shores that together form its southern coastline. In the north, the coast is a series of tranquil salt marshes and dune systems. This is a perfect location for landscape photography Wales</t>
+          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details GowerDescription: This is a 3-day, 2-night residential landscape photography workshop on the Gower Peninsula in South Wales — the UK's very first Area of Outstanding Natural Beauty, and one of the finest stretches of coast for landscape photography in Wales. Open to all levels from beginner to advanced, it takes you along 19 miles of dramatic shoreline west of Swansea, where lofty limestone cliffs, golden sandy beaches and jagged rocky shores meet wild moorland, dunes and tranquil salt marshes.Over three days we work the peninsula's most iconic locations as the light and tides allow — from the sweeping expanse of Rhossili Bay and the dramatic outline of Worms Head to the wreck of the Helvetia and the snug cove of Pwll Du. The focus is on three things that make a strong coastal image: composing cliffs, beaches and rock forms into a balanced frame, mastering long exposure to draw movement out of sea and sky, and timing each shoot from dawn to dusk to catch the best light and tide. Throughout, the emphasis isn't just on the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and colour as a harmony rather than chasing the obvious shot. You'll photograph at sunrise and sunset, the richest hours on this coast, and return to locations in changing conditions to capture them at their best.With a small group taught personally, this is genuinely one-to-one tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Be prepared for some longer walks over cliff paths and rougher coastal ground to reach the best viewpoints. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Gower's iconic Welsh coastline — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: Photography Workshop Norfolk - We will photograph the North Norfolk coastline ranging from Overstand and Cromer sea fronts and groynes to the atmospheric estuaries of Morston Quay and Blakeney Harbour. Beach huts, boats, estuaries, marshland, there is something for everyone on this 3 day North Norfolk photography workshop.Abandoned boats, windmills, nature reserve, sand dunes, coastal erosion, coastal path/estuary, optional seal trip and of course seascapes. The silting has left a fascinating landscape of marshes, sandhills and mud banks, with many creeks and channels twisting and turning their way through. Blakeney village is set on a small hill leading down to the harbour and has pretty flint cottages.</t>
+          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: This is a 3-day, 2-night residential landscape photography workshop on the beautiful North Norfolk coast, based near Cromer — open to all levels from beginner to advanced. North Norfolk is one of the most varied and atmospheric stretches of coastline in England, and across a long weekend you'll photograph everything from classic seafronts and groynes to wild estuaries, windmills and big skies, learning to read and capture this ever-changing coastal landscape in its best light.There really is something for everyone here, and over three days we work a rich variety of locations as the light and tides allow — the seafronts and groynes at Overstrand and Cromer, the atmospheric estuaries of Morston Quay and Blakeney Harbour with their abandoned boats and twisting creeks, and the beach huts, windmills, sand dunes and flint-cottage charm of Blakeney village. The focus is on three things that make a strong coastal image: composing order from busy, expansive scenes, mastering long exposure to draw movement out of sea, sky and water, and timing each shoot to the tides and the soft coastal light. There's even an optional boat trip to see the seals along the way.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the North Norfolk coast — seascapes, estuaries, windmills and beach huts — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625462292-PCMT7Q118L1X51MPSENJ/Wells+Next+To+Sea+%2302+-+Sep+2022.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e301c931-8fdc-4ff0-bc78-618aea6241a1/Norfolk+Nov+2024+-+%2303.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Anglesey PhotographyDescription: A great location for a Landscape Photography Workshop Anglesey is a large island of 220 square miles of mainly farmland, but the coastline is excellent for photography with sandy coves, harbours, and rocky headlands in addition to the lighthouses. We will also explore some other areas, Parys Mountain, once the world's biggest copper mine, which has been used in many science fiction films and TV shows for its Martian-like coloured appearance.</t>
+          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Anglesey PhotographyDescription: This is a 3-day, 2-night residential landscape photography workshop on the iconic island of Anglesey, off the north-west coast of Wales, open to all levels from beginner to advanced. Anglesey's coastline is a photographer's dream — over 200 square miles ringed by sandy coves, working harbours, rocky headlands and three iconic lighthouses — and across a weekend you'll shoot it in the golden hours when its colour, light and sea views are at their most spectacular.We work the island's finest coastal locations — from Penmon Point's Trwyn Du Lighthouse and the Church in the Sea to South Stack, Llanddwyn Island and the strange, Martian-coloured landscape of Parys Mountain, once the world's largest copper mine. The focus is on three things that make a strong coastal landscape: composing sea, shore and sky into a balanced frame, working the golden-hour light at sunrise and sunset, and using long exposure to capture the movement of the Welsh sea. Throughout, the emphasis isn't just on the iconic view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading colour and light as a harmony rather than chasing the obvious shot. The days follow the light — optional sunrise and sunset shoots, full days on location with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Anglesey coastal images and the field craft to read light and sea anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2061,12 +2061,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 30 May</t>
+          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 7 Jun</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: Embark on a captivating journey of long-exposure photography amidst the secluded Welsh valley of Nant Mill. Join us for an immersive workshop where you'll discover the mesmerizing art of capturing river and waterfall scenes in this ancient woodland near Wrexham.</t>
+          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: This Nant Mill long exposure photography workshop takes you into a secluded Welsh valley near Wrexham, where a river and its waterfalls tumble through enchanting ancient woodland — open to all levels and any camera. Flowing water in a quiet, leafy gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this beautiful, tucked-away place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working the river, falls and woodland together, you'll learn to find order among the rocks, water and trees, to compose the intimate, close-up detail as readily as the wider valley view, and to read the soft, dappled light and the natural greens and browns of this ancient wood as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels the way the place actually feels.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of North Wales' hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventrySummaryLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 3 Weekly 2hr Evening Classes - All evening classes are from 19:00 to 21:00Participants: Max 3Lightroom Courses Event Details: Editing CourseCoventry 3 wks - Wed 4 Mar - 18 Mar 2026Coventry 3 wks - Wed 13 May - 27 May 2026Coventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Experience - Level: BeginnersThe beginners Lightroom photo editing classes are aimed at anyone wishing to learn photo editing and photo management with a workflow and consistencyEquipment Needed:You will need a laptop with Adobe Lightroom Classic subscription and the App installedAlan will provide you with training Lightroom Library with images and use that to explain and then demonstrate the various tools</t>
+          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventryLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 3Start Dates: Lightroom Editing Course Coventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Level: BeginnersDescription: A practical three-week evening course that takes you from a messy photo library and untouched RAW files to a finished, repeatable Lightroom Classic workflow — working on your own laptop throughout.Week 1 is about getting organised: catalogues, importing, collections, keywords and star ratings, so you can find and manage your photos for good rather than losing them across folders.Week 2 moves on to global adjustments — reading the histogram, then exposure, white balance, contrast, tone curves and sharpening — the core develop tools that do most of the work on any image.Week 3 covers local adjustments — graduated and radial filters, adjustment brushes and spot removal — and pulling it together into a consistent, repeatable style across your photos.With a maximum of three people, you get real hands-on help on your own screen whenever you hit a problem, plus course notes for each module and practical assignments to work on between sessions. Beginners welcome — no editing experience needed; just bring a laptop with Adobe Lightroom Classic installed and an active subscription.Equipment: You will need a laptop with Adobe Lightroom Classic subscription and the App installed. Alan will provide you with a training Lightroom Library with images and use that to explain and then demonstrate the various tools.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2142,11 +2142,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6876661", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Wed 4 Mar - 18 Mar 2026"}, {"@type": "Offer", "sku": "SQ0415856", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Wed 13 May - 27 May 2026"}, {"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>150</v>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SQ6876661, SQ0415856, SQ7526725, SQ6831161</t>
+          <t>SQ7526725, SQ6831161</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SQ6876661</t>
+          <t>SQ7526725</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 11 May 2026 - 18:30 - 20:30Tue 1 Sep 2026 - 18:00 - 20:00Wed 23 Sep 2026 - 17:45 - 19:45Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: KenilworthDescription: Join me for this evening Long Exposure Photography Workshop, where we will shoot Kenilworth Castle ruins against the night sky.Kenilworth Castle, formerly one of the strongest fortifications in the country, was reinvented in the Elizabethan era by Robert Dudley as an impressive palace for his queen. Initially built in the 1120s by Geoffrey de Clinton, the Norman keep served as a basis for the structure, and King John later added an external stone wall, as well as a reservoir, to the complex.</t>
+          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 11 May 2026 - 18:30 - 20:30Tue 1 Sep 2026 - 18:00 - 20:00Wed 23 Sep 2026 - 17:45 - 19:45Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details KenilworthDescription: This Long Exposure Photography Workshop is an evening shoot around the floodlit ruins of Kenilworth Castle in Warwickshire, open to all levels and any camera. Once one of England's mightiest fortresses and Robert Dudley's Elizabethan palace, the castle makes a dramatic subject against a darkening sky — and this workshop is built around the magic of long exposure at dusk, when the fading light, the castle's silhouette and a slow shutter combine to create atmospheric images that capture a sense of place, not just a record of a building.The long-exposure craft is the floor we build on, and we'll cover it properly: calculating exposure times for the movement and mood you want, focusing and exposing confidently in low light, and balancing ISO, shutter and aperture as the light drops. But the real work is learning to see. As the sky changes you'll compose the castle with intention — finding the frame beyond the obvious silhouette, working detail and texture as readily as the grand wide view, and reading the interplay of fading light, floodlight and deep shadow as a harmony rather than a problem to fight. The aim is an image with mood and restraint, where every element earns its place.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of England's most romantic castles — and a sharper, more intentional way of seeing light, movement and mood after dark anywhere.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Fairy GlenDescription: Long exposure and creating spectacular movement photos. Two great locations within a couple of miles of each other. Flowing River through gorge. A magical serene and secluded gorge through the river Conwy at Betws-y- Coed provides a great opportunity to practise long exposure photography and make images that capture the wonderful natural colours and light that frequently falls into this glen.</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Fairy GlenDescription: This Fairy Glen long exposure photography workshop takes you into one of Wales' most magical locations — a serene, secluded gorge where the River Conwy tumbles through the woods at Betws-y-Coed — and is open to all levels and any camera. Flowing water through a wooded gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this enchanting place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working two great locations within a couple of miles of each other, you'll learn to find order among the rocks, water and woodland, to compose the intimate detail as readily as the wider gorge, and to read the soft, dappled light and the natural greens and browns of the glen as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels like the place actually feels.With a maximum of just four photographers, this is genuinely personal tuition, with Alan guiding each person through observation, shot design, shooting and image reviews at both locations. You'll come away with a set of atmospheric long-exposure images of one of Snowdonia's hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 1st Aug 2026 - 18:45 - 21:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: BurnhamDescription: Experience the magic of long exposure photography against the breathtaking backdrop of Burnham on Sea's iconic lighthouse. Join us for an unforgettable workshop where you'll master the art of capturing stunning sunset seascapes. Our expert instructors will guide you through the process, helping you harness the beauty of this picturesque location in Somerset</t>
+          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 1st Aug 2026 - 18:45 - 21:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details BurnhamDescription: This Burnham on Sea long exposure photography workshop is an evening on the Somerset coast built around one of the most photogenic subjects in the country — the town's iconic nine-legged lighthouse, standing on stilts on the open beach. Open to all levels and any camera, it's about the art of long exposure: not just the silky-water effect, but learning to see this minimalist coast and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on, and we'll cover it properly — setting up, calculating shutter times and using filters — before heading onto the beach to shoot on an incoming tide as the sun sets. But the real work is composition and seeing. As the light builds you'll learn to place the lighthouse with real intention in a clean, minimalist frame, to work the intimate detail of stilts, reflections and wet sand as readily as the wide seascape, and to read the soft, shifting colour of a coastal sunset as a harmony rather than chasing a loud, over-saturated sky. The aim is mood and restraint — an image that feels like the quiet of that beach at dusk.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for settings, composition and one-to-one guidance in the field. Whether long exposure is new to you or you're refining your technique, you'll come away with a set of atmospheric sunset images of this famous Somerset landmark — and a sharper, more intentional way of seeing light, movement and mood that you can take to any coast.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2341,51 +2341,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Monthly Photography Mentoring Sessions - Online - Zoom</t>
+          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Photography mentoring online. Receive a monthly assignment to increase your skills across multiple genres and get expert feedback on your images each month</t>
+          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1559474612221-TBJKYSCMOO6IM7FTXJJI/online-photography-mentoring.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-online-photography-mentoring</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>online, photography-tuition, photography-courses</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1067929", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H35" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I35" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SQ1067929</t>
+          <t>SQ3248242</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2397,107 +2397,107 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details North YorkshireDescription: This is a 4-day, 3-night residential landscape photography workshop on the dramatic northeast coast of England, exploring the iconic coastline and moors of North Yorkshire — open to all levels from beginner to advanced. Based on the coast, you'll photograph some of the most atmospheric scenery in the country, from the tumbling fishing village of Staithes and the sweeping bay at Runswick to the harbour and abbey town of Whitby, with the wild North York Moors as a backdrop.Over four full days we work from sunrise to sunset to make the most of the best light, tides and empty beaches — far more time on location than a short workshop allows. The focus is on three things that make a strong coastal image: composing the rocks, headlands and shoreline into a balanced frame, mastering long exposure to draw out movement in the sea and sky, and timing each shoot to the tides and the golden light of dawn and dusk. Throughout, the emphasis isn't just on the postcard view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. Across the four days you'll build a real working rhythm for coastal photography, returning to locations in different conditions to capture them at their very best.With a maximum of just three photographers, this is exceptionally personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of iconic Yorkshire coast and moorland images — and the field craft to read light, tide and weather on any coastline. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714649253207-Y2XV1QZ3QPAVYS7CEE33/Flamborough+-+Temptation.jpg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>42</v>
+        <v>1450</v>
       </c>
       <c r="I36" t="n">
-        <v>250</v>
+        <v>1450</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SQ3248242</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
+          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: North YorkshireDescription: North Yorkshire Landscape Photography - We will be based on the northeast coast of England (North Yorkshire and the Moors) and visit some of the iconic coastlines of Staithes, Runswick, Whitby and more. We will concentrate our workshop time along the impressive coastline and work from sunrise to sunset to ensure we make use of the best light, tides and empty beaches. This is the perfect workshop for practising long exposures and working at sunrise and sunsets to get those iconic views on the coast.</t>
+          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details HeathersDescription: Every August the moors of the Peak District turn a spectacular purple as the heather comes into bloom, and this Peak District Heather Photography Workshop is your chance to capture that fleeting display at its very best — open to all levels and any camera. Run as short, focused sessions at the magic hours of sunrise and sunset, it pairs one of Britain's most iconic landscapes with its richest seasonal colour, and the low golden light that makes heather and gritstone glow.You can join either of two sessions, or both: a sunset shoot at Surprise View above Hathersage in Derbyshire — one of the finest viewpoints in the Peak, with sweeping heather foregrounds, the Mother Cap stone and famously dark skies — or a sunrise shoot among the dramatic gritstone of The Roaches, Hen Cloud and Ramshaw Rocks in Staffordshire, weathered into extraordinary shapes above a sea of purple moorland.A blaze of purple is more seductive than it is easy, and the real work is learning to see past the obvious. The technical craft is the floor we build on — controlling exposure to hold rich colour and a dramatic sky, and working quickly in the brief light of dawn and dusk — but the focus is on composing with intention: balancing the heather and the gritstone rock forms into a frame with order, working the intimate detail of bloom and weathered stone as readily as the wide moorland vista, and treating the purple, the gold and the low light as a harmony rather than a colour to crank. We shoot two to three locations each session as conditions allow, and the aim throughout is an image with mood and restraint — one that feels like that moor at first or last light.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you take the sunset, the sunrise or make a weekend of both, you'll come away with a portfolio of the Peak District's heather at its peak — and a sharper, more intentional way of seeing colour, light and landscape that you can take anywhere. If you're booking both sessions, please arrange your own overnight accommodation near The Roaches for the early sunrise shoot. Please also note this is a seasonal workshop tied to the heather bloom, so exact dates may shift slightly with the season.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707212716744-VYD7AYV9U6N6VEZ3C4D1/North+Yorkshire+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1685361335026-KNDKR6D00CTPUASRDWDV/Surprise%2BView%2B2.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>1450</v>
+        <v>125</v>
       </c>
       <c r="I37" t="n">
-        <v>1450</v>
+        <v>200</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ1994489, SQ1389945, SQ5395624</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ1994489</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2509,51 +2509,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
+          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: HeathersDescription: Peak District heather WorkshopsSurprise View, perched atop Hathersage, is one of the best viewpoints in the Peak District. It's a perfect spot to admire the sunset and, on a clear night, is a designated 'Dark Skies' stargazing location. To access this special place, head uphill in a northerly direction from the car park and find the strangely shaped Mother Cap stone. Then, marvel at the vivid stars filling the Peak District's dark skies.The Roaches, with Hen Cloud and Ramshaw Rocks, form a gritstone escarpment that marks the Peak's south-western edge. Best viewed from the approach along the Leek road, they stand as a line of silent sentinels guarding the entrance to the Peak District, worn into fantastic shapes by the elements.</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details ChestertonDescription: This sunset landscape photography workshop is an evening shoot at Chesterton Windmill, one of Warwickshire's most iconic landmarks, open to all levels and any camera. A striking 17th-century tower windmill on its arched stone legs, standing alone on a hilltop for nearly 350 years, it's one of the most photogenic structures in the county — and this workshop is built around capturing it in the golden light of sunset and the long-exposure drama of the hour that follows, in a way that's genuinely your own rather than the postcard everyone already has.The technical craft is the floor we build on — exposure, depth of field, and setting up long exposures to draw movement out of cloud and sky as dusk falls. But the real work is learning to see this familiar landmark freshly: composing the windmill with intention against the sky and the rolling countryside, finding the unexpected angle and the intimate detail as readily as the wide hilltop vista, and reading the warm, directional light of sunset as a harmony to compose with rather than just a pretty backdrop to point at. As the colour builds and fades, you'll learn to design a frame where the light, the land and the windmill all work together.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to landscape photography or refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric images of this famous Warwickshire landmark — golden-hour silhouettes and long-exposure skies — and a sharper, more intentional way of seeing light and composition that lets you photograph any landmark at its best.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707246605883-FVZKLJN54Z455J1Q13CV/peak+district+heather.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="I38" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SQ1994489, SQ1389945, SQ5395624</t>
+          <t>SQ3572999, SQ0796814, SQ9554270, SQ5307067</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SQ1994489</t>
+          <t>SQ3572999</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2565,107 +2565,107 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Photo Print Preparation Service 30-min – File Check &amp; Advice</t>
+          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Book a 30 min Photo Print Preparation Service. I check crop, aspect ratio and DPI, enlarge, retouch, sharpen and supply print-ready image for you to print</t>
+          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details LavenderDescription: This Lavender Photography Workshop is a magical evening among the lavender rows of the Cotswolds at Snowshill in Gloucestershire — open to all levels and any camera. Best of all, you'll photograph the fields after the farm has closed to the general public, so instead of working around coachloads of day-trippers you have the spectacular sea of purple and the wildflower areas largely to yourselves — making it far easier to slow down, see properly and compose clean shots as the light softens towards sunset and the colour comes alive.A field of lavender is seductive but deceptively hard — it's all too easy to come home with the loud, over-saturated purple shot everyone takes. The real work here is learning to see past that. The technical craft is the floor we build on — focusing and exposing accurately in fading light, and holding both shadow and highlight as the sun drops — but the focus is on composing with intention: finding order and a lead-in through the endless rows, working the intimate, abstract close-up of colour and texture as readily as the sweeping vista, and treating the purple, the green and the warm evening light as a harmony to balance rather than a colour to crank. The aim is a photograph with mood and restraint — one that feels like that quiet evening in the field.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance throughout. With the crowds gone and the fields quiet, you'll have the space and time to really work your compositions — and you'll come away with a portfolio of vivid lavender images at their most atmospheric, plus a sharper, more intentional way of seeing colour, light and detail that you can take anywhere. This is a special after-hours session: the farm opens to us beyond its normal public hours so we can shoot from 5pm into the early sunset light, and your workshop fee includes that commercial after-hours access. Please note the dates and finish times are set by the lavender farm rather than by Alan, and may be subject to change with the season and flowering.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photo-print-preparation-service-30min</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5582230", "price": "29.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ6748367, SQ7542811</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SQ5582230</t>
+          <t>SQ6748367</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
+          <t>Poppy Fields Photography Workshops | Worcestershire</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: ChestertonDescription: Immerse yourself in the beauty of Warwickshire's iconic Chesterton Windmill with our exclusive sunset landscape photography workshop. Join us for an enriching experience where you'll delve into the art of composition and light, guided by experienced photography professionals.</t>
+          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: There are few sights in the English summer to beat rolling Worcestershire hills washed red with wild poppies, and this Poppy Fields Photography Workshop is built to catch them at their fleeting best. Open to all levels and any camera, it runs as short, focused sessions at the golden hours of sunset and sunrise — the two times of day when low, warm light makes a field of poppies truly glow.A field of red is more seductive than it is easy, and the work is learning to turn it into a photograph rather than a snapshot. The focus is on three things: composing with intention to find order and a lead-in through a busy, repeating scene, controlling exposure and depth of field to decide what's sharp and what dissolves into colour, and reading light, texture and colour as a harmony — letting the reds sing without tipping into the over-saturated cliché. You'll work both the intimate, single-stem detail and the sweeping vista, and learn to see past the obvious shot everyone else takes.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you join the sunset session, the dawn one, or both, you'll come away with a portfolio of poppy-field images at their most atmospheric — and a stronger way of seeing colour, light and composition that carries into everything you photograph next. Please note that poppies bloom briefly and unpredictably each June, so both the exact dates and the field we use are confirmed at short notice once the flowering is at its best. A flexible approach is essential — but it's exactly what lets us photograph the poppies at their absolute peak.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="I40" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SQ3572999, SQ0796814, SQ9554270, SQ5307067</t>
+          <t>SQ8740143, SQ7189877</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SQ3572999</t>
+          <t>SQ8740143</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2677,331 +2677,331 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
+          <t>Online Photography Classes 121 - Zoom - Package Options</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: LavenderDescription: Join me in the Cotswolds for a spectacular sight of Lavender. We will shoot into the evening hours and capture some great colour - go abstract or vista; the choice is yours.</t>
+          <t>Private Online Photography Classes (Zoom)Summary - Private Online Photography Classes - Key InformationFormat: Online 1-2-1 via Zoom (free to use)Sessions: Single 1hr lesson, or discounted packages of 4, 6, 8 or 12 hoursAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — use within 12 months of purchaseLevel: All levels, beginner to advancedDescription: Private online photography classes tailored to your needs — tuition and support on any aspect of photography, with no other students, so the time you pay for is dedicated entirely to your own style and pace.Equipment: Anything you want to learn or improve on. Sessions run over Zoom, with notes provided; submit images for detailed feedback between lessons.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
+          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SQ6748367, SQ7542811</t>
+          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SQ6748367</t>
+          <t>SQ1461156</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Poppy Fields Photography Workshops | Worcestershire</t>
+          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: Rolling hills full of poppies takes some beating. Join me for one of the poppy fields photography location shoots from early June to end of June in Worcestershire - These are provisional dates and may change depending on mother nature.</t>
+          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="I42" t="n">
-        <v>95</v>
+        <v>750</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SQ8740143, SQ7189877</t>
+          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SQ8740143</t>
+          <t>SQ4217445</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Online Photography Classes 121 - Zoom - Package Options</t>
+          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Private online photography classes tailored to your needs - Tuition &amp; support on any aspect of photography - Pay Now - Book dates later.Online photography classes and support are run via Zoom (free to use)Must be used within 12 months of purchase dateIf you want a package (series) of lessons, these package options offer a discount for purchasing multiples. Mon - Fri - 9 am - 5 pm1 x 1hr - £50 - Normal Price for lesson4 x 1hr - 15% Off normal price6 x 1hr - 20% Off normal price8 x 1hr - 25% Off normal price12 x 1hr - 25% Off normal price</t>
+          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select a package of Zoom sessions within twelve months at intervals to suit youDescription: Independent one-to-one RPS mentoring for your Licentiate (LRPS) or Associate (ARPS) distinction — online via Zoom, with a mentor who holds both distinctions himself and has a 100% pass rate to date. Most photographers who fall short don't fail on technique — they submit a collection of strong individual images rather than a planned, cohesive panel, and a panel is judged as a whole. That judgement — image selection, sequencing, the hanging plan and your Statement of Intent — is exactly what mentoring brings. We work in three stages: plan the panel, build and refine it, then test readiness before you submit. Sessions are flexible 1-hour Zoom slots — buy only what you need and book your dates later, across up to twelve months. Start fresh, or revise a panel that didn't pass first time.Format: One-to-one, online via Zoom — private and personal to you and your panel.Equipment Needed: Zoom App; free Dropbox account for sharing portfolios and updated images.Terms: A package of Zoom sessions must be used within 12 months of purchase or it is forfeited. You can extend the timeline or purchase additional sessions if needed.Method: Honest technical and creative critique with suggestions for improvement; advice on image selection, sequencing, the hanging plan and your Statement of Intent.Package Options: Choose Mon–Fri 9am–5pm daytime rates, or Mon–Sun 9am–9pm for evening and weekend flexibility.1 × 1hr — single session (fact-find &amp; review)4 × 1hr — 15% off (reset a failed panel)6 × 1hr — 20% off (from scratch, recommended)8 × 1hr — 25% off (extended panel build)12 × 1hr — 25% off (best value, full programme)More Details: about the RPS Mentoring Course</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
+          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H43" t="n">
         <v>50</v>
       </c>
       <c r="I43" t="n">
-        <v>450</v>
+        <v>675</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
+          <t>SQ7839038, SQ3867813, SQ8903198, SQ4831915, SQ1077689, SQ8233730, SQ9139531, SQ0776423, SQ2385997, SQ9440259</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SQ1461156</t>
+          <t>SQ7839038</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
+          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: The Secrets of Woodland Photography is a 1-Day Masterclass in Coventry, open to all levels and any camera. Woodland is the hardest subject there is — chaotic, cluttered, endlessly busy — which is exactly why it's the best place to learn to see. Most people come away with the tangled, cliché shot; this day is about learning to find the order, the light and the quiet beauty hidden within the chaos, and to make woodland images that are calm, intentional and your own.The technical setup matters, but it's only the floor we build on. Rather than a typical walk-and-shoot, the day runs as three connected sessions — theory, practical and editing — so we can go deeper than settings. We start with the thinking behind a strong woodland image and the craft that delivers it: simplifying a busy scene, using light and shadow, choosing what to include and what to leave out. Then you put it into practice on a woodland walk, working the close-up, the macro detail and the abstract as readily as the wider view — reading texture and colour as a harmony, not chasing the loud, over-saturated shot. Finally we review your images together and finish on the editing that brings the quiet colours of the forest to life without shouting.The day runs from Alan's home, which offers three things most workshops can't: instant access to woodland straight from the garden, a comfortable covered and heated space for the presentations and image reviews, and a large screen to study your shots on — so the day works whatever the weather. You'll leave not just with a set of woodland images, but with a way of seeing — light, simplicity and restraint — that changes how you photograph trees, nature and detail wherever you go next.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 11th Apr 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I44" t="n">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
+          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SQ4217445</t>
+          <t>SQ4914997</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
+          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select six online Zoom sessions within twelve months at intervals to suit youRPS Courses - Mentoring for DistinctionsParticipants: Via Zoom online in a group of max 3, or on 1-2-1 basis.Equipment Needed: Zoom AppDropbox App used for updated portfolios and imagesTerms: Sessions must be taken within 12 months of booking the course or forfeited, but there are options to extend the timeline and retain unused classes or add additional classes.Method:Technical and creative critique with suggestions for improvementAdvice on image selection and panel layoutMore Details about the RPS Mentoring Course*Note: Your tutor, Alan Ranger, holds both the RPS's Licentiate and Associate Distinctions, but the RPS does not accredit this Course. This is not an approved course or endorsed by the RPS as an organisation. Alan’s advice is private, unofficial and based on his experience and understanding of the elements required to reach the standard that may result in being awarded a distinction without any guarantee.</t>
+          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Sezincote Garden Photography Workshop takes you into one of the most extraordinary gardens in the Cotswolds — the grounds of a Mughal Indian palace, complete with copper dome and minarets, set in the gentle hills of Gloucestershire and open to all levels and any camera. Few gardens offer a photographer this much: a water garden of seven pools, waterfalls and a grotto, a temple to the Hindu sun god Surya, and a curving Orangery framing a Persian Garden of Paradise — all waiting to be explored through your lens.A setting this rich is a wonderful place to slow down and learn to see. The technical craft is the floor we build on — sharp focus, controlling depth of field to isolate a subject, the settings that give you control — but the real work is composition and intention. Working through the estate's grounds together, you'll learn to find a strong frame within a busy, ornate scene, to work the intimate macro and close-up detail as readily as the wide views of pools, temple and dome, and to read the light and the colour as a harmony rather than chasing the loud, obvious shot. The aim is always an image that's considered and your own, not just a record of a remarkable place.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for camera settings, composition and one-to-one guidance, plus image reviews to spark ideas and inspiration on the day. You'll come away with a portfolio of images from one of England's most unusual gardens — and a sharper, more intentional way of seeing detail, composition and light in any garden you photograph. Please note the workshop fee does not include the entrance fee to Sezincote garden and house, which is payable separately on the day.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3499847", "price": "295.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Distinctions Course - 6 Sessions"}, {"@type": "Offer", "sku": "SQ5925235", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 6 Months (No Extra Sessions)"}, {"@type": "Offer", "sku": "SQ1898169", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 2 classes within 3 months"}, {"@type": "Offer", "sku": "SQ7296901", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 4 classes within 6 months"}, {"@type": "Offer", "sku": "SQ4136369", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "RPS Extend 6 classes 12 months Extra"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I45" t="n">
-        <v>295</v>
+        <v>50</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SQ3499847, SQ5925235, SQ1898169, SQ7296901, SQ4136369</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SQ3499847</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
+          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: It will be different from other workshops in the format as it will be divided into separate sessions during the day to tackle theory, set-up, shooting, image review, and post-production.A theory session and discussion on woodland photography and its challenges and some answers, followed by practical advice on settings, lenses, equipment, etc.A presentation on developing creative vision and simplification in woodland settingsA 2hr woodland exploration and walk-making compositions and turning theory into practice in the field.Initial image reviews and critiques to shortlist images to editDemonstration, advice and post-production of your woodland images</t>
+          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SuffolkDescription: This is a 3-day, 2-night residential Suffolk landscape photography workshop based on the Southwold and Aldeburgh coast, open to all levels from beginner to advanced. The Suffolk coastline is one of England's most photogenic and most varied — wide shoreline vistas, big skies, and a wealth of subjects most coastlines can't match: weathered piers, painted beach huts, iconic sea-defence structures and the traditional sails of Herringfleet Windmill. It's a landscape that rewards photographers who slow down and learn to see it.The focus is on long exposure and the art of black and white photography — learning to compose a strong coastal frame, to use long exposures to smooth water and sky into mood, and to recognise when a scene works better in mono. It's about more than the technical craft, though: the real work is learning to see — composing with intention, working intimate detail as readily as the wide vista, and reading light and tone as a harmony rather than chasing the obvious shot. It's never prescriptive either: over three days and two to three locations a day — from Southwold and Walberswick to Dunwich, Orford and Aldeburgh — we work with whatever light and conditions the coast gives us, with early sunrise shoots, full days in the field with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the group, the season, the tides and the forecast, and sends a detailed location itinerary a few days ahead. En-suite accommodation and breakfast are included, so all you have to think about for three days is your photography. You'll come away with a portfolio of atmospheric Suffolk coastal images and a real grasp of long exposure and black and white technique. An extra night is available the day before on request, ideal for those travelling from a distance — contact me to arrange.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714667523305-2SEM1T5WD278HHO4HJIV/Southwold+Sunrise.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
+          <t>coastal, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun 11th Apr 2026 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>150</v>
+        <v>995</v>
       </c>
       <c r="I46" t="n">
-        <v>150</v>
+        <v>995</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SQ4914997</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3013,51 +3013,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
+          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Garden PhotographyDescription: Sezincote is a Mughal Indian palace set in the Cotswold Hills, created by the nabob Charles Cockerell in 1805.The house is surmounted by a copper dome and minarets, and set in a picturesque water garden with seven pools, waterfalls, a grotto and a temple to Surya, the Hindu Sun God. A curving Orangery frames the Persian Garden of Paradise.</t>
+          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: This Urban Architecture Photography workshop is an evening walk through the historic heart of Coventry — once UK City of Culture — open to all levels and any camera. Cities transform after dark: artificial light, deep shadow and the last colour in the sky turn ordinary buildings and ruins into something dramatic, and this 2.5-hour workshop is built around learning to see and design photographs at night, in the tricky low light most people find hardest to shoot.Confident technique in the dark is the floor we build on — and we'll cover it: focusing and exposing accurately in low light, and setting up long exposures to capture movement and mood. But the real work is learning to see the city as a photographer. Walking together through old and new architectural corners — including the cathedral area and its ruins — you'll learn to compose with form, line, texture and contrast, to read the interplay of artificial light and shadow as a harmony rather than a problem, and to find the considered, intentional frame instead of the obvious postcard of a landmark. Old against new, light against dark, detail against sweep — it's about designing an image, not just recording a building.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to night photography or refining your eye you get real one-to-one guidance in the field. You'll come away with a set of atmospheric urban and architectural images — long exposures, abstracts, dramatic skies — and a sharper, more intentional way of seeing that lets you photograph any city after dark.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "55.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3069,51 +3069,51 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
+          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: SuffolkDescription: Suffolk Landscape Photography Workshop - The Suffolk coastline offers a wide variety of views and caters for all styles and ways of interpreting the land and seascapes. There will be a rich mixture of coastal shoreline vista to shoreline architecture including piers, beach huts and iconic sea defence structures.</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details Lake VyrnwyDescription: This is a 2-day, 1-night residential Wales photography workshop based in the valleys of Mid-Wales, open to all levels from beginner to advanced. It's built around two of the country's most rewarding landscape locations — Pistyll Rhaeadr, an enchanting waterfall in the Berwyn Mountains and, at 240ft, Britain's tallest single-drop fall, and the tranquil 11-mile shoreline of Lake Vyrnwy — giving you woodlands, water, mountains and one of the seven wonders of Wales in a single weekend.Over two days we work both locations at their best. At Pistyll Rhaeadr you'll photograph the three-stage falls from the viewing platform and bridge, then drop down to water level among the slate beds and mini-falls for intimate compositions; around Lake Vyrnwy we take a leisurely circuit of the reservoir, stopping at quiet bays and outlets and walking the river to the waterfall at the valley head. The focus is on three things that make moving water and big Welsh landscape work: composing a strong frame from a busy natural scene, mastering long exposure to turn falling water into silk, and reading the light and weather that give these valleys their mood. Throughout, the emphasis isn't just on the famous waterfall but on learning to see it — working intimate detail as readily as the wide vista, and treating light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of Welsh waterfalls, lakes and valleys — and a real command of long-exposure water technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714650055069-5DPM44ERXSX234XAGLA9/Southwold+%2304+-+February+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>coastal, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>995</v>
+        <v>695</v>
       </c>
       <c r="I48" t="n">
-        <v>995</v>
+        <v>695</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3125,51 +3125,51 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
+          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: Join me on this evening urban architecture photography workshop and learn how to see and design images at night! We will walk around several historic parts of Coventry in this 2.5hr workshop, photographing buildings and ruins - all to practise the art of dealing with tricky light, learning how to focus in the dark, long exposures and hopefully some good skies to help us capture that big space above us.</t>
+          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Crackley Wood, Kenilworth - Fri Nov 6Hay Woods - Solihull Fri Dec 4Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: This is a relaxed, informal woodland photography walk through the beautiful woodlands in and around Warwickshire — a regular monthly outing open to all levels and any camera. It's a gentle two hours among the trees with camera in hand, and it's as much about slowing down and reconnecting with nature as it is about photography: we walk, we observe, we take in the wood around us, and we make a photograph when something moves us to — or simply enjoy being there.My aim isn't to tell you what to shoot. It's to help you develop your own visual awareness, your photographic eye and your personal interpretation of what's in front of you. Woodland is one of the hardest subjects there is — chaotic, cluttered, endlessly busy — so the real work is learning to see: to simplify the scene, to find the quiet order and the light within the tangle, and to photograph the close-up, the intimate detail and the abstract as readily as the wider woodland view. I'm always on hand for the "how to" — the settings and the craft — but in service of what you feel drawn to express, not a shot list.The walks rotate through a lovely variety of local woodlands across the seasons — among them Crackley Wood, Hay Wood, Tile Hill Nature Reserve, Millisons Wood and Piles Coppice — so there's always something new to see. With no more than six of us it stays personal and unhurried, with one-to-one guidance whenever you want it. You'll come away with images that are genuinely your own — and a calmer, more intentional way of seeing that stays with you long after the walk.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
+          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I49" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ1654264, SQ1288994, SQ0063623, SQ6524101, SQ7078023, SQ3819844</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ1654264</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3181,22 +3181,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
+          <t>Landscape YORKSHIRE DALES Photography Workshop - 16 - 18 Apr</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details: Lake VyrnwyDescription: Pistyll Rhaeadr is an enchanting waterfall in the Berwyn Mountains, just inside Wales, west of Oswestry and Shrewsbury. At 240ft (73m) high, Britain's tallest single-drop waterfall (with a drop 20m higher than Niagara Falls) captivates all who visit her—known as one of the seven wonders of Wales with its three stages of drops. Generation after generation take in the spirit and presence of this remarkable place. Surrounding the falls is a viewing platform, bridge, and woodland alongside the Afon Rhaeadr.Pistyll Rhaeadr offers an excellent opportunity to practice long exposure photography of moving water with many viewpoints of the falls and also down at water level with its laminated slate beds and plenty of mini falls and closer-up compositions to make.Lake Vyrnwy is a reservoir in Powys, Wales, built in the 1880s for Liverpool Corporation Waterworks to supply Liverpool with fresh water. It flooded the head of the Vyrnwy valley and submerged the village of Llanwddyn. These two locations to give you a real taste of Wales photography</t>
+          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Yorkshire DalesDescription: This is a 3-day, 2-night residential landscape photography workshop in the Yorkshire Dales — one of England's most iconic and varied landscapes, open to all levels from beginner to advanced. From dramatic limestone pavements and amphitheatre cliffs to tumbling waterfalls, soaring viaducts and lone, wind-sculpted trees, the Dales pack an extraordinary range of subjects into one area, and over a long weekend you'll learn to read and photograph this moody, dramatic country in its best light.Across three days we work some of the Dales' most rewarding locations as the conditions and season allow — the natural amphitheatre of Malham Cove and the ravine at Gordale Scar, the waterfalls of Ingleton, Aysgarth and Janet's Foss, the sweeping arches of Ribblehead Viaduct, and the famous lone tree set on its bare limestone pavement. The focus is on three things that make a strong Dales image: composing rock, water and vista into a balanced frame, mastering long exposure to bring waterfalls and rivers to life, and timing each shoot — including early morning starts — to the dramatic light and weather these hills are known for. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Yorkshire Dales — waterfalls, limestone pavements, viaducts and classic vistas — and the field craft to capture dramatic upland landscape anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>695</v>
+        <v>895</v>
       </c>
       <c r="I50" t="n">
-        <v>695</v>
+        <v>895</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3237,426 +3237,54 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2025 - 09:30 - 11:30Crackley Wood, Kenilworth - Fri Nov 7Hay Woods - Solihull Fri Dec 5Tile Hill Nature Reserve Mon Dec 82026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: Simplifying Woodland Photography: Unlocking the Secrets to Capturing the Beauty of Nature on a photography walkMy aim is not to instruct you what to shoot, instead, I want to help you develop your own sense of visual awareness, photographic eye and your personal interpretation. I will be happy to help you with the “how to shoot” whatever it is you feel drawn to and wish to express through your creative vision using the camera to construct your intention. The photography walks around these selected woodlands are aimed to promote our senses and connection to trees/woodland/nature - as we walk, observe and take in our environment we may decide to make a photograph, or not.</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
+          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops, photography-gift-vouchers;photography-presents</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Nov 7 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Dec 5 - Hay Wood - Lapworth"}, {"@type": "Offer", "sku": "SQ3142823", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon Dec 8 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Fri Oct 16 - Piles Coppice, Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SQ7078023, SQ3819844, SQ3142823, SQ1654264, SQ1288994, SQ0063623, SQ6524101</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SQ7078023</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Landscape YORKSHIRE DALES Photography Workshop - 16 - 18 Apr</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Yorkshire DalesDescription: Yorkshire Dales photography workshop - An exciting 3-day residential photography workshop visiting some gorgeous spots around the Yorkshire Dales. Includes early morning shoots and a variety of moody and dramatic scenes for you to practice, learn and hone your photographic skills.</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18"}]</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="n">
-        <v>895</v>
-      </c>
-      <c r="I52" t="n">
-        <v>895</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>SQ9211910</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>SQ9211910</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops, photography-gift-vouchers;photography-presents</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>5</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Alan Ranger Academy - Photography Foundation Course eBook</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Alan Ranger Academy - Photography Foundation Course eBook</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/578e5993-00d9-4963-9053-6241bc6c4336/Photography+Course+Sixty+Foundation+Modules-For+Beginners-.jpg</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-foundation-course-ebook</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-", "price": "25.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Alan Ranger Academy - Photography Foundation Course eBook"}]</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="n">
-        <v>25</v>
-      </c>
-      <c r="I54" t="n">
-        <v>25</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>SUP-ALAN-RANGER-ACADEMY-PHOTOGRAPHY-</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>course</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>15 Camera Settings — Photography Field Checklists PDF Bundle</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>15 Camera Settings — Photography Field Checklists PDF Bundle</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/camera-settings-photography-field-checklists</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "15 Camera Settings — Photography Field Checklists PDF Bundle"}]</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>15</v>
-      </c>
-      <c r="I55" t="n">
-        <v>15</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>SUP-15-CAMERA-SETTINGS-PHOTOGRAPHY-F</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>10 Composition PDFs — Photography Field Checklists Bundle</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10 Composition PDFs — Photography Field Checklists Bundle</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/composition-settings-photography-field-checklists</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-", "price": "10.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "10 Composition PDFs — Photography Field Checklists Bundle"}]</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="n">
-        <v>10</v>
-      </c>
-      <c r="I56" t="n">
-        <v>10</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>SUP-10-COMPOSITION-PDFS-PHOTOGRAPHY-</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>35 PDFs — 1 Page Photography Field Checklists Bundle</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/703f4ba2-fd71-4744-a5b2-b93502115372/field_checklists_cover_square_v2.jpg</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-35bundle-photography-field-checklists</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "35 PDFs — 1 Page Photography Field Checklists Bundle"}]</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" t="n">
-        <v>30</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>SUP-35-PDFS-1-PAGE-PHOTOGRAPHY-FIELD</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Foundation Digital Pack – 60 Modules, Checklists &amp; Exams</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/99e1a922-9f30-4f2a-a27e-5e7ba52c72de/Digital+Download+Product+1-+Academy.png</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://www.alanranger.com/photography-services-near-me/foundation-digital-pack-plus</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>[{"@type": "Offer", "sku": "SUP-FOUNDATION-DIGITAL-PACK-60-MODUL", "price": "69.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-05-18", "priceValidUntil": "2027-05-18", "name": "Foundation Digital Pack – 60 Modules, Checklists &amp; Exams"}]</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="n">
-        <v>69</v>
-      </c>
-      <c r="I58" t="n">
-        <v>69</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>SUP-FOUNDATION-DIGITAL-PACK-60-MODUL</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
         <is>
           <t>product</t>
         </is>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue Jul 7th - 6:30pm - 8:30pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8660736", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue Sep 8th - 6:00pm - 8:00pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue Jul 7th - 6:30pm - 8:30pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8660736", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue Sep 8th - 6:00pm - 8:00pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -666,12 +666,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 4Start Dates: Beginners Photography Course3wks Thursdays - Jun 11 - Jun 25 Coventry3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 CoventryLevel: Beginner and NoviceDescription:A practical three-week evening course that takes you from Auto to confident manual control, built around your own camera.Week 1 is about getting off Auto for good — the exposure modes, then aperture, shutter speed and ISO, and how they work together as the exposure triangle, with practical assignments to put it into practice.Week 2 goes deeper into getting the exposure right: manual exposure, metering, reading the histogram, exposure compensation, stops and dynamic range, and bracketing — followed by a review of your assignment work.Week 3 moves on to focusing and depth of field, white balance, JPEG vs RAW, and the foundations of composition, finishing with a final assignment review.With a maximum of four people, you get genuine attention and plenty of room to ask questions, and you'll leave with a printed course book covering every topic to revisit at home. Beginner and novice friendly — just bring a DSLR or mirrorless camera with manual modes.What You'll Learn: How to get off Auto and use manual exposure, aperture, shutter speed and ISO; how focus works; and the foundations of composition to make stronger, more deliberate photos.Includes: A printed course book covering every topic, so you can revisit it all afterwards.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
+          <t>Beginners Photography Course CoventrySummary - Camera Courses For Beginners - Key InformationLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 4Start Dates: Beginners Photography Course3wks Wednesdays - Jul 1 - Jul 15 Coventry3wks Mondays - Jul 6 - Jul 20 Coventry3wks Thursdays - Sep 17 - Oct 1 Coventry3wks Tuesdays - Sep 22 - Oct 6 Coventry3wks Mondays - Oct 12 - Oct 26 Coventry3wks Wednesdays - Oct 14 - Oct 28 Coventry3wks Mondays - Nov 9 - Nov 23 Coventry3wks Tuesdays - Dec 1 - Dec 15 Coventry3wks Wednesdays - Jan 13 - Jan 27 Coventry3wks Thursdays - Jan 28 - Feb 11 CoventryLevel: Beginner and NoviceDescription:A practical three-week evening course that takes you from Auto to confident manual control, built around your own camera.Week 1 is about getting off Auto for good — the exposure modes, then aperture, shutter speed and ISO, and how they work together as the exposure triangle, with practical assignments to put it into practice.Week 2 goes deeper into getting the exposure right: manual exposure, metering, reading the histogram, exposure compensation, stops and dynamic range, and bracketing — followed by a review of your assignment work.Week 3 moves on to focusing and depth of field, white balance, JPEG vs RAW, and the foundations of composition, finishing with a final assignment review.With a maximum of four people, you get genuine attention and plenty of room to ask questions, and you'll leave with a printed course book covering every topic to revisit at home. Beginner and novice friendly — just bring a DSLR or mirrorless camera with manual modes.What You'll Learn: How to get off Auto and use manual exposure, aperture, shutter speed and ISO; how focus works; and the foundations of composition to make stronger, more deliberate photos.Includes: A printed course book covering every topic, so you can revisit it all afterwards.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e7a77ef5-4a16-4466-9e54-7d29287e9a95/photography+training.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/773443e9-940a-440b-9faa-14e22b8c4236/beginners+photography+classes+coventry.png</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -686,11 +686,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0678506", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Thursdays - Jun 18- Jun 25 Coventry"}, {"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}, {"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
         <v>150</v>
@@ -700,12 +700,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SQ0678506, SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762</t>
+          <t>SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762, SQ5616379, SQ3231903, SQ5559634, SQ0659870</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SQ0678506</t>
+          <t>SQ4322859</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Coventry - 1 Day</t>
+          <t>Beginners Portrait Photography Course - Coventry - 11 Oct 2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707238641610-VHWSAVN4IPEHPVRGJNQZ/portrait+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7d4f9092-b44c-4d74-b858-cc2bcf675b8b/portraits+class.png</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -773,219 +773,219 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Professional Black and White Photography Course | Coventry</t>
+          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr - 30 Apr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Black and White Photography CourseLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 2 × 2.5hr evening classesParticipants: Max 4Start Dates: Black &amp; White CourseCoventry 2 wks - Mon 3 Sep - 10 Sep 2025Level: Beginner to IntermediateDescription: A two-week course to help beginners and intermediates recognise the visual building blocks of strong black &amp; white images, capture the best data in camera, and convert to mono on the computer.Equipment: A DSLR or mirrorless camera with manual exposure modes. (confirm any editing software requirement)</t>
+          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-274hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Bluebell WoodsDescription: This Bluebell Woodlands photography workshop gives you exclusive access to a private Warwickshire bluebell wood near Stratford-upon-Avon, open to all levels and any camera. For a few short weeks each spring the woodland floor turns into a sea of blue — and unlike the well-known public bluebell spots, this one is yours to photograph without the crowds, so you can slow right down and work the scene properly in soft woodland light, rather than grabbing the same shot everyone else takes.You choose how you shoot it. Pick a four-hour half-day session — sunrise (5:45am–9:45am) for soft, warm early light, or mid-morning (10:30am–2:30pm) for brighter colour — or book the full day (5:45am–2:30pm) to shoot both, with a brunch break in between (9:45–10:30, not included). Whichever you choose, the technical craft is the floor we build on — composition, depth of field, the settings that hold a carpet of blue in focus — but the real work is learning to see. Woodland is a beautifully chaotic subject, so we'll work on simplifying it into a frame with order and intention, on finding the intimate, close-up detail as readily as the wide woodland view, and on reading the soft spring light and the blue-and-green as a quiet harmony rather than chasing a loud, over-saturated bluebell cliché.It's a small group of no more than six, taught personally and pitched at exactly your level, with easy walks along the bluebell trails and one-to-one guidance throughout. Because bluebells wait for no one, dates flex to the flowering — you'll pick a first-choice date and I'll confirm the peak display nearer the time. You'll come away with a portfolio of atmospheric spring woodland images that feel like the place — and a calmer, more intentional way of seeing colour, light and detail that you can take anywhere.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1721724334692-7KPD0E90A6E4YZMAR324/black+and+white+photography+course+.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/black-and-white-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>photography-courses</t>
+          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9709344", "price": "165.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="I7" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SQ9709344</t>
+          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SQ9709344</t>
+          <t>SQ8599409</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLUEBELL WOODLANDS Photography - Warks - 20 Apr- 30 Apr</t>
+          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bluebell woodlands photography workshop - Choose a sunrise or mid-morning 4hr bluebell photography shoot or both sessions at this private bluebell woodland with exclusive accessSummaryLocation: Warwickshire (Near Stratford Upon Avon)Dates (are subject to the timing of the bluebell flowering and their peek display - you will be contacted nearer the time to consider alt-dates, please pick your initial first date choice but be flexible if nearer the time it needs to change)Tue-20-Apr-27Wed-21-Apr-27Thu-22-Apr-27Fri-23-Apr-27Sat-24-Apr-27Sun-25-Apr-27Mon-26-Apr-27Tue-27-Apr-27Wed-28-Apr-27Thu-29-Apr-27Fri-30-Apr-274hrs - 5:45 am to 9:45 am or 10:30 am to 2:30 pmOR 1 day - 5:45 am to 2:30 pmBrunch between 9:45-10:30 (not included)Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Bluebell WoodsDescription: This Bluebell Woodlands photography workshop gives you exclusive access to a private Warwickshire bluebell wood near Stratford-upon-Avon, open to all levels and any camera. For a few short weeks each spring the woodland floor turns into a sea of blue — and unlike the well-known public bluebell spots, this one is yours to photograph without the crowds, so you can slow right down and work the scene properly in soft woodland light, rather than grabbing the same shot everyone else takes.You choose how you shoot it. Pick a four-hour half-day session — sunrise (5:45am–9:45am) for soft, warm early light, or mid-morning (10:30am–2:30pm) for brighter colour — or book the full day (5:45am–2:30pm) to shoot both, with a brunch break in between (9:45–10:30, not included). Whichever you choose, the technical craft is the floor we build on — composition, depth of field, the settings that hold a carpet of blue in focus — but the real work is learning to see. Woodland is a beautifully chaotic subject, so we'll work on simplifying it into a frame with order and intention, on finding the intimate, close-up detail as readily as the wide woodland view, and on reading the soft spring light and the blue-and-green as a quiet harmony rather than chasing a loud, over-saturated bluebell cliché.It's a small group of no more than six, taught personally and pitched at exactly your level, with easy walks along the bluebell trails and one-to-one guidance throughout. Because bluebells wait for no one, dates flex to the flowering — you'll pick a first-choice date and I'll confirm the peak display nearer the time. You'll come away with a portfolio of atmospheric spring woodland images that feel like the place — and a calmer, more intentional way of seeing colour, light and detail that you can take anywhere.</t>
+          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707309659883-DPISYTNT0T584VPXCK39/bluebell+photography+workshops.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/bluebell-woodlands-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>'- half-day photo work..., - one day photo workshops, Landscape, Woodlands, Flowering</t>
+          <t>photography-services</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SQ8599409, SQ7560082, SQ7443277, SQ8437523, SQ8685603, SQ1561078, SQ1660230, SQ1568285, SQ5411810, SQ5831738, SQ3014350, SQ5312475, SQ1318075, SQ8270632, SQ4260038, SQ6145280, SQ2267773, SQ2428415, SQ6117337, SQ8500857, SQ1516510, SQ1102782, SQ5885147, SQ3102560, SQ1465142, SQ1264314, SQ8706845, SQ7100218, SQ2446216, SQ3086312, SQ1353684, SQ0574386, SQ2004510</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SQ8599409</t>
+          <t>SQ5650040</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Professional Digital DSLR Camera Sensor Clean | Coventry</t>
+          <t>Christmas Photography Seasonal Workshops | Warwickshire</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Get a camera sensor clean in Coventry . Sensor checked and cleaned using professional equipment, swabs | Full Frame and Cropped Sensors | 24hr Turnaround</t>
+          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details: Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495201980-KD6BKH54J01HJR93XXR6/photography-support-Services-1.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1573822266360-1I7REB8B91RNZXW2PNKP/christmas-sparkle-photography-workshop.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/camera-sensor-clean</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/christmas-photography-workshops</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>photography-services</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Urban</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ8119747, SQ6178610</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SQ5650040</t>
+          <t>SQ8119747</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Christmas Photography Seasonal Workshops | Warwickshire</t>
+          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details: Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
+          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details NorthumberlandDescription: This is a 4-day, 3-night residential Northumberland photography workshop along one of the most dramatic coastlines in Britain, open to all levels from beginner to advanced. Northumberland has more castles than any English county — over seventy — and on this coast the great ones meet the sea: Bamburgh rising from its rocky outcrop, Lindisfarne silhouetted against the North Sea, Dunstanburgh ringed by the black boulders of Embleton Beach. It's a coastline made for photographers who want history, drama and big coastal light in one trip.Based on the Northumberland coast, we spend four days chasing the best conditions across its finest locations — Bamburgh, Dunstanburgh, Lindisfarne, Beadnell, Craster and more — and because it's the east coast, you can shoot both sunrise and sunset from the same stretch of shore. The focus is on three things that define great coastal photography here: composing castles and shoreline into a strong frame, mastering long exposure to turn tide and sky into mood, and working the magical light of sunrise and sunset over the Farne Islands and empty beaches. Throughout, the emphasis isn't just on the famous castle view but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition, planned each day around the tides, the light and the forecast, with a detailed location itinerary sent a few days ahead. Across four days you'll shoot empty beaches at first light, iconic castles and long-exposure seascapes — and come away with a portfolio of dramatic Northumbrian coastal images and a real command of long-exposure and coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1573822266360-1I7REB8B91RNZXW2PNKP/christmas-sparkle-photography-workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/eb76126f-7580-40f0-ac80-39b29897cdc7/Northumberland+-+March+2025+-+%2302.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/christmas-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Urban</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>1095</v>
       </c>
       <c r="I10" t="n">
-        <v>125</v>
+        <v>1095</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SQ8119747, SQ6178610</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SQ8119747</t>
+          <t>SQ8540187</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -997,51 +997,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NORTHUMBERLAND Photography Workshops - Mar 18 - 21</t>
+          <t>DARTMOOR Photography Workshop - Landscapes - 2nd - 4th Apr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Exciting 4 day residential Northumberland Landscape Photography Workshops - Coastline Photography visiting the iconic spots on the Northumbrian coastSummaryLocation: Northumberland, LowickDates:Thu 18 Mar, 13:00 - Sun 21st Mar, 13:00 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodNorthumberland Photography Workshops Event Details NorthumberlandDescription: This is a 4-day, 3-night residential Northumberland photography workshop along one of the most dramatic coastlines in Britain, open to all levels from beginner to advanced. Northumberland has more castles than any English county — over seventy — and on this coast the great ones meet the sea: Bamburgh rising from its rocky outcrop, Lindisfarne silhouetted against the North Sea, Dunstanburgh ringed by the black boulders of Embleton Beach. It's a coastline made for photographers who want history, drama and big coastal light in one trip.Based on the Northumberland coast, we spend four days chasing the best conditions across its finest locations — Bamburgh, Dunstanburgh, Lindisfarne, Beadnell, Craster and more — and because it's the east coast, you can shoot both sunrise and sunset from the same stretch of shore. The focus is on three things that define great coastal photography here: composing castles and shoreline into a strong frame, mastering long exposure to turn tide and sky into mood, and working the magical light of sunrise and sunset over the Farne Islands and empty beaches. Throughout, the emphasis isn't just on the famous castle view but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition, planned each day around the tides, the light and the forecast, with a detailed location itinerary sent a few days ahead. Across four days you'll shoot empty beaches at first light, iconic castles and long-exposure seascapes — and come away with a portfolio of dramatic Northumbrian coastal images and a real command of long-exposure and coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 2nd - Sun 4th Apr 2027Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DartmoorDescription: This is a 3-day, 2-night residential landscape photography workshop based around Dartmoor National Park in South Devon, open to all levels from beginner to advanced. Dartmoor is one of England's most atmospheric wild landscapes — a vast sweep of rugged open moor, dramatic granite tors, ancient stunted woodland and serene rivers running through hidden valleys — and across a weekend you'll learn to read and photograph this dramatic terrain in its ever-changing light.Over three days we range across the moor and its woodlands, working a variety of locations as the conditions dictate — from the sculptural granite tors and big moorland vistas to the mossy, otherworldly ancient woods and tumbling rivers. The focus is on three things that make a strong landscape image here: composing order from a wild, expansive scene, controlling exposure and depth of field across big tonal ranges, and timing your shoot to the moods of Dartmoor light, with optional sunrise and sunset shoots and evening picture reviews. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and weather as a harmony rather than chasing the obvious shot. Be prepared for some longer walks over rougher ground — this is a more demanding workshop that takes you to the moor's most rewarding spots.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation, breakfast and evening meals are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of dramatic Dartmoor landscapes — moors, tors and ancient woodland — and the field craft to capture wild country anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/eb76126f-7580-40f0-ac80-39b29897cdc7/Northumberland+-+March+2025+-+%2302.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/coastal-northumberland-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1095</v>
+        <v>875</v>
       </c>
       <c r="I11" t="n">
-        <v>1095</v>
+        <v>875</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SQ8540187</t>
+          <t>SQ5540434</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1053,51 +1053,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DARTMOOR Photography Workshop - Landscapes - 9th - 11th Oct</t>
+          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Join me on this Landscape Dartmoor Photography Workshop - in the iconic woodlands, and landscape of Dartmoor TorsSummaryLocation: Dartmoor - South DevonDates: Fri 9th - Sun 11th Oct 2026Participants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DartmoorDescription: This is a 3-day, 2-night residential landscape photography workshop based around Dartmoor National Park in South Devon, open to all levels from beginner to advanced. Dartmoor is one of England's most atmospheric wild landscapes — a vast sweep of rugged open moor, dramatic granite tors, ancient stunted woodland and serene rivers running through hidden valleys — and across a weekend you'll learn to read and photograph this dramatic terrain in its ever-changing light.Over three days we range across the moor and its woodlands, working a variety of locations as the conditions dictate — from the sculptural granite tors and big moorland vistas to the mossy, otherworldly ancient woods and tumbling rivers. The focus is on three things that make a strong landscape image here: composing order from a wild, expansive scene, controlling exposure and depth of field across big tonal ranges, and timing your shoot to the moods of Dartmoor light, with optional sunrise and sunset shoots and evening picture reviews. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and weather as a harmony rather than chasing the obvious shot. Be prepared for some longer walks over rougher ground — this is a more demanding workshop that takes you to the moor's most rewarding spots.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation, breakfast and evening meals are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of dramatic Dartmoor landscapes — moors, tors and ancient woodland — and the field craft to capture wild country anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DorsetDescription: This is a 3-day, 2-night residential landscape photography workshop along the Jurassic Coast of Dorset, open to all levels from beginner to advanced. Dorset's Purbeck coastline is one of the UK's great seascape locations — a prehistoric, World Heritage shore of sculpted arches, sea stacks and folded cliffs, with the iconic Durdle Door and Lulworth Cove at its heart — and across a weekend you'll learn to photograph it in its best light.Based on the Purbeck coast, we work the area's finest locations — from Durdle Door, Man O'War and Lulworth Cove to Kimmeridge, Dancing Ledge, Mupe Bay and the ghost village of Tyneham. The focus is on three things that make a strong coastal image: composing rock, sea and sky into a balanced frame, using long exposure to turn the moving water into mood, and timing your shoot to the light and the tide. It's never prescriptive though — this varied coastline lends itself to any style, so whether you're drawn to classic seascapes, black and white or abstract, there's scope to follow your own creative vision; throughout, the emphasis is on learning to see, composing with intention and reading light and tone as a harmony rather than chasing the obvious shot. There are optional sunrise and sunset shoots and evenings for relaxed picture reviews.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. B&amp;B accommodation and an evening meal are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Jurassic Coast images and a real command of seascape and long-exposure technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707237329064-99H533NMXCONH5J276LM/dartmoor+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dartmoor-photography-landscape-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>875</v>
+        <v>925</v>
       </c>
       <c r="I12" t="n">
-        <v>875</v>
+        <v>925</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SQ5540434</t>
+          <t>SQ2754105</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1109,22 +1109,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DORSET Landscape Photography Workshop Purbeck 25 - 27 Sep</t>
+          <t>EXMOOR Photography Workshop - Sat 8 - Sun 9 May 2027</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Join me on this 3-day/2-night fantastic Dorset Photography workshop along the Jurassic coastline of Dorset - PurbeckSummary - Dorset Landscape PhotographyLocation: DorsetDates: Fri 2nd - Sun 4th Oct 2026 3 Days/2 Nights(Price includes B&amp;B and evening meal - Half Board)Participants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details DorsetDescription: This is a 3-day, 2-night residential landscape photography workshop along the Jurassic Coast of Dorset, open to all levels from beginner to advanced. Dorset's Purbeck coastline is one of the UK's great seascape locations — a prehistoric, World Heritage shore of sculpted arches, sea stacks and folded cliffs, with the iconic Durdle Door and Lulworth Cove at its heart — and across a weekend you'll learn to photograph it in its best light.Based on the Purbeck coast, we work the area's finest locations — from Durdle Door, Man O'War and Lulworth Cove to Kimmeridge, Dancing Ledge, Mupe Bay and the ghost village of Tyneham. The focus is on three things that make a strong coastal image: composing rock, sea and sky into a balanced frame, using long exposure to turn the moving water into mood, and timing your shoot to the light and the tide. It's never prescriptive though — this varied coastline lends itself to any style, so whether you're drawn to classic seascapes, black and white or abstract, there's scope to follow your own creative vision; throughout, the emphasis is on learning to see, composing with intention and reading light and tone as a harmony rather than chasing the obvious shot. There are optional sunrise and sunset shoots and evenings for relaxed picture reviews.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. B&amp;B accommodation and an evening meal are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Jurassic Coast images and a real command of seascape and long-exposure technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 8 10:30 - Sun 9 May 14:00 2027 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event DetailsLynmouthDescription: This is a 2-day, 1-night residential seascape photography workshop based at Lynmouth on the dramatic Exmoor coast of North Devon, open to all levels from beginner to advanced. Lynmouth is a photographer's paradise — where the East and West Lyn rivers meet the sea beneath towering cliffs, fringed by secluded bays, weathered rock formations and the quaint harbour village with its iconic Rhenish Tower. It's a compact, richly varied coastline that rewards a focused weekend of shooting.Over two days we work the area's finest coastal locations — from the secluded bays and rock formations around Lynmouth and the sweeping Valley of Rocks to Watersmeet, Heddon's Mouth and Porlock Weir. The focus is on three things that make a strong seascape: composing rock, water and sky into a balanced frame, using long exposure to turn the moving sea into mood, and timing your shoot to the light and the tide. Throughout, the emphasis isn't just on the grand view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. The days follow the conditions — full days on location with tuition, an optional sunset shoot, and an optional sunrise, with evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a portfolio of dramatic Exmoor seascapes and the field craft to read light and tide on any coast. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714681245814-0QW8DK4XQ18FM0JLBXYN/Harry+Rocks+%2301+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/dorset-landscape-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1134,26 +1134,26 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>925</v>
+        <v>575</v>
       </c>
       <c r="I13" t="n">
-        <v>925</v>
+        <v>575</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SQ2754105</t>
+          <t>SQ8057321</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1165,78 +1165,78 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXMOOR Photography Workshop - Sat 18 - Sun 19 Jul 2026</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lynmouth - Exmoor Photography Workshop - Join me for this exciting and inspiring trip to explore and capture the stunning coastal landscapes and breathtaking natural beauty of North Devon.SummaryLocation: Lynmouth - ExmoorDates: Sat 18 10:30 - Sun 19 July 14:00 2026 2 Days/1 NightParticipants:Max 4 (1 Car, transport between locations included)Fitness: 1. Easy (5-15 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodExmoor Photography Workshop Event Details LynmouthDescription: This is a 2-day, 1-night residential seascape photography workshop based at Lynmouth on the dramatic Exmoor coast of North Devon, open to all levels from beginner to advanced. Lynmouth is a photographer's paradise — where the East and West Lyn rivers meet the sea beneath towering cliffs, fringed by secluded bays, weathered rock formations and the quaint harbour village with its iconic Rhenish Tower. It's a compact, richly varied coastline that rewards a focused weekend of shooting.Over two days we work the area's finest coastal locations — from the secluded bays and rock formations around Lynmouth and the sweeping Valley of Rocks to Watersmeet, Heddon's Mouth and Porlock Weir. The focus is on three things that make a strong seascape: composing rock, water and sky into a balanced frame, using long exposure to turn the moving sea into mood, and timing your shoot to the light and the tide. Throughout, the emphasis isn't just on the grand view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. The days follow the conditions — full days on location with tuition, an optional sunset shoot, and an optional sunrise, with evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a portfolio of dramatic Exmoor seascapes and the field craft to read light and tide on any coast. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714638630127-79B9OMJPFF60L8Q9VLJL/Timeless+Memories.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/exmoor-photography-workshops-lynmouth</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>575</v>
+        <v>135.95</v>
       </c>
       <c r="I14" t="n">
-        <v>575</v>
+        <v>459.95</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SQ8057321</t>
+          <t>SQ0105911</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round - Multi Size</t>
+          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Canvas wrap-round creates a contemporary finish to your photo- available in seven sizes. Include in the image title when ordering</t>
+          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1572426141642-UH9GBUDOUFH8QMTUA0KA/cavas%2Bsizes.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-canvas</t>
+          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1246,26 +1246,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>135.95</v>
+        <v>50.57</v>
       </c>
       <c r="I15" t="n">
-        <v>459.95</v>
+        <v>416.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SQ0105911, SQ4206024, SQ0781804, SQ3982814, SQ8209269, SQ7901040, SQ7260825</t>
+          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SQ0105911</t>
+          <t>SQ4872440</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1277,163 +1277,163 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Unframed Prints - Multi Sizes</t>
+          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints available in seven sizes. Giclee print on archival paper. Please include in the image title when ordering | Pro-Lab Printing</t>
+          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: This Fireworks Photography Workshop is a one-off evening capturing one of the most exciting subjects in photography — a full fireworks display bursting over the floodlit ruins of Kenilworth Castle. Open to all levels and any camera, it's built around the Round Table's spectacular annual display, and the magical, fleeting moment when long exposure turns streaking light and exploding colour into a single dramatic image with the castle as its backdrop.Fireworks look chaotic but reward a calm, technical approach, and that's exactly what we'll work on. The focus is on three things that make the difference between a lucky snap and a controlled image: setting up for long exposure — shutter, aperture and the timing that lets you build a burst on the sensor — composing the frame so the castle and the sky work together rather than fighting, and reading the rhythm of the display to know when to open and close the shutter. You'll learn to anticipate rather than react, and to keep shooting cleanly when the sky is at its busiest.It's a small group of no more than four, taught personally and right beside you in the dark, so you get real one-to-one guidance exactly when the action is happening. Better still, we photograph from outside the castle walls, so there's no admission ticket to buy for the display. You'll come away with a set of dramatic fireworks images over a historic castle — and the long-exposure and timing skills to photograph fireworks, light trails and night scenes anywhere. (Please note this is an annual event with the date set by the organisers, so timing is confirmed each year nearer the display.)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240002916-MMJ7CA3MX9HLO60532BO/fine+art+photography+prints.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/fine-art-photography-prints-unframed</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>50.57</v>
+        <v>75</v>
       </c>
       <c r="I16" t="n">
-        <v>416.85</v>
+        <v>75</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SQ4872440, SQ0453600, SQ7485354, SQ0167262, SQ1664775, SQ0377820, SQ8780582</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SQ4872440</t>
+          <t>SQ1182401</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop | Long Exposure | Kenilworth</t>
+          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fireworks Photography Workshop - Long exposure and fireworks. Learn about camera settings, exposure use and composition.SummaryLocation: KenilworthDates: TBCParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: FireworksDescription: This Fireworks Photography Workshop is a one-off evening capturing one of the most exciting subjects in photography — a full fireworks display bursting over the floodlit ruins of Kenilworth Castle. Open to all levels and any camera, it's built around the Round Table's spectacular annual display, and the magical, fleeting moment when long exposure turns streaking light and exploding colour into a single dramatic image with the castle as its backdrop.Fireworks look chaotic but reward a calm, technical approach, and that's exactly what we'll work on. The focus is on three things that make the difference between a lucky snap and a controlled image: setting up for long exposure — shutter, aperture and the timing that lets you build a burst on the sensor — composing the frame so the castle and the sky work together rather than fighting, and reading the rhythm of the display to know when to open and close the shutter. You'll learn to anticipate rather than react, and to keep shooting cleanly when the sky is at its busiest.It's a small group of no more than four, taught personally and right beside you in the dark, so you get real one-to-one guidance exactly when the action is happening. Better still, we photograph from outside the castle walls, so there's no admission ticket to buy for the display. You'll come away with a set of dramatic fireworks images over a historic castle — and the long-exposure and timing skills to photograph fireworks, light trails and night scenes anywhere. (Please note this is an annual event with the date set by the organisers, so timing is confirmed each year nearer the display.)</t>
+          <t>4 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 4 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1713518270092-GJSBASA0ZLL4NBMCK355/Kenilworth+Fireworks+2017+-+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/17054018-4804-4c2d-ad29-c57cba809028/face+to+face+private+photography+classes.png</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/fireworks-photography-workshop-kenilworth</t>
+          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="I17" t="n">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SQ1182401</t>
+          <t>SQ6583676</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4 x 2hr Private Photography Classes - Face to Face Coventry</t>
+          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4 × 2hr Private Photography Classes (Face to Face, Coventry)Summary - Private Photography Classes (Face to Face) - Key InformationLocation: Coventry (face to face)Format: Private 1-2-1 tuition, in personSessions: 4 × 2hr classes, scheduled to suit youAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — you'll be sent a code to book your datesLevel: All levels, beginner to advancedDescription: A package of four private, face-to-face photography classes in Coventry — two hours each, tailored entirely to you and what you want to learn or improve.</t>
+          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1522495550918-139R34YFWLG3Q89CXENT/PRIVATE-PHOTOGRAPHY-LESSONS.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/four-private-photography-classes</t>
+          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition, photography-courses</t>
+          <t>print</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>360</v>
+        <v>133.85</v>
       </c>
       <c r="I18" t="n">
-        <v>360</v>
+        <v>356.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SQ6583676</t>
+          <t>SQ6825544</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1445,219 +1445,219 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Framed Fine Art Photography Prints - Multiple Sizes</t>
+          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fine Art Photography Prints - Giclee Framed Prints available in four sizes. Black frame with white mount. Please include in the image title when ordering</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates: DatesSun Jul 12th 2026 - 15:00 - 17:00Sun May 23rd 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707240165500-DB965TUR2FYMNEFPXS90/fine+art+photography+prints+-+framed.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/framed-fine-art-photography-prints</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun Jul 12 2026 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>133.85</v>
+        <v>45</v>
       </c>
       <c r="I19" t="n">
-        <v>356.9</v>
+        <v>45</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SQ6825544, SQ3786581, SQ1355351, SQ0156134</t>
+          <t>SQ3644687, SQ0939451</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SQ6825544</t>
+          <t>SQ3644687</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>The Art of GARDEN PHOTOGRAPHY  - Coventry -  May and July</t>
+          <t>Intermediates Intentions Photography Project Course</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates: DatesSun Jul 12th 2026 - 15:00 - 17:00Sun May 23rd 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
+          <t>Six-month photography project and showcase your images in a public exhibition in WarwickshireLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 6-month project, 6 classesParticipants: Max 4Level: IntermediateDescription: Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire — a course designed to develop your intentions, vision and a coherent body of work.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709974516534-UJBRDOK5RXR4QNLPTECD/_-677.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>photography-classes, photography-courses</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun Jul 12 2026 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>45</v>
+        <v>400</v>
       </c>
       <c r="I20" t="n">
-        <v>45</v>
+        <v>400</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SQ3644687, SQ0939451</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SQ3644687</t>
+          <t>SQ9898707</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Intermediates Intentions Photography Project Course</t>
+          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Six-month photography project and showcase your images in a public exhibition in WarwickshireLocation: 45 Hathaway Road, Tile Hill Village, Coventry, CV4 9HWDuration: 6-month project, 6 classesParticipants: Max 4Level: IntermediateDescription: Embark on a six-month photography project and showcase your images in a public exhibition in Warwickshire — a course designed to develop your intentions, vision and a coherent body of work.Equipment: A DSLR or mirrorless camera with manual exposure modes.</t>
+          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: This is a 5-day, 4-night residential photography workshop in the south-west of Ireland — the longest and most immersive trip I run, based around Dingle and exploring some of the most beautiful country in Europe. Open to all levels and any camera, it takes in three extraordinary areas of County Kerry: the wild, sea-battered Dingle Peninsula, the dramatic coastline of South Kerry along the Skellig Ring, and the mountains, lakes and ancient woodland of Killarney National Park.The variety here is the gift and the challenge — mountains, lakes, waterfalls, woodland, coastline and rock formations, often within a single day — and five days gives us the time to do it justice. We'll cover the technical control you need, but the real focus is on learning to see: composing order and intention out of these vast, busy scenes, working close-up and intimate detail as readily as the grand vista, and reading light, weather and tide as a harmony rather than chasing the obvious postcard shot. Some stops are quick laybys to catch a fleeting moment; others we'll work slowly, waiting for the light and water to come good.With a maximum of just four photographers and five full days on the ground, this is genuinely personal tuition with the time to slow down and work properly — Alan plans each day around the season, the forecast and the tides, and sends a detailed itinerary ahead. You'll come away not just with a portfolio from one of Europe's great landscapes, but with a stronger way of seeing — light, composition and restraint — that will change how you photograph wherever you go next. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707220703945-94B0SK8PWUMOS78FTJMO/photography+project+-+intentions+photography+course.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/intermediates-intentions-photography-project-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>400</v>
+        <v>1595</v>
       </c>
       <c r="I21" t="n">
-        <v>400</v>
+        <v>1595</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SQ9898707</t>
+          <t>SQ7419716</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KERRY - Southern Ireland Photography Workshop - Mar 2026</t>
+          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Photograph amazing areas in South Kerry, Dingle, and Killarney National Park on this 5-day Ireland photography workshopSummaryLocation: Dingle and Killarney - Kerry Southern IrelandDates: Thu 5th - Mon 10th Mar 2026 - 5 Days/4 NightsParticipants: Max 4Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: DingleDescription: This is a 5-day, 4-night residential photography workshop in the south-west of Ireland — the longest and most immersive trip I run, based around Dingle and exploring some of the most beautiful country in Europe. Open to all levels and any camera, it takes in three extraordinary areas of County Kerry: the wild, sea-battered Dingle Peninsula, the dramatic coastline of South Kerry along the Skellig Ring, and the mountains, lakes and ancient woodland of Killarney National Park.The variety here is the gift and the challenge — mountains, lakes, waterfalls, woodland, coastline and rock formations, often within a single day — and five days gives us the time to do it justice. We'll cover the technical control you need, but the real focus is on learning to see: composing order and intention out of these vast, busy scenes, working close-up and intimate detail as readily as the grand vista, and reading light, weather and tide as a harmony rather than chasing the obvious postcard shot. Some stops are quick laybys to catch a fleeting moment; others we'll work slowly, waiting for the light and water to come good.With a maximum of just four photographers and five full days on the ground, this is genuinely personal tuition with the time to slow down and work properly — Alan plans each day around the season, the forecast and the tides, and sends a detailed itinerary ahead. You'll come away not just with a portfolio from one of Europe's great landscapes, but with a stronger way of seeing — light, composition and restraint — that will change how you photograph wherever you go next. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Lake DistrictDescription: This is a 3-day, 2-night residential Lake District photography workshop, based in the north lakes and open to all levels from beginner to advanced. The Lake District has been a favourite of landscape photographers for decades, and for good reason: nowhere else in England packs in such variety — mountains, tarns, ancient woodland, waterfalls and reflective lakes — and the changeable Cumbrian weather means it's never the same place twice. Misty mornings, atmospheric light, stormy skies and quiet reflections can all arrive within a single weekend.Over three days we shoot the iconic scenes at their best, basing ourselves in the north lakes and working two to three carefully chosen locations a day — from Derwent Water, Castlerigg and Ashness Bridge to the tarns and valleys of Langdale, Coniston and Buttermere. The rhythm follows the light: optional sunrise shoots, full days on location with tuition in the field, and optional sunset sessions, with evenings for relaxed picture reviews over a meal. Throughout, the emphasis isn't just on being at the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot. You'll come away with a portfolio of dramatic Lakeland images and the field craft to read light and weather anywhere.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the group, the season and the forecast, sends a detailed location itinerary a few days ahead, and adapts on the ground to chase the best conditions. Accommodation and breakfast are included, so you can switch off from the logistics and focus entirely on your photography for three days. Extra night B&amp;B available for Thursday — contact me for details and booking separately.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1710060195646-WLFJL2H358FJD4GKV1CP/Coumeenoole+Strand+2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/ireland-photography-workshops-dingle</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>1595</v>
+        <v>975</v>
       </c>
       <c r="I22" t="n">
-        <v>1595</v>
+        <v>1125</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SQ7419716</t>
+          <t>SQ9100538</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1669,51 +1669,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAKE DISTRICT Photography Workshops - Jan - Mar - Sep - Nov</t>
+          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>An exciting 3 day/2 night residential lake district photography workshop visiting some gorgeous spots around Cumbria. Runs every Jan, Mar, Sep, NovSummaryLocation: Cumbria - Lake DistrictDates:Fri 18 Sep - Sun 20 Sep - 3 Days/2 Nights 2026Fri 13 Nov - Sun 15 Nov - 3 Days/2 Nights 2026Fri 22 Jan - Sun 24 Jan - 3 Days/2 Nights 2027Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027Extra night B&amp;B available for Thu - Contact me for details and booking separatelyParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Lake DistrictDescription: This is a 3-day, 2-night residential Lake District photography workshop, based in the north lakes and open to all levels from beginner to advanced. The Lake District has been a favourite of landscape photographers for decades, and for good reason: nowhere else in England packs in such variety — mountains, tarns, ancient woodland, waterfalls and reflective lakes — and the changeable Cumbrian weather means it's never the same place twice. Misty mornings, atmospheric light, stormy skies and quiet reflections can all arrive within a single weekend.Over three days we shoot the iconic scenes at their best, basing ourselves in the north lakes and working two to three carefully chosen locations a day — from Derwent Water, Castlerigg and Ashness Bridge to the tarns and valleys of Langdale, Coniston and Buttermere. The rhythm follows the light: optional sunrise shoots, full days on location with tuition in the field, and optional sunset sessions, with evenings for relaxed picture reviews over a meal. Throughout, the emphasis isn't just on being at the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the grand vista, and reading light and weather as a harmony rather than chasing the obvious shot. You'll come away with a portfolio of dramatic Lakeland images and the field craft to read light and weather anywhere.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the group, the season and the forecast, sends a detailed location itinerary a few days ahead, and adapts on the ground to chase the best conditions. Accommodation and breakfast are included, so you can switch off from the logistics and focus entirely on your photography for three days. Extra night B&amp;B available for Thursday — contact me for details and booking separately.</t>
+          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Sat 22nd May 2027 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: This Peak District photography workshop is a full day in the heart of Derbyshire's Hope Valley, open to all levels from beginner to advanced. It's built around two of the area's most rewarding and contrasting locations — the wooded, water-filled drama of Padley Gorge in the morning and the rugged, sculptural landscape of Bolehill Quarry in the afternoon — so in a single day you photograph two completely different faces of the Peak District, and learn to read each one rather than just point a camera at it.The morning at Padley Gorge — a deep, tree-lined valley with the Burbage Brook tumbling through it — is all about slowing down and seeing: simplifying a busy woodland scene into intimate close-ups of rock, moss and water, finding the quiet order in the chaos, and using long exposure to draw movement out of the brook. The afternoon at Bolehill Quarry opens out to the heights of Millstone Edge and silver birch woodland, where the work shifts to composing the bigger landscape. Across both, the technical craft is the floor we build on — exposure, depth of field, the settings that give you control — but the real lesson is learning to see: composing with intention, working close-up detail as readily as the wide vista, and reading light, texture and colour as a harmony rather than chasing the loud, obvious shot.We meet at the Grindleford Railway Café, where you can grab an optional pre-shoot breakfast before we head into the gorge. Lunch is back at the café halfway through — buy on the day or bring your own — before a short drive over to Bolehill for the afternoon session. Taught personally in a small group, this is hands-on, on-location tuition pitched at exactly your level, with Alan beside you in the field throughout; a detailed itinerary is sent a few days ahead, adjusted for the season and forecast, so you'll come away with a varied portfolio of Peak District images and a sharper, more intentional way of seeing landscape anywhere.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714301696717-TME057MTL131H9UHU82H/Bassenthwaite+Rise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/lake-district-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>975</v>
+        <v>150</v>
       </c>
       <c r="I23" t="n">
-        <v>1125</v>
+        <v>150</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SQ9100538, SQ5158309, SQ9016326, SQ0142956</t>
+          <t>SQ3794821, SQ8457424, SQ9037810, SQ2363666</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SQ9100538</t>
+          <t>SQ3794821</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1725,51 +1725,51 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT Photography Workshops - May, Oct and Nov</t>
+          <t>Landscape Photography DEVON Workshops - Various Dates</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Join me in the Peak District in Hope Valley. Padley Gorge and Bolehill Quarry throughout the year on Peak District photography workshops | All levels welcomeSummaryLocation: Peak District - DerbyshireDates: Sat 17th Oct 2026 - 09:30 - 16:00Sun 1st Nov 2026 - 09:30 - 16:00Sat 7th Nov 2026 - 09:30 - 16:00Sat 22nd May 2027 - 09:30 - 16:00Participants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Padley Gorge And Bolehill QuarryDescription: This Peak District photography workshop is a full day in the heart of Derbyshire's Hope Valley, open to all levels from beginner to advanced. It's built around two of the area's most rewarding and contrasting locations — the wooded, water-filled drama of Padley Gorge in the morning and the rugged, sculptural landscape of Bolehill Quarry in the afternoon — so in a single day you photograph two completely different faces of the Peak District, and learn to read each one rather than just point a camera at it.The morning at Padley Gorge — a deep, tree-lined valley with the Burbage Brook tumbling through it — is all about slowing down and seeing: simplifying a busy woodland scene into intimate close-ups of rock, moss and water, finding the quiet order in the chaos, and using long exposure to draw movement out of the brook. The afternoon at Bolehill Quarry opens out to the heights of Millstone Edge and silver birch woodland, where the work shifts to composing the bigger landscape. Across both, the technical craft is the floor we build on — exposure, depth of field, the settings that give you control — but the real lesson is learning to see: composing with intention, working close-up detail as readily as the wide vista, and reading light, texture and colour as a harmony rather than chasing the loud, obvious shot.We meet at the Grindleford Railway Café, where you can grab an optional pre-shoot breakfast before we head into the gorge. Lunch is back at the café halfway through — buy on the day or bring your own — before a short drive over to Bolehill for the afternoon session. Taught personally in a small group, this is hands-on, on-location tuition pitched at exactly your level, with Alan beside you in the field throughout; a detailed itinerary is sent a few days ahead, adjusted for the season and forecast, so you'll come away with a varied portfolio of Peak District images and a sharper, more intentional way of seeing landscape anywhere.</t>
+          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsThu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND Filters (tripod and filters can be provided)Photography Workshop Event Details DevonDescription: This is a multi-day residential landscape photography workshop based at Hartland Quay on the dramatic North Devon coast, open to all levels from beginner to advanced. Hartland Quay is one of the UK's most spectacular seascape locations — long slithers of rock formations running out into a fierce Atlantic tide — and it's the perfect base for learning seascape photography on a coastline that rewards drama, patience and timing.Across the workshop you'll photograph the classic Hartland Quay views and range out along some of the finest coast in the South West — from Bude and Clovelly to Welcombe Bay, Saunton Sands and Woolacombe. The focus is on the craft of seascape photography: composing a strong coastal frame, mastering long exposure to turn moving water and sky into mood, and timing your shoot to the light and the tide. But the technical side is only the floor — the real work is learning to see, composing with intention and reading light and tide as a harmony rather than chasing the obvious shot, working the intimate detail as readily as the grand vista. Each day follows that rhythm — optional sunrise and sunset shoots when the light is best, full days in the field with tuition, and evening photo reviews and editing sessions to sharpen your eye.With a maximum of just four photographers, this is genuinely personal tuition, and because the whole coast is tide- and light-dependent, Alan plans each day around the forecast and sends a detailed location itinerary a few days ahead. Tripods and ND filters can be lent if you don't yet own them, accommodation and breakfast are included, and you'll come away with a portfolio of dramatic Devon seascapes and a real command of long-exposure coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1709626967694-M4DJSC9GYR1R1LZFYBUF/Padley+Gorge+%2304+-+Mar+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-peak-district-photography-workshops-derbyshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Landscape, Woodlands</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}, {"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 Nights"}]</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>150</v>
+        <v>775</v>
       </c>
       <c r="I24" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SQ3794821, SQ8457424, SQ9037810, SQ2363666</t>
+          <t>SQ2516659, SQ3856406</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SQ3794821</t>
+          <t>SQ2516659</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1781,51 +1781,51 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Landscape Photography DEVON Workshops - Various Dates</t>
+          <t>Landscape Photography SNOWDONIA - Sat 26 - Sun 27 Sep 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hartland Quay - Landscape Photography Devon Workshop - Join me for this photo workshop to the best coastal and dramatic parts of Devon.SummaryLocation: North Devon - Hartland QuayDates:Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 NightsThu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 NightsParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera, Tripod and ND Filters (tripod and filters can be provided)Photography Workshop Event Details DevonDescription: This is a multi-day residential landscape photography workshop based at Hartland Quay on the dramatic North Devon coast, open to all levels from beginner to advanced. Hartland Quay is one of the UK's most spectacular seascape locations — long slithers of rock formations running out into a fierce Atlantic tide — and it's the perfect base for learning seascape photography on a coastline that rewards drama, patience and timing.Across the workshop you'll photograph the classic Hartland Quay views and range out along some of the finest coast in the South West — from Bude and Clovelly to Welcombe Bay, Saunton Sands and Woolacombe. The focus is on the craft of seascape photography: composing a strong coastal frame, mastering long exposure to turn moving water and sky into mood, and timing your shoot to the light and the tide. But the technical side is only the floor — the real work is learning to see, composing with intention and reading light and tide as a harmony rather than chasing the obvious shot, working the intimate detail as readily as the grand vista. Each day follows that rhythm — optional sunrise and sunset shoots when the light is best, full days in the field with tuition, and evening photo reviews and editing sessions to sharpen your eye.With a maximum of just four photographers, this is genuinely personal tuition, and because the whole coast is tide- and light-dependent, Alan plans each day around the forecast and sends a detailed location itinerary a few days ahead. Tripods and ND filters can be lent if you don't yet own them, accommodation and breakfast are included, and you'll come away with a portfolio of dramatic Devon seascapes and a real command of long-exposure coastal technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SnowdoniaDescription: This is a 2-day, 1-night residential landscape photography workshop in Snowdonia National Park, North Wales — open to all levels from beginner to advanced. Home to the highest mountain ranges in England and Wales, Snowdonia is a landscape that will both inspire and challenge any photographer: rugged peaks and flowing rivers, serene lakes and ancient slate quarries, all within a compact corner of Wales that you'll learn to read and photograph in its ever-changing light.What makes Snowdonia so rewarding is its variety, and over two days we work three very different faces of it: the waterfalls and rivers that are perfect for long exposure, turning moving water to silk; the starker, striking world of the historic slate quarries and mining relics, where industry and mountain meet; and the majestic lakes, where still water mirrors the peaks for compelling, reflective compositions. Across all of it the focus stays on the same craft — composing order from a vast scene, controlling exposure across big tonal ranges, and timing your shoot to the light and weather that shift the mood from rugged to serene and back. And throughout, the emphasis isn't just on the grand vista but on learning to see it — working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers and transport between locations included, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Likely locations include the reflective waters of Llynnau Mymbyr beneath the Snowdon massif, the Capel Curig pinnacles, Swallow Falls and the hidden lake of Llyn Craftnant. Accommodation and breakfast are included, so all you have to think about is your photography — and you'll leave with a varied portfolio that captures both the drama and the stillness of this remarkable landscape. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714299365471-K36RWNIKFNGJ4C70UEXB/Atlantic+Force.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-devon-hartland-quay</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2516659", "price": "775.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 4th Sep - Sun 6th Sep 2026 - 3 Days/2 Nights"}, {"@type": "Offer", "sku": "SQ3856406", "price": "950.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Thu 18th 12:30 - Sun 21st 12:30 Feb 2027 - 4 Days/3 Nights"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>775</v>
+        <v>595</v>
       </c>
       <c r="I25" t="n">
-        <v>950</v>
+        <v>595</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SQ2516659, SQ3856406</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SQ2516659</t>
+          <t>SQ0548499</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1837,51 +1837,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Landscape Photography SNOWDONIA - Sat 26 - Sun 27 Sep 2026</t>
+          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Join me on this landscape photography Snowdonia workshop in the iconic mountains, quarries and landscape of Snowdonia national park.Summary - Snowdonia Landscape photography workshopLocation:Wales - Snowdonia National ParkDates: Sat 26th - Sun 27th Sep 2026 - 2 Days/1 NightParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SnowdoniaDescription: This is a 2-day, 1-night residential landscape photography workshop in Snowdonia National Park, North Wales — open to all levels from beginner to advanced. Home to the highest mountain ranges in England and Wales, Snowdonia is a landscape that will both inspire and challenge any photographer: rugged peaks and flowing rivers, serene lakes and ancient slate quarries, all within a compact corner of Wales that you'll learn to read and photograph in its ever-changing light.What makes Snowdonia so rewarding is its variety, and over two days we work three very different faces of it: the waterfalls and rivers that are perfect for long exposure, turning moving water to silk; the starker, striking world of the historic slate quarries and mining relics, where industry and mountain meet; and the majestic lakes, where still water mirrors the peaks for compelling, reflective compositions. Across all of it the focus stays on the same craft — composing order from a vast scene, controlling exposure across big tonal ranges, and timing your shoot to the light and weather that shift the mood from rugged to serene and back. And throughout, the emphasis isn't just on the grand vista but on learning to see it — working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers and transport between locations included, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Likely locations include the reflective waters of Llynnau Mymbyr beneath the Snowdon massif, the Capel Curig pinnacles, Swallow Falls and the hidden lake of Llyn Craftnant. Accommodation and breakfast are included, so all you have to think about is your photography — and you'll leave with a varied portfolio that captures both the drama and the stillness of this remarkable landscape. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details GowerDescription: This is a 3-day, 2-night residential landscape photography workshop on the Gower Peninsula in South Wales — the UK's very first Area of Outstanding Natural Beauty, and one of the finest stretches of coast for landscape photography in Wales. Open to all levels from beginner to advanced, it takes you along 19 miles of dramatic shoreline west of Swansea, where lofty limestone cliffs, golden sandy beaches and jagged rocky shores meet wild moorland, dunes and tranquil salt marshes.Over three days we work the peninsula's most iconic locations as the light and tides allow — from the sweeping expanse of Rhossili Bay and the dramatic outline of Worms Head to the wreck of the Helvetia and the snug cove of Pwll Du. The focus is on three things that make a strong coastal image: composing cliffs, beaches and rock forms into a balanced frame, mastering long exposure to draw movement out of sea and sky, and timing each shoot from dawn to dusk to catch the best light and tide. Throughout, the emphasis isn't just on the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and colour as a harmony rather than chasing the obvious shot. You'll photograph at sunrise and sunset, the richest hours on this coast, and return to locations in changing conditions to capture them at their best.With a small group taught personally, this is genuinely one-to-one tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Be prepared for some longer walks over cliff paths and rougher coastal ground to reach the best viewpoints. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Gower's iconic Welsh coastline — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1711625824431-22D7V1RNKR8H2LBRW4Z9/Snowdonia+%2301+-+Oct+2023.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-snowdonia-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Landscape, - weekend residential photo workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0548499", "price": "595.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>595</v>
+        <v>825</v>
       </c>
       <c r="I26" t="n">
-        <v>595</v>
+        <v>825</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SQ0548499</t>
+          <t>SQ5141863</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1893,22 +1893,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GOWER Landscape Photography Wales - 28 Aug - 30 Aug 2026</t>
+          <t>Landscape Photography Workshop NORFOLK - Coastal 20 - 22 Nov</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stunning shorelines and beauty of South Wales and the Gower Peninsular. Max 3 places for this residential photography workshop - landscape photography walesSummaryLocation: South Wales - Gower PeninsularDates:Fri 28th Aug - Sun 30th Aug 2026 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. HardExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodLandscape photography Wales Photography Workshop Event Details GowerDescription: This is a 3-day, 2-night residential landscape photography workshop on the Gower Peninsula in South Wales — the UK's very first Area of Outstanding Natural Beauty, and one of the finest stretches of coast for landscape photography in Wales. Open to all levels from beginner to advanced, it takes you along 19 miles of dramatic shoreline west of Swansea, where lofty limestone cliffs, golden sandy beaches and jagged rocky shores meet wild moorland, dunes and tranquil salt marshes.Over three days we work the peninsula's most iconic locations as the light and tides allow — from the sweeping expanse of Rhossili Bay and the dramatic outline of Worms Head to the wreck of the Helvetia and the snug cove of Pwll Du. The focus is on three things that make a strong coastal image: composing cliffs, beaches and rock forms into a balanced frame, mastering long exposure to draw movement out of sea and sky, and timing each shoot from dawn to dusk to catch the best light and tide. Throughout, the emphasis isn't just on the famous viewpoint but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and colour as a harmony rather than chasing the obvious shot. You'll photograph at sunrise and sunset, the richest hours on this coast, and return to locations in changing conditions to capture them at their best.With a small group taught personally, this is genuinely one-to-one tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Be prepared for some longer walks over cliff paths and rougher coastal ground to reach the best viewpoints. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Gower's iconic Welsh coastline — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: This is a 3-day, 2-night residential landscape photography workshop on the beautiful North Norfolk coast, based near Cromer — open to all levels from beginner to advanced. North Norfolk is one of the most varied and atmospheric stretches of coastline in England, and across a long weekend you'll photograph everything from classic seafronts and groynes to wild estuaries, windmills and big skies, learning to read and capture this ever-changing coastal landscape in its best light.There really is something for everyone here, and over three days we work a rich variety of locations as the light and tides allow — the seafronts and groynes at Overstrand and Cromer, the atmospheric estuaries of Morston Quay and Blakeney Harbour with their abandoned boats and twisting creeks, and the beach huts, windmills, sand dunes and flint-cottage charm of Blakeney village. The focus is on three things that make a strong coastal image: composing order from busy, expansive scenes, mastering long exposure to draw movement out of sea, sky and water, and timing each shoot to the tides and the soft coastal light. There's even an optional boat trip to see the seals along the way.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the North Norfolk coast — seascapes, estuaries, windmills and beach huts — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715702409761-590M3MJ45KYXBDH1KSM0/Gower+%2305+-+May+2024.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e301c931-8fdc-4ff0-bc78-618aea6241a1/Norfolk+Nov+2024+-+%2303.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-wales-photo-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1918,26 +1918,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5141863", "price": "825.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="I27" t="n">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SQ5141863</t>
+          <t>SQ8747213</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1949,51 +1949,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop NORFOLK - Coastal 20 - 22 Nov</t>
+          <t>ANGLESEY Landscape Photography Workshop -  May 2027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Landscape Photography Workshop Norfolk - Coastal Photography Based Nr CromerSummary - Norfolk Photography WorkshopLocation: North Norfolk Coast - Cromer AreaDates: Fri 20th, 09:30am - Sun 22nd Nov 2026, 14:00 - 3 Days/2 NightsParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: NorfolkDescription: This is a 3-day, 2-night residential landscape photography workshop on the beautiful North Norfolk coast, based near Cromer — open to all levels from beginner to advanced. North Norfolk is one of the most varied and atmospheric stretches of coastline in England, and across a long weekend you'll photograph everything from classic seafronts and groynes to wild estuaries, windmills and big skies, learning to read and capture this ever-changing coastal landscape in its best light.There really is something for everyone here, and over three days we work a rich variety of locations as the light and tides allow — the seafronts and groynes at Overstrand and Cromer, the atmospheric estuaries of Morston Quay and Blakeney Harbour with their abandoned boats and twisting creeks, and the beach huts, windmills, sand dunes and flint-cottage charm of Blakeney village. The focus is on three things that make a strong coastal image: composing order from busy, expansive scenes, mastering long exposure to draw movement out of sea, sky and water, and timing each shoot to the tides and the soft coastal light. There's even an optional boat trip to see the seals along the way.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the North Norfolk coast — seascapes, estuaries, windmills and beach huts — and the field craft to read light, tide and weather on any shore. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Anglesey PhotographyDescription: This is a 3-day, 2-night residential landscape photography workshop on the iconic island of Anglesey, off the north-west coast of Wales, open to all levels from beginner to advanced. Anglesey's coastline is a photographer's dream — over 200 square miles ringed by sandy coves, working harbours, rocky headlands and three iconic lighthouses — and across a weekend you'll shoot it in the golden hours when its colour, light and sea views are at their most spectacular.We work the island's finest coastal locations — from Penmon Point's Trwyn Du Lighthouse and the Church in the Sea to South Stack, Llanddwyn Island and the strange, Martian-coloured landscape of Parys Mountain, once the world's largest copper mine. The focus is on three things that make a strong coastal landscape: composing sea, shore and sky into a balanced frame, working the golden-hour light at sunrise and sunset, and using long exposure to capture the movement of the Welsh sea. Throughout, the emphasis isn't just on the iconic view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading colour and light as a harmony rather than chasing the obvious shot. The days follow the light — optional sunrise and sunset shoots, full days on location with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Anglesey coastal images and the field craft to read light and sea anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/e301c931-8fdc-4ff0-bc78-618aea6241a1/Norfolk+Nov+2024+-+%2303.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshop-norfolk</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>coastal, Landscape, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8747213", "price": "1025.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "1025.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1025</v>
+        <v>975</v>
       </c>
       <c r="I28" t="n">
-        <v>1025</v>
+        <v>975</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SQ8747213</t>
+          <t>SQ8503376</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2005,51 +2005,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ANGLESEY Landscape Photography Workshop -  May 2027</t>
+          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 7 Jun</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Join me for this exciting Anglesey landscape photography workshop, where we will shoot along the stunning coastline features to capture breathtaking vistas that showcase the natural beauty surrounding the shorelines and iconic lighthouses.Summary - Anglesey Photography WorkshopLocation: Wales - Anglesey IslandDates: Fri 14th May 15:00 - Sun 16th May 14:00, 2027Duration: 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Anglesey PhotographyDescription: This is a 3-day, 2-night residential landscape photography workshop on the iconic island of Anglesey, off the north-west coast of Wales, open to all levels from beginner to advanced. Anglesey's coastline is a photographer's dream — over 200 square miles ringed by sandy coves, working harbours, rocky headlands and three iconic lighthouses — and across a weekend you'll shoot it in the golden hours when its colour, light and sea views are at their most spectacular.We work the island's finest coastal locations — from Penmon Point's Trwyn Du Lighthouse and the Church in the Sea to South Stack, Llanddwyn Island and the strange, Martian-coloured landscape of Parys Mountain, once the world's largest copper mine. The focus is on three things that make a strong coastal landscape: composing sea, shore and sky into a balanced frame, working the golden-hour light at sunrise and sunset, and using long exposure to capture the movement of the Welsh sea. Throughout, the emphasis isn't just on the iconic view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading colour and light as a harmony rather than chasing the obvious shot. The days follow the light — optional sunrise and sunset shoots, full days on location with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the tides, the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about for three days is your photography, and you'll come away with a portfolio of dramatic Anglesey coastal images and the field craft to read light and sea anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: This Nant Mill long exposure photography workshop takes you into a secluded Welsh valley near Wrexham, where a river and its waterfalls tumble through enchanting ancient woodland — open to all levels and any camera. Flowing water in a quiet, leafy gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this beautiful, tucked-away place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working the river, falls and woodland together, you'll learn to find order among the rocks, water and trees, to compose the intimate, close-up detail as readily as the wider valley view, and to read the soft, dappled light and the natural greens and browns of this ancient wood as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels the way the place actually feels.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of North Wales' hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707225841274-TEMCPAEP5DHDVCBJP2RD/anglesey+photography+workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-anglesey</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>coastal, Landscape, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8503376", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>975</v>
+        <v>125</v>
       </c>
       <c r="I29" t="n">
-        <v>975</v>
+        <v>125</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SQ8503376</t>
+          <t>SQ4568959</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2061,134 +2061,134 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NANT MILL Woodlands and Waterfalls Photo Workshop 7 Jun</t>
+          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Long exposures photography on the river and waterfalls that run through this enchanting woodland, secluded Welsh valley at Nant MillSummaryLocation: Wales - Wrexham - Nant MillDates: Sat 7th June 202510:30 am to 2 pmParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Nant MillDescription: This Nant Mill long exposure photography workshop takes you into a secluded Welsh valley near Wrexham, where a river and its waterfalls tumble through enchanting ancient woodland — open to all levels and any camera. Flowing water in a quiet, leafy gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this beautiful, tucked-away place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working the river, falls and woodland together, you'll learn to find order among the rocks, water and trees, to compose the intimate, close-up detail as readily as the wider valley view, and to read the soft, dappled light and the natural greens and browns of this ancient wood as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels the way the place actually feels.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of North Wales' hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
+          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventryLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 3Start Dates:Lightroom Editing CourseCoventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Coventry 3 wks - Tue 12 Jan - 26 Jan 2027Coventry 3 wks - Thu 6 May - 20 May 2027Level: BeginnersDescription: A practical three-week evening course that takes you from a messy photo library and untouched RAW files to a finished, repeatable Lightroom Classic workflow — working on your own laptop throughout.Week 1 is about getting organised: catalogues, importing, collections, keywords and star ratings, so you can find and manage your photos for good rather than losing them across folders.Week 2 moves on to global adjustments — reading the histogram, then exposure, white balance, contrast, tone curves and sharpening — the core develop tools that do most of the work on any image.Week 3 covers local adjustments — graduated and radial filters, adjustment brushes and spot removal — and pulling it together into a consistent, repeatable style across your photos.With a maximum of three people, you get real hands-on help on your own screen whenever you hit a problem, plus course notes for each module and practical assignments to work on between sessions. Beginners welcome — no editing experience needed; just bring a laptop with Adobe Lightroom Classic installed and an active subscription.Equipment: You will need a laptop with Adobe Lightroom Classic subscription and the App installed. Alan will provide you with a training Lightroom Library with images and use that to explain and then demonstrate the various tools.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/83fecb77-55e2-4a1b-b532-efa4213e832a/limbs.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/landscape-photography-workshops-nant-mill</t>
+          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Woodlands</t>
+          <t>photography-classes, photography-courses, photo editing, lightroom</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4568959", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}, {"@type": "Offer", "sku": "SQ1021857", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Coventry 3 wks - Tue 12 Jan - 26 Jan 2027"}, {"@type": "Offer", "sku": "SQ3349262", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Coventry 3 wks - Thu 6 May - 20 May 2027"}]</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="I30" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ7526725, SQ6831161, SQ1021857, SQ3349262</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SQ4568959</t>
+          <t>SQ7526725</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lightroom Courses for Beginners Photo Editing - Coventry</t>
+          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>For those who want to implement the best workflow for image management and all the dos and don'ts of post-production with these Photo Editing Classes with LightroomAdobe Lightroom Classic Courses for Beginners - CoventryLocation: 45 Hathaway Road, Coventry, CV4 9HWDuration: 3 × 2hr evening classes (19:00–21:00)Participants: Max 3Start Dates: Lightroom Editing Course Coventry 3 wks - Mon 7 Sep - 21 Sep 2026Coventry 3 wks - Thu 12 Nov - 26 Nov 2026Level: BeginnersDescription: A practical three-week evening course that takes you from a messy photo library and untouched RAW files to a finished, repeatable Lightroom Classic workflow — working on your own laptop throughout.Week 1 is about getting organised: catalogues, importing, collections, keywords and star ratings, so you can find and manage your photos for good rather than losing them across folders.Week 2 moves on to global adjustments — reading the histogram, then exposure, white balance, contrast, tone curves and sharpening — the core develop tools that do most of the work on any image.Week 3 covers local adjustments — graduated and radial filters, adjustment brushes and spot removal — and pulling it together into a consistent, repeatable style across your photos.With a maximum of three people, you get real hands-on help on your own screen whenever you hit a problem, plus course notes for each module and practical assignments to work on between sessions. Beginners welcome — no editing experience needed; just bring a laptop with Adobe Lightroom Classic installed and an active subscription.Equipment: You will need a laptop with Adobe Lightroom Classic subscription and the App installed. Alan will provide you with a training Lightroom Library with images and use that to explain and then demonstrate the various tools.</t>
+          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 11 May 2026 - 18:30 - 20:30Tue 1 Sep 2026 - 18:00 - 20:00Wed 23 Sep 2026 - 17:45 - 19:45Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details KenilworthDescription: This Long Exposure Photography Workshop is an evening shoot around the floodlit ruins of Kenilworth Castle in Warwickshire, open to all levels and any camera. Once one of England's mightiest fortresses and Robert Dudley's Elizabethan palace, the castle makes a dramatic subject against a darkening sky — and this workshop is built around the magic of long exposure at dusk, when the fading light, the castle's silhouette and a slow shutter combine to create atmospheric images that capture a sense of place, not just a record of a building.The long-exposure craft is the floor we build on, and we'll cover it properly: calculating exposure times for the movement and mood you want, focusing and exposing confidently in low light, and balancing ISO, shutter and aperture as the light drops. But the real work is learning to see. As the sky changes you'll compose the castle with intention — finding the frame beyond the obvious silhouette, working detail and texture as readily as the grand wide view, and reading the interplay of fading light, floodlight and deep shadow as a harmony rather than a problem to fight. The aim is an image with mood and restraint, where every element earns its place.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of England's most romantic castles — and a sharper, more intentional way of seeing light, movement and mood after dark anywhere.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fe40a5e1-7fa2-4057-982e-555479b97022/Lightroom+courses+-+photo+editing+course.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/lightroom-courses-for-beginners-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photo editing, lightroom</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7526725", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Coventry 3 wks - Mon 7 Sep - 21 Sep 2026"}, {"@type": "Offer", "sku": "SQ6831161", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Coventry 3 wks - Thu 12 Nov - 26 Nov 2026"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I31" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SQ7526725, SQ6831161</t>
+          <t>SQ5325711, SQ9140400, SQ8220723, SQ0932604, SQ1178418</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SQ7526725</t>
+          <t>SQ5325711</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Long Exposure Photography Workshop KENILWORTH Sunset</t>
+          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sunset landscape long exposure photography workshop shoots around Kenilworth Castle - Warwickshire - Various Dates | Long Exposures | Open to all levels| Book TodaySummaryLocation: Warwickshire - KenilworthDates:Mon 11 May 2026 - 18:30 - 20:30Tue 1 Sep 2026 - 18:00 - 20:00Wed 23 Sep 2026 - 17:45 - 19:45Mon 22 Mar 2027 - 18:00 - 20:00Wed 14 Apr 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details KenilworthDescription: This Long Exposure Photography Workshop is an evening shoot around the floodlit ruins of Kenilworth Castle in Warwickshire, open to all levels and any camera. Once one of England's mightiest fortresses and Robert Dudley's Elizabethan palace, the castle makes a dramatic subject against a darkening sky — and this workshop is built around the magic of long exposure at dusk, when the fading light, the castle's silhouette and a slow shutter combine to create atmospheric images that capture a sense of place, not just a record of a building.The long-exposure craft is the floor we build on, and we'll cover it properly: calculating exposure times for the movement and mood you want, focusing and exposing confidently in low light, and balancing ISO, shutter and aperture as the light drops. But the real work is learning to see. As the sky changes you'll compose the castle with intention — finding the frame beyond the obvious silhouette, working detail and texture as readily as the grand wide view, and reading the interplay of fading light, floodlight and deep shadow as a harmony rather than a problem to fight. The aim is an image with mood and restraint, where every element earns its place.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether long exposure is new to you or you're refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric long-exposure images of one of England's most romantic castles — and a sharper, more intentional way of seeing light, movement and mood after dark anywhere.</t>
+          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Fairy GlenDescription: This Fairy Glen long exposure photography workshop takes you into one of Wales' most magical locations — a serene, secluded gorge where the River Conwy tumbles through the woods at Betws-y-Coed — and is open to all levels and any camera. Flowing water through a wooded gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this enchanting place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working two great locations within a couple of miles of each other, you'll learn to find order among the rocks, water and woodland, to compose the intimate detail as readily as the wider gorge, and to read the soft, dappled light and the natural greens and browns of the glen as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels like the place actually feels.With a maximum of just four photographers, this is genuinely personal tuition, with Alan guiding each person through observation, shot design, shooting and image reviews at both locations. You'll come away with a set of atmospheric long-exposure images of one of Snowdonia's hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1712472502735-OHOKCDKMCP1BAMQ0JQUA/kenilworth+defenses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-kenilworth</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2198,26 +2198,26 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5325711", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 11 May 2026 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9140400", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 1 Sep 2026 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8220723", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 23 Sep 2026 - 17:45 - 19:45", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0932604", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 22 Mar 2027 - 18:00 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1178418", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 14 Apr 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SQ5325711, SQ9140400, SQ8220723, SQ0932604, SQ1178418</t>
+          <t>SQ8778402, SQ9080164, SQ6636860</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SQ5325711</t>
+          <t>SQ8778402</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2229,51 +2229,51 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FAIRY GLEN and Fairy Falls Long Exposure Photography</t>
+          <t>BURNHAM ON SEA Long Exposure Photography Workshop 1 Aug</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A magical gorge on the River Conwy at Betws-y-Coed. Fairy Glen and Fairy Falls provide an opportunity to practise long exposure photography on the magic of this river. Fairy Glen Betws-y-Coed Long Exposure Photography WorkshopSummaryLocation: Wales - Betws-y-CoedDates:Sat 26th Sep 2026 - 10:00 - 13:30Sat 6th Mar 2027 - 10:00 - 13:30Fri 14th May 2027 - 10:00 - 13:30 + Option for Anglesey Weekend WorkshopParticipants: Max 4Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Fairy GlenDescription: This Fairy Glen long exposure photography workshop takes you into one of Wales' most magical locations — a serene, secluded gorge where the River Conwy tumbles through the woods at Betws-y-Coed — and is open to all levels and any camera. Flowing water through a wooded gorge is the perfect subject for long exposure, and this half-day workshop is about more than the silky-water effect: it's about learning to see this enchanting place and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on — setting up your tripod and filters, and calculating the right exposure time for the effect you want — but the real work is composition and seeing. Working two great locations within a couple of miles of each other, you'll learn to find order among the rocks, water and woodland, to compose the intimate detail as readily as the wider gorge, and to read the soft, dappled light and the natural greens and browns of the glen as a quiet harmony rather than chasing a loud, over-processed look. The aim is a photograph with mood and restraint — moving water that feels like the place actually feels.With a maximum of just four photographers, this is genuinely personal tuition, with Alan guiding each person through observation, shot design, shooting and image reviews at both locations. You'll come away with a set of atmospheric long-exposure images of one of Snowdonia's hidden gems — and a stronger, more intentional way of seeing moving water and woodland that you can take anywhere.</t>
+          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 1st Aug 2026 - 18:45 - 21:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details BurnhamDescription: This Burnham on Sea long exposure photography workshop is an evening on the Somerset coast built around one of the most photogenic subjects in the country — the town's iconic nine-legged lighthouse, standing on stilts on the open beach. Open to all levels and any camera, it's about the art of long exposure: not just the silky-water effect, but learning to see this minimalist coast and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on, and we'll cover it properly — setting up, calculating shutter times and using filters — before heading onto the beach to shoot on an incoming tide as the sun sets. But the real work is composition and seeing. As the light builds you'll learn to place the lighthouse with real intention in a clean, minimalist frame, to work the intimate detail of stilts, reflections and wet sand as readily as the wide seascape, and to read the soft, shifting colour of a coastal sunset as a harmony rather than chasing a loud, over-saturated sky. The aim is mood and restraint — an image that feels like the quiet of that beach at dusk.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for settings, composition and one-to-one guidance in the field. Whether long exposure is new to you or you're refining your technique, you'll come away with a set of atmospheric sunset images of this famous Somerset landmark — and a sharper, more intentional way of seeing light, movement and mood that you can take to any coast.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707214813724-6QPD5O2XJNRQNOEIRBXO/Fairy+Glen+Betws-y-Coed+Photography+Workshop.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshop-fairy-glen</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8778402", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 26th Sep 2026 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ9080164", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 6th Mar 2027 - 10:00 - 13:30"}, {"@type": "Offer", "sku": "SQ6636860", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri 14th May 2027 - 10:00 - 13:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="I33" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SQ8778402, SQ9080164, SQ6636860</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SQ8778402</t>
+          <t>SQ9466277</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2285,163 +2285,163 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BURNHAM ON SEA Long Exposure Photography Workshop 1 Aug</t>
+          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Seascape and Long Exposure Photography workshop at this iconic location in Somerset with the lighthouse at Burnham on SeaSummaryLocation: Somerset - Burnham On SeaDates: Sat 1st Aug 2026 - 18:45 - 21:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details BurnhamDescription: This Burnham on Sea long exposure photography workshop is an evening on the Somerset coast built around one of the most photogenic subjects in the country — the town's iconic nine-legged lighthouse, standing on stilts on the open beach. Open to all levels and any camera, it's about the art of long exposure: not just the silky-water effect, but learning to see this minimalist coast and make images of it that are calm, considered and your own, rather than the same shot everyone takes.The long-exposure craft is the floor we build on, and we'll cover it properly — setting up, calculating shutter times and using filters — before heading onto the beach to shoot on an incoming tide as the sun sets. But the real work is composition and seeing. As the light builds you'll learn to place the lighthouse with real intention in a clean, minimalist frame, to work the intimate detail of stilts, reflections and wet sand as readily as the wide seascape, and to read the soft, shifting colour of a coastal sunset as a harmony rather than chasing a loud, over-saturated sky. The aim is mood and restraint — an image that feels like the quiet of that beach at dusk.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for settings, composition and one-to-one guidance in the field. Whether long exposure is new to you or you're refining your technique, you'll come away with a set of atmospheric sunset images of this famous Somerset landmark — and a sharper, more intentional way of seeing light, movement and mood that you can take to any coast.</t>
+          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714573609279-RSKP2ELI51B1VY87SOCS/Burnham+Still.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/long-exposure-photography-workshops-burnham</t>
+          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - half-day photo workshops</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9466277", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "12 x £250 = £3000"}]</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H34" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="I34" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SQ9466277</t>
+          <t>SQ3248242</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription | Interest Free Payment Plan</t>
+          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Monthly Pick N Mix Subscription Package. 10% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details North YorkshireDescription: This is a 4-day, 3-night residential landscape photography workshop on the dramatic northeast coast of England, exploring the iconic coastline and moors of North Yorkshire — open to all levels from beginner to advanced. Based on the coast, you'll photograph some of the most atmospheric scenery in the country, from the tumbling fishing village of Staithes and the sweeping bay at Runswick to the harbour and abbey town of Whitby, with the wild North York Moors as a backdrop.Over four full days we work from sunrise to sunset to make the most of the best light, tides and empty beaches — far more time on location than a short workshop allows. The focus is on three things that make a strong coastal image: composing the rocks, headlands and shoreline into a balanced frame, mastering long exposure to draw out movement in the sea and sky, and timing each shoot to the tides and the golden light of dawn and dusk. Throughout, the emphasis isn't just on the postcard view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. Across the four days you'll build a real working rhythm for coastal photography, returning to locations in different conditions to capture them at their very best.With a maximum of just three photographers, this is exceptionally personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of iconic Yorkshire coast and moorland images — and the field craft to read light, tide and weather on any coastline. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/7c76925a-43b0-425c-995e-4f4e0190221c/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714649253207-Y2XV1QZ3QPAVYS7CEE33/Flamborough+-+Temptation.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/monthly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3248242", "price": "42.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £42 = £500"}, {"@type": "Offer", "sku": "SQ3113323", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £50 = £600"}, {"@type": "Offer", "sku": "SQ4824271", "price": "60.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £60 = £720"}, {"@type": "Offer", "sku": "SQ5162846", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £65 = £780"}, {"@type": "Offer", "sku": "SQ0960457", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £75 = £900"}, {"@type": "Offer", "sku": "SQ6021981", "price": "85.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £85 = £1020"}, {"@type": "Offer", "sku": "SQ3596605", "price": "100.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £100 = £1200"}, {"@type": "Offer", "sku": "SQ2188035", "price": "120.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £120 = £1440"}, {"@type": "Offer", "sku": "SQ5970824", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £150 = £1800"}, {"@type": "Offer", "sku": "SQ0439157", "price": "175.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £175 = £2100"}, {"@type": "Offer", "sku": "SQ9583245", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £200 = £2400"}, {"@type": "Offer", "sku": "SQ9424558", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "12 x £250 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>42</v>
+        <v>1450</v>
       </c>
       <c r="I35" t="n">
-        <v>250</v>
+        <v>1450</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SQ3248242, SQ3113323, SQ4824271, SQ5162846, SQ0960457, SQ6021981, SQ3596605, SQ2188035, SQ5970824, SQ0439157, SQ9583245, SQ9424558</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SQ3248242</t>
+          <t>SQ9283225</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NORTH YORKSHIRE Landscape Photography Workshop - Sep 2026</t>
+          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>An exciting 4-day residential Yorkshire Landscape Photography Workshop - visiting some of the iconic spots around the North Yorkshire Coast and MoorsSummary - Photography Workshops YorkshireLocation: North YorkshireDates:Thu 10 Sep - Sun 13 Sep 2026 - 4 Days/3 NightsParticipants: Max 3Fitness: 2. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details North YorkshireDescription: This is a 4-day, 3-night residential landscape photography workshop on the dramatic northeast coast of England, exploring the iconic coastline and moors of North Yorkshire — open to all levels from beginner to advanced. Based on the coast, you'll photograph some of the most atmospheric scenery in the country, from the tumbling fishing village of Staithes and the sweeping bay at Runswick to the harbour and abbey town of Whitby, with the wild North York Moors as a backdrop.Over four full days we work from sunrise to sunset to make the most of the best light, tides and empty beaches — far more time on location than a short workshop allows. The focus is on three things that make a strong coastal image: composing the rocks, headlands and shoreline into a balanced frame, mastering long exposure to draw out movement in the sea and sky, and timing each shoot to the tides and the golden light of dawn and dusk. Throughout, the emphasis isn't just on the postcard view but on learning to see it — composing with intention, working intimate detail as readily as the wide vista, and reading light and tide as a harmony rather than chasing the obvious shot. Across the four days you'll build a real working rhythm for coastal photography, returning to locations in different conditions to capture them at their very best.With a maximum of just three photographers, this is exceptionally personal tuition — Alan plans each day around the season, the forecast and the tide times, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of iconic Yorkshire coast and moorland images — and the field craft to read light, tide and weather on any coastline. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details HeathersDescription: Every August the moors of the Peak District turn a spectacular purple as the heather comes into bloom, and this Peak District Heather Photography Workshop is your chance to capture that fleeting display at its very best — open to all levels and any camera. Run as short, focused sessions at the magic hours of sunrise and sunset, it pairs one of Britain's most iconic landscapes with its richest seasonal colour, and the low golden light that makes heather and gritstone glow.You can join either of two sessions, or both: a sunset shoot at Surprise View above Hathersage in Derbyshire — one of the finest viewpoints in the Peak, with sweeping heather foregrounds, the Mother Cap stone and famously dark skies — or a sunrise shoot among the dramatic gritstone of The Roaches, Hen Cloud and Ramshaw Rocks in Staffordshire, weathered into extraordinary shapes above a sea of purple moorland.A blaze of purple is more seductive than it is easy, and the real work is learning to see past the obvious. The technical craft is the floor we build on — controlling exposure to hold rich colour and a dramatic sky, and working quickly in the brief light of dawn and dusk — but the focus is on composing with intention: balancing the heather and the gritstone rock forms into a frame with order, working the intimate detail of bloom and weathered stone as readily as the wide moorland vista, and treating the purple, the gold and the low light as a harmony rather than a colour to crank. We shoot two to three locations each session as conditions allow, and the aim throughout is an image with mood and restraint — one that feels like that moor at first or last light.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you take the sunset, the sunrise or make a weekend of both, you'll come away with a portfolio of the Peak District's heather at its peak — and a sharper, more intentional way of seeing colour, light and landscape that you can take anywhere. If you're booking both sessions, please arrange your own overnight accommodation near The Roaches for the early sunrise shoot. Please also note this is a seasonal workshop tied to the heather bloom, so exact dates may shift slightly with the season.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714649253207-Y2XV1QZ3QPAVYS7CEE33/Flamborough+-+Temptation.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1685361335026-KNDKR6D00CTPUASRDWDV/Surprise%2BView%2B2.jpg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/north-yorkshire-landscape-photography</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>coastal, All Photography Workshops, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9283225", "price": "1450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "1450.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>1450</v>
+        <v>125</v>
       </c>
       <c r="I36" t="n">
-        <v>1450</v>
+        <v>200</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ1994489, SQ1389945, SQ5395624</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SQ9283225</t>
+          <t>SQ1994489</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2453,51 +2453,51 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PEAK DISTRICT HEATHER Photography Workshops - 15-16 Aug</t>
+          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Join me for the Peak District heather displays over this iconic landscape in August - 4hr Heather Peak District Photography Workshops | All levels welcomeSummaryLocation: Peak District - Derbyshire/Staffordshire2026 - Sat 15th Aug 18:15 21:15 - Derbyshire Surprise View2026 - Sun 17th Aug 05:45 08:45 - Staffordshire - The RoachesParticipants: Max 6Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details HeathersDescription: Every August the moors of the Peak District turn a spectacular purple as the heather comes into bloom, and this Peak District Heather Photography Workshop is your chance to capture that fleeting display at its very best — open to all levels and any camera. Run as short, focused sessions at the magic hours of sunrise and sunset, it pairs one of Britain's most iconic landscapes with its richest seasonal colour, and the low golden light that makes heather and gritstone glow.You can join either of two sessions, or both: a sunset shoot at Surprise View above Hathersage in Derbyshire — one of the finest viewpoints in the Peak, with sweeping heather foregrounds, the Mother Cap stone and famously dark skies — or a sunrise shoot among the dramatic gritstone of The Roaches, Hen Cloud and Ramshaw Rocks in Staffordshire, weathered into extraordinary shapes above a sea of purple moorland.A blaze of purple is more seductive than it is easy, and the real work is learning to see past the obvious. The technical craft is the floor we build on — controlling exposure to hold rich colour and a dramatic sky, and working quickly in the brief light of dawn and dusk — but the focus is on composing with intention: balancing the heather and the gritstone rock forms into a frame with order, working the intimate detail of bloom and weathered stone as readily as the wide moorland vista, and treating the purple, the gold and the low light as a harmony rather than a colour to crank. We shoot two to three locations each session as conditions allow, and the aim throughout is an image with mood and restraint — one that feels like that moor at first or last light.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you take the sunset, the sunrise or make a weekend of both, you'll come away with a portfolio of the Peak District's heather at its peak — and a sharper, more intentional way of seeing colour, light and landscape that you can take anywhere. If you're booking both sessions, please arrange your own overnight accommodation near The Roaches for the early sunrise shoot. Please also note this is a seasonal workshop tied to the heather bloom, so exact dates may shift slightly with the season.</t>
+          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details ChestertonDescription: This sunset landscape photography workshop is an evening shoot at Chesterton Windmill, one of Warwickshire's most iconic landmarks, open to all levels and any camera. A striking 17th-century tower windmill on its arched stone legs, standing alone on a hilltop for nearly 350 years, it's one of the most photogenic structures in the county — and this workshop is built around capturing it in the golden light of sunset and the long-exposure drama of the hour that follows, in a way that's genuinely your own rather than the postcard everyone already has.The technical craft is the floor we build on — exposure, depth of field, and setting up long exposures to draw movement out of cloud and sky as dusk falls. But the real work is learning to see this familiar landmark freshly: composing the windmill with intention against the sky and the rolling countryside, finding the unexpected angle and the intimate detail as readily as the wide hilltop vista, and reading the warm, directional light of sunset as a harmony to compose with rather than just a pretty backdrop to point at. As the colour builds and fades, you'll learn to design a frame where the light, the land and the windmill all work together.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to landscape photography or refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric images of this famous Warwickshire landmark — golden-hour silhouettes and long-exposure skies — and a sharper, more intentional way of seeing light and composition that lets you photograph any landmark at its best.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1685361335026-KNDKR6D00CTPUASRDWDV/Surprise%2BView%2B2.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/peak-district-heather-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape, Flowering</t>
+          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1994489", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 15 Aug 2026 - Hathersage 18:15 - 21:15", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1389945", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 16 Aug 2026 - The Roaches &amp; Ramshaw 05:45 - 08:45", "priceSpecification": {"price": "125.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5395624", "price": "200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Both sessions - 15 and 16 Aug - sunset and sunrise"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="I37" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SQ1994489, SQ1389945, SQ5395624</t>
+          <t>SQ3572999, SQ0796814, SQ9554270, SQ5307067</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SQ1994489</t>
+          <t>SQ3572999</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2509,51 +2509,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Photography Workshops CHESTERTON WINDMILL - Warwickshire</t>
+          <t>LAVENDER FIELD Photography Workshop - Glouc or Warks July</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chesterton windmill is one of Warwickshire's most famous landmarks. Join me in a sunset landscape photography workshop and learn about composition and lightSummaryLocation: Warwickshire - ChestertonDates:Wed 16th Sep 2026 - 18:00 - 20:30Mon 5th Oct 2026 - 17:30 - 20:00Tue 13th May 2027 - 18:15 - 20:15Mon 10th May 2027 - 18:30 - 20:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details ChestertonDescription: This sunset landscape photography workshop is an evening shoot at Chesterton Windmill, one of Warwickshire's most iconic landmarks, open to all levels and any camera. A striking 17th-century tower windmill on its arched stone legs, standing alone on a hilltop for nearly 350 years, it's one of the most photogenic structures in the county — and this workshop is built around capturing it in the golden light of sunset and the long-exposure drama of the hour that follows, in a way that's genuinely your own rather than the postcard everyone already has.The technical craft is the floor we build on — exposure, depth of field, and setting up long exposures to draw movement out of cloud and sky as dusk falls. But the real work is learning to see this familiar landmark freshly: composing the windmill with intention against the sky and the rolling countryside, finding the unexpected angle and the intimate detail as readily as the wide hilltop vista, and reading the warm, directional light of sunset as a harmony to compose with rather than just a pretty backdrop to point at. As the colour builds and fades, you'll learn to design a frame where the light, the land and the windmill all work together.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to landscape photography or refining your technique, you get real one-to-one guidance in the field. You'll come away with a set of atmospheric images of this famous Warwickshire landmark — golden-hour silhouettes and long-exposure skies — and a sharper, more intentional way of seeing light and composition that lets you photograph any landmark at its best.</t>
+          <t>Join me in the Cotswolds, or Warwickshire for a spectacular lavender field landscape workshop . Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30 for either of the lavender farmsSummaryLocation: Snowshill - Gloucestershire or Bubbenhall · Warwickshire, Lavender FarmsDates:Sat 4th Jul 2026 - 18:00 21:00Sat 11th Jul 2025 - 18:00 21:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and Tripod (tripod available to borrow)Photography Workshop Event Details LavenderDescription: This Lavender Photography Workshop is a magical evening among the lavender rows of the Cotswolds at Snowshill in Gloucestershire or depending on arrangements at Warwickshire Lavender Farm, Bubbenhall — open to all levels and any camera. Best of all, you'll photograph the fields after the farm has closed to the general public, so instead of working around coachloads of day-trippers you have the spectacular sea of purple and the wildflower areas largely to yourselves — making it far easier to slow down, see properly and compose clean shots as the light softens towards sunset and the colour comes alive.A field of lavender is seductive but deceptively hard — it's all too easy to come home with the loud, over-saturated purple shot everyone takes. The real work here is learning to see past that. The technical craft is the floor we build on — focusing and exposing accurately in fading light, and holding both shadow and highlight as the sun drops — but the focus is on composing with intention: finding order and a lead-in through the endless rows, working the intimate, abstract close-up of colour and texture as readily as the sweeping vista, and treating the purple, the green and the warm evening light as a harmony to balance rather than a colour to crank. The aim is a photograph with mood and restraint — one that feels like that quiet evening in the field.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance throughout. With the crowds gone and the fields quiet, you'll have the space and time to really work your compositions — and you'll come away with a portfolio of vivid lavender images at their most atmospheric, plus a sharper, more intentional way of seeing colour, light and detail that you can take anywhere. This is a special after-hours session: the farm opens to us beyond its normal public hours so we can shoot from 5p/6pmm into the early sunset light 9/9:30pm, and your workshop fee includes that commercial after-hours access. Please note the dates and finish times are set by the lavender farm rather than by Alan, and may be subject to change with the season, flowering and weather as they do not extend the hours if rain is forecast on the day, so you need to be flexible and be able to swap to an alternative Saturday evening that the farm has extended hours. Usually the first 3 Saturdays of July.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714682519866-NVMB6B7Q4F93DGOGPQIK/Moonlit+Chesterton.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-chesterton-windmill</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3572999", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Wed 16th Sep 2026 - 18:00 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0796814", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 5th Oct 2026 - 17:30 - 20:00", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9554270", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Tue 13th Apr 2027 - 18:15 - 20:15", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5307067", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon 10th May 2027 - 18:30 - 20:30", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 4th Jul 2026 - 18:00 21:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 11th Jul 2026 - 18:00 21:00"}]</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I38" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SQ3572999, SQ0796814, SQ9554270, SQ5307067</t>
+          <t>SQ6748367, SQ7542811</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SQ3572999</t>
+          <t>SQ6748367</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2565,51 +2565,51 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LAVENDER FIELD Photography Workshop - Gloucestershire July</t>
+          <t>Poppy Fields Photography Workshops | Worcestershire</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Join me in the Cotswolds for a spectacular lavender field landscape workshop. Photograph in the evening hours by arrangement of owners (date is subject to change or weather on the day) Price includes entry fee of £30SummaryLocation: Snowshill - GloucestershireDates:Sat 4th Jul 2026 - 17:00 20:00Sat 11th Jul 2025 - 17:00 20:00Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details LavenderDescription: This Lavender Photography Workshop is a magical evening among the lavender rows of the Cotswolds at Snowshill in Gloucestershire — open to all levels and any camera. Best of all, you'll photograph the fields after the farm has closed to the general public, so instead of working around coachloads of day-trippers you have the spectacular sea of purple and the wildflower areas largely to yourselves — making it far easier to slow down, see properly and compose clean shots as the light softens towards sunset and the colour comes alive.A field of lavender is seductive but deceptively hard — it's all too easy to come home with the loud, over-saturated purple shot everyone takes. The real work here is learning to see past that. The technical craft is the floor we build on — focusing and exposing accurately in fading light, and holding both shadow and highlight as the sun drops — but the focus is on composing with intention: finding order and a lead-in through the endless rows, working the intimate, abstract close-up of colour and texture as readily as the sweeping vista, and treating the purple, the green and the warm evening light as a harmony to balance rather than a colour to crank. The aim is a photograph with mood and restraint — one that feels like that quiet evening in the field.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance throughout. With the crowds gone and the fields quiet, you'll have the space and time to really work your compositions — and you'll come away with a portfolio of vivid lavender images at their most atmospheric, plus a sharper, more intentional way of seeing colour, light and detail that you can take anywhere. This is a special after-hours session: the farm opens to us beyond its normal public hours so we can shoot from 5pm into the early sunset light, and your workshop fee includes that commercial after-hours access. Please note the dates and finish times are set by the lavender farm rather than by Alan, and may be subject to change with the season and flowering.</t>
+          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: There are few sights in the English summer to beat rolling Worcestershire hills washed red with wild poppies, and this Poppy Fields Photography Workshop is built to catch them at their fleeting best. Open to all levels and any camera, it runs as short, focused sessions at the golden hours of sunset and sunrise — the two times of day when low, warm light makes a field of poppies truly glow.A field of red is more seductive than it is easy, and the work is learning to turn it into a photograph rather than a snapshot. The focus is on three things: composing with intention to find order and a lead-in through a busy, repeating scene, controlling exposure and depth of field to decide what's sharp and what dissolves into colour, and reading light, texture and colour as a harmony — letting the reds sing without tipping into the over-saturated cliché. You'll work both the intimate, single-stem detail and the sweeping vista, and learn to see past the obvious shot everyone else takes.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you join the sunset session, the dawn one, or both, you'll come away with a portfolio of poppy-field images at their most atmospheric — and a stronger way of seeing colour, light and composition that carries into everything you photograph next. Please note that poppies bloom briefly and unpredictably each June, so both the exact dates and the field we use are confirmed at short notice once the flowering is at its best. A flexible approach is essential — but it's exactly what lets us photograph the poppies at their absolute peak.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714572933715-EIVNF6O80HEJCSEU5D4U/lavender+sprint.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/photography-workshops-lavender-fields</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6748367", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 4th Jul 2026 - 17:00 20:00"}, {"@type": "Offer", "sku": "SQ7542811", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 11th Jul 2026 - 17:00 20:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 9 Jun 05:00-07:30"}]</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="I39" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SQ6748367, SQ7542811</t>
+          <t>SQ8740143, SQ7189877</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SQ6748367</t>
+          <t>SQ8740143</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2621,107 +2621,107 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poppy Fields Photography Workshops | Worcestershire</t>
+          <t>Online Photography Classes 121 - Zoom - Package Options</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Poppy fields photography workshop - Choose a sunrise or sunset 2.5hrs photo workshop at amazing poppy fields in Worcestershire | Seasonal DependantSummaryLocation: WorcestershireDates: (dates are subject to change based on when the poppy fields flower in June)8th Jun 19:15 - 21:459th Jun 05:00 - 07:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: PoppiesDescription: There are few sights in the English summer to beat rolling Worcestershire hills washed red with wild poppies, and this Poppy Fields Photography Workshop is built to catch them at their fleeting best. Open to all levels and any camera, it runs as short, focused sessions at the golden hours of sunset and sunrise — the two times of day when low, warm light makes a field of poppies truly glow.A field of red is more seductive than it is easy, and the work is learning to turn it into a photograph rather than a snapshot. The focus is on three things: composing with intention to find order and a lead-in through a busy, repeating scene, controlling exposure and depth of field to decide what's sharp and what dissolves into colour, and reading light, texture and colour as a harmony — letting the reds sing without tipping into the over-saturated cliché. You'll work both the intimate, single-stem detail and the sweeping vista, and learn to see past the obvious shot everyone else takes.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you join the sunset session, the dawn one, or both, you'll come away with a portfolio of poppy-field images at their most atmospheric — and a stronger way of seeing colour, light and composition that carries into everything you photograph next. Please note that poppies bloom briefly and unpredictably each June, so both the exact dates and the field we use are confirmed at short notice once the flowering is at its best. A flexible approach is essential — but it's exactly what lets us photograph the poppies at their absolute peak.</t>
+          <t>Private Online Photography Classes (Zoom)Summary - Private Online Photography Classes - Key InformationFormat: Online 1-2-1 via Zoom (free to use)Sessions: Single 1hr lesson, or discounted packages of 4, 6, 8 or 12 hoursAvailability: Standard Mon–Fri, 9am–5pm or Premium - Mon-Sun 9am -9pmValidity: Pay now, book dates later — use within 12 months of purchaseLevel: All levels, beginner to advancedDescription: Private online photography classes tailored to your needs — tuition and support on any aspect of photography, with no other students, so the time you pay for is dedicated entirely to your own style and pace.Equipment: Anything you want to learn or improve on. Sessions run over Zoom, with notes provided; submit images for detailed feedback between lessons.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714575407530-MBS3PUSXD9GGHA68754C/poppy+dawn.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/4ac49e77-bfdc-435d-bf46-d82bda3bec91/online+photography+lessons.png</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/poppy-fields-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8740143", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sat 8 Jun 19:15-21:45"}, {"@type": "Offer", "sku": "SQ7189877", "price": "95.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 9 Jun 05:00-07:30"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Standard (Weekdays 9-5) - 1 x 1hr - Pay as you go    £50"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Standard (Weekdays 9-5) - 4 x 1hr (15% Off)          £170"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Standard (Weekdays 9-5) - 6 x 1hr (20% Off)          £240"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Standard (Weekdays 9-5) - 8 x 1hr (25% Off)          £300"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Standard (Weekdays 9-5) - 12 x 1hr (25% Off)         £450"}, {"@type": "Offer", "sku": "SQ6476466", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 1 x 1hr - Pay as you go  £75"}, {"@type": "Offer", "sku": "SQ4036849", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 4 x 1hr (15% Off)        £255"}, {"@type": "Offer", "sku": "SQ6369047", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 6 x 1hr (20% Off)        £360"}, {"@type": "Offer", "sku": "SQ7040572", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 8 x 1hr (25% Off)        £450"}, {"@type": "Offer", "sku": "SQ6714463", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Zoom Premium (Eve/Weekend 9-9) - 12 x 1hr (25% Off)       £675"}]</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H40" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="I40" t="n">
-        <v>95</v>
+        <v>675</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SQ8740143, SQ7189877</t>
+          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258, SQ6476466, SQ4036849, SQ6369047, SQ7040572, SQ6714463</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SQ8740143</t>
+          <t>SQ1461156</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Online Photography Classes 121 - Zoom - Package Options</t>
+          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Private Online Photography Classes (Zoom)Summary - Private Online Photography Classes - Key InformationFormat: Online 1-2-1 via Zoom (free to use)Sessions: Single 1hr lesson, or discounted packages of 4, 6, 8 or 12 hoursAvailability: Mon–Fri, 9am–5pmValidity: Pay now, book dates later — use within 12 months of purchaseLevel: All levels, beginner to advancedDescription: Private online photography classes tailored to your needs — tuition and support on any aspect of photography, with no other students, so the time you pay for is dedicated entirely to your own style and pace.Equipment: Anything you want to learn or improve on. Sessions run over Zoom, with notes provided; submit images for detailed feedback between lessons.</t>
+          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1698395506000-MRZ4RFY6D3D1ZT6B2MND/photography-classes-online.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/private-online-photography-classes-zoom</t>
+          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-tuition</t>
+          <t>photography-classes, photography-courses, photography-workshops</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1461156", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom 1 x 1hr - 9am 5pm - Mon-Fri"}, {"@type": "Offer", "sku": "SQ5568703", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 4 x 1hr (15% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ6341100", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 6 x 1hr (20% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2281758", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 8 x 1hr (25% Off) 9am 5pm - Mon -Fri"}, {"@type": "Offer", "sku": "SQ2043258", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Zoom Package 12 x 1hr (25% Off) 9am 5pm - Mon -Fri"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x £750 = £3000"}]</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="I41" t="n">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SQ1461156, SQ5568703, SQ6341100, SQ2281758, SQ2043258</t>
+          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SQ1461156</t>
+          <t>SQ4217445</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2733,163 +2733,163 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription | Interest Free Payments</t>
+          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quarterly Pick N Mix Subscription Package. 15% Discount on events/services for one year | Interest Free Payment Plan | Take events or lessons immediately |</t>
+          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select a package of Zoom sessions within twelve months at intervals to suit youDescription: Independent one-to-one RPS mentoring for your Licentiate (LRPS) or Associate (ARPS) distinction — online via Zoom, with a mentor who holds both distinctions himself and has a 100% pass rate to date. Most photographers who fall short don't fail on technique — they submit a collection of strong individual images rather than a planned, cohesive panel, and a panel is judged as a whole. That judgement — image selection, sequencing, the hanging plan and your Statement of Intent — is exactly what mentoring brings. We work in three stages: plan the panel, build and refine it, then test readiness before you submit. Sessions are flexible 1-hour Zoom slots — buy only what you need and book your dates later, across up to twelve months. Start fresh, or revise a panel that didn't pass first time.Format: One-to-one, online via Zoom — private and personal to you and your panel.Equipment Needed: Zoom App; free Dropbox account for sharing portfolios and updated images.Terms: A package of Zoom sessions must be used within 12 months of purchase or it is forfeited. You can extend the timeline or purchase additional sessions if needed.Method: Honest technical and creative critique with suggestions for improvement; advice on image selection, sequencing, the hanging plan and your Statement of Intent.Package Options: Choose Mon–Fri 9am–5pm daytime rates, or Mon–Sun 9am–9pm for evening and weekend flexibility.1 × 1hr — single session (fact-find &amp; review)4 × 1hr — 15% off (reset a failed panel)6 × 1hr — 20% off (from scratch, recommended)8 × 1hr — 25% off (extended panel build)12 × 1hr — 25% off (best value, full programme)More Details: about the RPS Mentoring Course</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/fbab50ee-2fe8-4fe9-8804-e691b883cf4b/Photography+Payment+Plan.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/quarterly-pick-n-mix-subscription</t>
+          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>photography-classes, photography-courses, photography-workshops</t>
+          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4217445", "price": "250.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £250 = £1000"}, {"@type": "Offer", "sku": "SQ6277577", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £300 = £1200"}, {"@type": "Offer", "sku": "SQ7788516", "price": "350.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £350 = £1400"}, {"@type": "Offer", "sku": "SQ5124608", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x 400 = £1600"}, {"@type": "Offer", "sku": "SQ2657628", "price": "500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £500 = £2000"}, {"@type": "Offer", "sku": "SQ2267503", "price": "750.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "4 x £750 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H42" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="I42" t="n">
-        <v>750</v>
+        <v>675</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SQ4217445, SQ6277577, SQ7788516, SQ5124608, SQ2657628, SQ2267503</t>
+          <t>SQ7839038, SQ3867813, SQ8903198, SQ4831915, SQ1077689, SQ8233730, SQ9139531, SQ0776423, SQ2385997, SQ9440259</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SQ4217445</t>
+          <t>SQ7839038</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>course</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RPS Courses - Independent RPS Mentoring for RPS Distinctions</t>
+          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RPS Courses - Independant RPS Mentoring for RPS Distinctions - Start anytime, you select a package of Zoom sessions within twelve months at intervals to suit youDescription: Independent one-to-one RPS mentoring for your Licentiate (LRPS) or Associate (ARPS) distinction — online via Zoom, with a mentor who holds both distinctions himself and has a 100% pass rate to date. Most photographers who fall short don't fail on technique — they submit a collection of strong individual images rather than a planned, cohesive panel, and a panel is judged as a whole. That judgement — image selection, sequencing, the hanging plan and your Statement of Intent — is exactly what mentoring brings. We work in three stages: plan the panel, build and refine it, then test readiness before you submit. Sessions are flexible 1-hour Zoom slots — buy only what you need and book your dates later, across up to twelve months. Start fresh, or revise a panel that didn't pass first time.Format: One-to-one, online via Zoom — private and personal to you and your panel.Equipment Needed: Zoom App; free Dropbox account for sharing portfolios and updated images.Terms: A package of Zoom sessions must be used within 12 months of purchase or it is forfeited. You can extend the timeline or purchase additional sessions if needed.Method: Honest technical and creative critique with suggestions for improvement; advice on image selection, sequencing, the hanging plan and your Statement of Intent.Package Options: Choose Mon–Fri 9am–5pm daytime rates, or Mon–Sun 9am–9pm for evening and weekend flexibility.1 × 1hr — single session (fact-find &amp; review)4 × 1hr — 15% off (reset a failed panel)6 × 1hr — 20% off (from scratch, recommended)8 × 1hr — 25% off (extended panel build)12 × 1hr — 25% off (best value, full programme)More Details: about the RPS Mentoring Course</t>
+          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: The Secrets of Woodland Photography is a 1-Day Masterclass in Coventry, open to all levels and any camera. Woodland is the hardest subject there is — chaotic, cluttered, endlessly busy — which is exactly why it's the best place to learn to see. Most people come away with the tangled, cliché shot; this day is about learning to find the order, the light and the quiet beauty hidden within the chaos, and to make woodland images that are calm, intentional and your own.The technical setup matters, but it's only the floor we build on. Rather than a typical walk-and-shoot, the day runs as three connected sessions — theory, practical and editing — so we can go deeper than settings. We start with the thinking behind a strong woodland image and the craft that delivers it: simplifying a busy scene, using light and shadow, choosing what to include and what to leave out. Then you put it into practice on a woodland walk, working the close-up, the macro detail and the abstract as readily as the wider view — reading texture and colour as a harmony, not chasing the loud, over-saturated shot. Finally we review your images together and finish on the editing that brings the quiet colours of the forest to life without shouting.The day runs from Alan's home, which offers three things most workshops can't: instant access to woodland straight from the garden, a comfortable covered and heated space for the presentations and image reviews, and a large screen to study your shots on — so the day works whatever the weather. You'll leave not just with a set of woodland images, but with a way of seeing — light, simplicity and restraint — that changes how you photograph trees, nature and detail wherever you go next.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707307452323-G3C2AIXAHRLLVB36VASA/RPS+Courses.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714646680135-9EB3PR57B78W9NMZ09JI/Plant+Hill+Woods+%2310+-+Jan+2022.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/rps-mentoring-photography-course</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1-2-1-private-lessons, photography-classes, photography-courses, photography-tuition, rps</t>
+          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7839038", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ3867813", "price": "170.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ8903198", "price": "240.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ4831915", "price": "300.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm  8x 1hr"}, {"@type": "Offer", "sku": "SQ1077689", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Fri 9am-5pm 12 x 1hr"}, {"@type": "Offer", "sku": "SQ8233730", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 1 x 1hr"}, {"@type": "Offer", "sku": "SQ9139531", "price": "255.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 4 x 1hr"}, {"@type": "Offer", "sku": "SQ0776423", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 6 x 1hr"}, {"@type": "Offer", "sku": "SQ2385997", "price": "450.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 8 x 1hr"}, {"@type": "Offer", "sku": "SQ9440259", "price": "675.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon- Sun 9am-9pm 12 x 1hr"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 11th Apr 2027 - 10am - 4pm"}]</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I43" t="n">
-        <v>675</v>
+        <v>150</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SQ7839038, SQ3867813, SQ8903198, SQ4831915, SQ1077689, SQ8233730, SQ9139531, SQ0776423, SQ2385997, SQ9440259</t>
+          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SQ7839038</t>
+          <t>SQ4914997</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>The Secret of WOODLAND PHOTOGRAPHY- 1-Day Jan, Apr, Aug, Oct</t>
+          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Simplifying Woodland Photography | Unlocking the Secrets to Capturing the Beauty of woods | Three sessions - Theory - Practical - Editing in one daySummaryLocation: Coventry - CV4 9HWDates: - 10:00 - 16:00Sun 2nd Aug - SummerSun 18th Oct - AutumnSun 10th Jan - WinterSun 11th Apr - SpringParticipants: Max 3Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and TripodPhotography Workshop Event Details: Woodland Photography MasterclassDescription: The Secrets of Woodland Photography is a 1-Day Masterclass in Coventry, open to all levels and any camera. Woodland is the hardest subject there is — chaotic, cluttered, endlessly busy — which is exactly why it's the best place to learn to see. Most people come away with the tangled, cliché shot; this day is about learning to find the order, the light and the quiet beauty hidden within the chaos, and to make woodland images that are calm, intentional and your own.The technical setup matters, but it's only the floor we build on. Rather than a typical walk-and-shoot, the day runs as three connected sessions — theory, practical and editing — so we can go deeper than settings. We start with the thinking behind a strong woodland image and the craft that delivers it: simplifying a busy scene, using light and shadow, choosing what to include and what to leave out. Then you put it into practice on a woodland walk, working the close-up, the macro detail and the abstract as readily as the wider view — reading texture and colour as a harmony, not chasing the loud, over-saturated shot. Finally we review your images together and finish on the editing that brings the quiet colours of the forest to life without shouting.The day runs from Alan's home, which offers three things most workshops can't: instant access to woodland straight from the garden, a comfortable covered and heated space for the presentations and image reviews, and a large screen to study your shots on — so the day works whatever the weather. You'll leave not just with a set of woodland images, but with a way of seeing — light, simplicity and restraint — that changes how you photograph trees, nature and detail wherever you go next.</t>
+          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Sezincote Garden Photography Workshop takes you into one of the most extraordinary gardens in the Cotswolds — the grounds of a Mughal Indian palace, complete with copper dome and minarets, set in the gentle hills of Gloucestershire and open to all levels and any camera. Few gardens offer a photographer this much: a water garden of seven pools, waterfalls and a grotto, a temple to the Hindu sun god Surya, and a curving Orangery framing a Persian Garden of Paradise — all waiting to be explored through your lens.A setting this rich is a wonderful place to slow down and learn to see. The technical craft is the floor we build on — sharp focus, controlling depth of field to isolate a subject, the settings that give you control — but the real work is composition and intention. Working through the estate's grounds together, you'll learn to find a strong frame within a busy, ornate scene, to work the intimate macro and close-up detail as readily as the wide views of pools, temple and dome, and to read the light and the colour as a harmony rather than chasing the loud, obvious shot. The aim is always an image that's considered and your own, not just a record of a remarkable place.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for camera settings, composition and one-to-one guidance, plus image reviews to spark ideas and inspiration on the day. You'll come away with a portfolio of images from one of England's most unusual gardens — and a sharper, more intentional way of seeing detail, composition and light in any garden you photograph. Please note the workshop fee does not include the entrance fee to Sezincote garden and house, which is payable separately on the day.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/52f3e506-547d-4b13-bcff-d770db619091/Batsford+%2314+-+Oct+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/secrets-of-woodland-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - one day photo workshops, Macro &amp; Abstract, Woodlands</t>
+          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4914997", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 2nd Aug 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ4894934", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 18th Oct 2026 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ2827052", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 10 Jan 2027 - 10am - 4pm"}, {"@type": "Offer", "sku": "SQ0512761", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun 11th Apr 2027 - 10am - 4pm"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SQ4914997, SQ4894934, SQ2827052, SQ0512761</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SQ4914997</t>
+          <t>SQ9859986</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2901,51 +2901,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEZINCOTE Garden Photography Workshop - Gloucs 29 May</t>
+          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Macro and abstract Garden photography workshop. Camera settings, controlling DoF and composition at this Mughal Indian palace in the Cotswolds.SummaryLocation: Moreton on Marsh (Sezincote) - GloucestershireDates: Thu 29th May 2026 - 11:00 - 13:30Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Sezincote Garden Photography Workshop takes you into one of the most extraordinary gardens in the Cotswolds — the grounds of a Mughal Indian palace, complete with copper dome and minarets, set in the gentle hills of Gloucestershire and open to all levels and any camera. Few gardens offer a photographer this much: a water garden of seven pools, waterfalls and a grotto, a temple to the Hindu sun god Surya, and a curving Orangery framing a Persian Garden of Paradise — all waiting to be explored through your lens.A setting this rich is a wonderful place to slow down and learn to see. The technical craft is the floor we build on — sharp focus, controlling depth of field to isolate a subject, the settings that give you control — but the real work is composition and intention. Working through the estate's grounds together, you'll learn to find a strong frame within a busy, ornate scene, to work the intimate macro and close-up detail as readily as the wide views of pools, temple and dome, and to read the light and the colour as a harmony rather than chasing the loud, obvious shot. The aim is always an image that's considered and your own, not just a record of a remarkable place.It's a small group of no more than six, taught personally and pitched at exactly your level, with Alan on hand throughout for camera settings, composition and one-to-one guidance, plus image reviews to spark ideas and inspiration on the day. You'll come away with a portfolio of images from one of England's most unusual gardens — and a sharper, more intentional way of seeing detail, composition and light in any garden you photograph. Please note the workshop fee does not include the entrance fee to Sezincote garden and house, which is payable separately on the day.</t>
+          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SuffolkDescription: This is a 3-day, 2-night residential Suffolk landscape photography workshop based on the Southwold and Aldeburgh coast, open to all levels from beginner to advanced. The Suffolk coastline is one of England's most photogenic and most varied — wide shoreline vistas, big skies, and a wealth of subjects most coastlines can't match: weathered piers, painted beach huts, iconic sea-defence structures and the traditional sails of Herringfleet Windmill. It's a landscape that rewards photographers who slow down and learn to see it.The focus is on long exposure and the art of black and white photography — learning to compose a strong coastal frame, to use long exposures to smooth water and sky into mood, and to recognise when a scene works better in mono. It's about more than the technical craft, though: the real work is learning to see — composing with intention, working intimate detail as readily as the wide vista, and reading light and tone as a harmony rather than chasing the obvious shot. It's never prescriptive either: over three days and two to three locations a day — from Southwold and Walberswick to Dunwich, Orford and Aldeburgh — we work with whatever light and conditions the coast gives us, with early sunrise shoots, full days in the field with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the group, the season, the tides and the forecast, and sends a detailed location itinerary a few days ahead. En-suite accommodation and breakfast are included, so all you have to think about for three days is your photography. You'll come away with a portfolio of atmospheric Suffolk coastal images and a real grasp of long exposure and black and white technique. An extra night is available the day before on request, ideal for those travelling from a distance — contact me to arrange.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1715077805264-XJYPE427XFHYBMW7L4TL/_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714667523305-2SEM1T5WD278HHO4HJIV/Southwold+Sunrise.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/sezincote-garden-photography-workshop</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Flowering, Macro &amp; Abstract</t>
+          <t>coastal, - weekend residential photo workshops</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9859986", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>50</v>
+        <v>995</v>
       </c>
       <c r="I45" t="n">
-        <v>50</v>
+        <v>995</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SQ9859986</t>
+          <t>SQ2176971</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2957,51 +2957,51 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUFFOLK Landscape Photography Workshops - 5th-7th Feb</t>
+          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Join us for an inspiring Suffolk landscape photography workshop, where you'll have the opportunity to create stunning long exposures during breathtaking sunrises and vibrant sunsets. We will explore picturesque quays, serene estuaries, intriguing piers, and tranquil marshes, all while capturing the beauty of charming beach huts and ancient woodlands. Emphasising artistic expression, we'll also delve into the world of black and white photography, allowing you to bring a classic touch to your coastal images.SummaryLocation: Suffolk - East Anglia / Southwold/Aldeburgh AreaDates: Fri 5th 09:30 - Sun 7th 14:30 Feb 2027 - 3 Days/2 NightsParticipants: Max 4 (1 Car, transport between locations included)Fitness: 2. Moderate (15-30 min walks)Experience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details SuffolkDescription: This is a 3-day, 2-night residential Suffolk landscape photography workshop based on the Southwold and Aldeburgh coast, open to all levels from beginner to advanced. The Suffolk coastline is one of England's most photogenic and most varied — wide shoreline vistas, big skies, and a wealth of subjects most coastlines can't match: weathered piers, painted beach huts, iconic sea-defence structures and the traditional sails of Herringfleet Windmill. It's a landscape that rewards photographers who slow down and learn to see it.The focus is on long exposure and the art of black and white photography — learning to compose a strong coastal frame, to use long exposures to smooth water and sky into mood, and to recognise when a scene works better in mono. It's about more than the technical craft, though: the real work is learning to see — composing with intention, working intimate detail as readily as the wide vista, and reading light and tone as a harmony rather than chasing the obvious shot. It's never prescriptive either: over three days and two to three locations a day — from Southwold and Walberswick to Dunwich, Orford and Aldeburgh — we work with whatever light and conditions the coast gives us, with early sunrise shoots, full days in the field with tuition, and evenings for relaxed picture reviews.With a maximum of just four photographers and transport between locations included, this is genuinely personal, hassle-free tuition — Alan plans each day around the group, the season, the tides and the forecast, and sends a detailed location itinerary a few days ahead. En-suite accommodation and breakfast are included, so all you have to think about for three days is your photography. You'll come away with a portfolio of atmospheric Suffolk coastal images and a real grasp of long exposure and black and white technique. An extra night is available the day before on request, ideal for those travelling from a distance — contact me to arrange.</t>
+          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: This Urban Architecture Photography workshop is an evening walk through the historic heart of Coventry — once UK City of Culture — open to all levels and any camera. Cities transform after dark: artificial light, deep shadow and the last colour in the sky turn ordinary buildings and ruins into something dramatic, and this 2.5-hour workshop is built around learning to see and design photographs at night, in the tricky low light most people find hardest to shoot.Confident technique in the dark is the floor we build on — and we'll cover it: focusing and exposing accurately in low light, and setting up long exposures to capture movement and mood. But the real work is learning to see the city as a photographer. Walking together through old and new architectural corners — including the cathedral area and its ruins — you'll learn to compose with form, line, texture and contrast, to read the interplay of artificial light and shadow as a harmony rather than a problem, and to find the considered, intentional frame instead of the obvious postcard of a landmark. Old against new, light against dark, detail against sweep — it's about designing an image, not just recording a building.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to night photography or refining your eye you get real one-to-one guidance in the field. You'll come away with a set of atmospheric urban and architectural images — long exposures, abstracts, dramatic skies — and a sharper, more intentional way of seeing that lets you photograph any city after dark.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714667523305-2SEM1T5WD278HHO4HJIV/Southwold+Sunrise.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/suffolk-landscape-photography-workshops</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>coastal, - weekend residential photo workshops</t>
+          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2176971", "price": "995.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "995.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>995</v>
+        <v>50</v>
       </c>
       <c r="I46" t="n">
-        <v>995</v>
+        <v>50</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SQ2176971</t>
+          <t>SQ4066377</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3013,51 +3013,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>URBAN ARCHITECTURE Photography Workshops - Coventry 9 Sep</t>
+          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>We will walk around several historic parts of Coventry in this 2.5hr Urban Architecture Photography Workshop, photographing buildings and ruins.SummaryLocation: Coventry City CentreDates: Wed 9 Sep 2026 - 18:15-20:15Participants: Max 6Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details: Street PhotographyDescription: This Urban Architecture Photography workshop is an evening walk through the historic heart of Coventry — once UK City of Culture — open to all levels and any camera. Cities transform after dark: artificial light, deep shadow and the last colour in the sky turn ordinary buildings and ruins into something dramatic, and this 2.5-hour workshop is built around learning to see and design photographs at night, in the tricky low light most people find hardest to shoot.Confident technique in the dark is the floor we build on — and we'll cover it: focusing and exposing accurately in low light, and setting up long exposures to capture movement and mood. But the real work is learning to see the city as a photographer. Walking together through old and new architectural corners — including the cathedral area and its ruins — you'll learn to compose with form, line, texture and contrast, to read the interplay of artificial light and shadow as a harmony rather than a problem, and to find the considered, intentional frame instead of the obvious postcard of a landmark. Old against new, light against dark, detail against sweep — it's about designing an image, not just recording a building.It's a small group of no more than six, taught personally and pitched at exactly your level, so whether you're new to night photography or refining your eye you get real one-to-one guidance in the field. You'll come away with a set of atmospheric urban and architectural images — long exposures, abstracts, dramatic skies — and a sharper, more intentional way of seeing that lets you photograph any city after dark.</t>
+          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details Lake VyrnwyDescription: This is a 2-day, 1-night residential Wales photography workshop based in the valleys of Mid-Wales, open to all levels from beginner to advanced. It's built around two of the country's most rewarding landscape locations — Pistyll Rhaeadr, an enchanting waterfall in the Berwyn Mountains and, at 240ft, Britain's tallest single-drop fall, and the tranquil 11-mile shoreline of Lake Vyrnwy — giving you woodlands, water, mountains and one of the seven wonders of Wales in a single weekend.Over two days we work both locations at their best. At Pistyll Rhaeadr you'll photograph the three-stage falls from the viewing platform and bridge, then drop down to water level among the slate beds and mini-falls for intimate compositions; around Lake Vyrnwy we take a leisurely circuit of the reservoir, stopping at quiet bays and outlets and walking the river to the waterfall at the valley head. The focus is on three things that make moving water and big Welsh landscape work: composing a strong frame from a busy natural scene, mastering long exposure to turn falling water into silk, and reading the light and weather that give these valleys their mood. Throughout, the emphasis isn't just on the famous waterfall but on learning to see it — working intimate detail as readily as the wide vista, and treating light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of Welsh waterfalls, lakes and valleys — and a real command of long-exposure water technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1658913526124-UHAZAOPDEELSFKC627FT/Coventry+1.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/urban-architecture-photography-workshops-coventry</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Urban</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4066377", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>695</v>
       </c>
       <c r="I47" t="n">
-        <v>50</v>
+        <v>695</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SQ4066377</t>
+          <t>SQ5697158</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3069,51 +3069,51 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WALES Photography Workshop | Lake Vyrnwy 10-11 Oct</t>
+          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Join me for this fantastic Wales photography workshop of woodlands, lakes and waterfalls in Mid-WalesLocation: Wales - Dee ValleyDates: Sat 10th - Sun 11th Oct 2026 - 2 Days/1 NightParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodWales Photography Workshop Event Details Lake VyrnwyDescription: This is a 2-day, 1-night residential Wales photography workshop based in the valleys of Mid-Wales, open to all levels from beginner to advanced. It's built around two of the country's most rewarding landscape locations — Pistyll Rhaeadr, an enchanting waterfall in the Berwyn Mountains and, at 240ft, Britain's tallest single-drop fall, and the tranquil 11-mile shoreline of Lake Vyrnwy — giving you woodlands, water, mountains and one of the seven wonders of Wales in a single weekend.Over two days we work both locations at their best. At Pistyll Rhaeadr you'll photograph the three-stage falls from the viewing platform and bridge, then drop down to water level among the slate beds and mini-falls for intimate compositions; around Lake Vyrnwy we take a leisurely circuit of the reservoir, stopping at quiet bays and outlets and walking the river to the waterfall at the valley head. The focus is on three things that make moving water and big Welsh landscape work: composing a strong frame from a busy natural scene, mastering long exposure to turn falling water into silk, and reading the light and weather that give these valleys their mood. Throughout, the emphasis isn't just on the famous waterfall but on learning to see it — working intimate detail as readily as the wide vista, and treating light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of Welsh waterfalls, lakes and valleys — and a real command of long-exposure water technique. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Crackley Wood, Kenilworth - Fri Nov 6Hay Woods - Solihull Fri Dec 4Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: This is a relaxed, informal woodland photography walk through the beautiful woodlands in and around Warwickshire — a regular monthly outing open to all levels and any camera. It's a gentle two hours among the trees with camera in hand, and it's as much about slowing down and reconnecting with nature as it is about photography: we walk, we observe, we take in the wood around us, and we make a photograph when something moves us to — or simply enjoy being there.My aim isn't to tell you what to shoot. It's to help you develop your own visual awareness, your photographic eye and your personal interpretation of what's in front of you. Woodland is one of the hardest subjects there is — chaotic, cluttered, endlessly busy — so the real work is learning to see: to simplify the scene, to find the quiet order and the light within the tangle, and to photograph the close-up, the intimate detail and the abstract as readily as the wider woodland view. I'm always on hand for the "how to" — the settings and the craft — but in service of what you feel drawn to express, not a shot list.The walks rotate through a lovely variety of local woodlands across the seasons — among them Crackley Wood, Hay Wood, Tile Hill Nature Reserve, Millisons Wood and Piles Coppice — so there's always something new to see. With no more than six of us it stays personal and unhurried, with one-to-one guidance whenever you want it. You'll come away with images that are genuinely your own — and a calmer, more intentional way of seeing that stays with you long after the walk.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714636535694-5SWM865PVWA9MMT8LCQB/Dawn+at+Lake+Vyrnwy_.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/wales-photography-workshop-pistyll-rhaeadr</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5697158", "price": "695.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>695</v>
+        <v>15</v>
       </c>
       <c r="I48" t="n">
-        <v>695</v>
+        <v>15</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ1654264, SQ1288994, SQ0063623, SQ6524101, SQ7078023, SQ3819844</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SQ5697158</t>
+          <t>SQ1654264</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3125,51 +3125,51 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WARWICKSHIRE Woodland PHOTOGRAPHY WALKS - Monthly - 2hrs</t>
+          <t>Landscape YORKSHIRE DALES Photography Workshop - 16 - 18 Apr</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Informal woodland photography walks in and around Warwickshire Woodlands - All Levels and types of camera welcome - Length 2hrs. 9:30 am-11:30 amSummaryLocation: Various Warwickshire Woodlands2026 - 09:30 - 11:30Hay Woods - Solihull Fri Jan 2Tile Hill Nature Reserve Mon Feb 2Millisons Wood, Meriden -Sun May 3Piles Coppice, Coventry - Fri Oct 16Crackley Wood, Kenilworth - Fri Nov 6Hay Woods - Solihull Fri Dec 4Participants: Max 6Fitness: 1. EasyExperience Level: Novice to BeginnerEquipment Needed: Phone or Digital CameraPhotography Workshop Event Details: Woodland WalksDescription: This is a relaxed, informal woodland photography walk through the beautiful woodlands in and around Warwickshire — a regular monthly outing open to all levels and any camera. It's a gentle two hours among the trees with camera in hand, and it's as much about slowing down and reconnecting with nature as it is about photography: we walk, we observe, we take in the wood around us, and we make a photograph when something moves us to — or simply enjoy being there.My aim isn't to tell you what to shoot. It's to help you develop your own visual awareness, your photographic eye and your personal interpretation of what's in front of you. Woodland is one of the hardest subjects there is — chaotic, cluttered, endlessly busy — so the real work is learning to see: to simplify the scene, to find the quiet order and the light within the tangle, and to photograph the close-up, the intimate detail and the abstract as readily as the wider woodland view. I'm always on hand for the "how to" — the settings and the craft — but in service of what you feel drawn to express, not a shot list.The walks rotate through a lovely variety of local woodlands across the seasons — among them Crackley Wood, Hay Wood, Tile Hill Nature Reserve, Millisons Wood and Piles Coppice — so there's always something new to see. With no more than six of us it stays personal and unhurried, with one-to-one guidance whenever you want it. You'll come away with images that are genuinely your own — and a calmer, more intentional way of seeing that stays with you long after the walk.</t>
+          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Yorkshire DalesDescription: This is a 3-day, 2-night residential landscape photography workshop in the Yorkshire Dales — one of England's most iconic and varied landscapes, open to all levels from beginner to advanced. From dramatic limestone pavements and amphitheatre cliffs to tumbling waterfalls, soaring viaducts and lone, wind-sculpted trees, the Dales pack an extraordinary range of subjects into one area, and over a long weekend you'll learn to read and photograph this moody, dramatic country in its best light.Across three days we work some of the Dales' most rewarding locations as the conditions and season allow — the natural amphitheatre of Malham Cove and the ravine at Gordale Scar, the waterfalls of Ingleton, Aysgarth and Janet's Foss, the sweeping arches of Ribblehead Viaduct, and the famous lone tree set on its bare limestone pavement. The focus is on three things that make a strong Dales image: composing rock, water and vista into a balanced frame, mastering long exposure to bring waterfalls and rivers to life, and timing each shoot — including early morning starts — to the dramatic light and weather these hills are known for. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Yorkshire Dales — waterfalls, limestone pavements, viaducts and classic vistas — and the field craft to capture dramatic upland landscape anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1707217364251-99ITJH38DI58S3G3YA47/Woodland+Photography+Walk.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/woodland-photography-walk-warwickshire</t>
+          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - half-day photo workshops, Woodlands</t>
+          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1654264", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Jan 2 Hay Woods - Solihull"}, {"@type": "Offer", "sku": "SQ1288994", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Mon Feb 2 - Tile Hill Nature Reserve - Coventry"}, {"@type": "Offer", "sku": "SQ0063623", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Sun May 3 - Millisons Wood, Meriden"}, {"@type": "Offer", "sku": "SQ6524101", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Oct 16 - Piles Coppice, Coventry"}, {"@type": "Offer", "sku": "SQ7078023", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Nov 6 - Crackley Wood, Kenilworth"}, {"@type": "Offer", "sku": "SQ3819844", "price": "15.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Fri Dec 4 - Hay Wood - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>15</v>
+        <v>895</v>
       </c>
       <c r="I49" t="n">
-        <v>15</v>
+        <v>895</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SQ1654264, SQ1288994, SQ0063623, SQ6524101, SQ7078023, SQ3819844</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SQ1654264</t>
+          <t>SQ9211910</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3181,110 +3181,166 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Landscape YORKSHIRE DALES Photography Workshop - 16 - 18 Apr</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Yorkshire Dales Photography Workshop - Join me for this fantastic landscape workshop on limestone pavements and waterfalls.SummaryLocation: Yorkshire DalesDates: Fri 16th - Sun 18th Apr 2027 - 3 Days/2 NightsParticipants: Max 4Fitness: 3. ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Yorkshire DalesDescription: This is a 3-day, 2-night residential landscape photography workshop in the Yorkshire Dales — one of England's most iconic and varied landscapes, open to all levels from beginner to advanced. From dramatic limestone pavements and amphitheatre cliffs to tumbling waterfalls, soaring viaducts and lone, wind-sculpted trees, the Dales pack an extraordinary range of subjects into one area, and over a long weekend you'll learn to read and photograph this moody, dramatic country in its best light.Across three days we work some of the Dales' most rewarding locations as the conditions and season allow — the natural amphitheatre of Malham Cove and the ravine at Gordale Scar, the waterfalls of Ingleton, Aysgarth and Janet's Foss, the sweeping arches of Ribblehead Viaduct, and the famous lone tree set on its bare limestone pavement. The focus is on three things that make a strong Dales image: composing rock, water and vista into a balanced frame, mastering long exposure to bring waterfalls and rivers to life, and timing each shoot — including early morning starts — to the dramatic light and weather these hills are known for. Throughout, the emphasis isn't just on the grand vista but on learning to see it — composing with intention, working intimate detail as readily as the wide view, and reading light and colour as a harmony rather than chasing the obvious shot.With a maximum of just four photographers, this is genuinely personal tuition — Alan plans each day around the season and the forecast, and sends a detailed location itinerary a few days ahead. Accommodation and breakfast are included, so all you have to think about is your photography, and you'll come away with a varied portfolio of the Yorkshire Dales — waterfalls, limestone pavements, viaducts and classic vistas — and the field craft to capture dramatic upland landscape anywhere. An extra night's accommodation is available the day before if required — please request in advance, subject to hotel availability.</t>
+          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1714659095505-TB874TXCA6ADNDFC82FX/Muker+%2302+-+July+2021.jpg</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photo-workshops-uk/yorkshire-dales-photography-workshops</t>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>All Photography Workshops, - weekend residential photo workshops, Landscape</t>
+          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops, photography-gift-vouchers;photography-presents</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9211910", "price": "895.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>895</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>895</v>
+        <v>5</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SQ9211910</t>
+          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
+          <t>Professional Black and White Photography Course | Coventry</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Photography Gift Vouchers | Digital eCard | Email Delivery</t>
+          <t>Professional Black and White Photography Course | Coventry</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1556527290185-GZJ3ZPC3M7AU34BFFVOE/photography-gift-vouchers.png</t>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1721724334692-7KPD0E90A6E4YZMAR324/black+and+white+photography+course+.jpg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.alanranger.com/photography-services-near-me/photography-gift-vouchers</t>
+          <t>https://www.alanranger.com/photography-services-near-me/black-and-white-photography-course</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>online;1-2-1-private-lessons;gift-voucher;photography-classes;photography-courses;photography-services;photography-tuition;photography-workshops, photography-gift-vouchers;photography-presents</t>
+          <t>photography-courses, beginners-photography-course</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA", "price": "5.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-19", "priceValidUntil": "2027-06-19", "name": "Photography Gift Vouchers | Digital eCard | Email Delivery"}]</t>
+          <t>[{"@type": "Offer", "sku": "SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Professional Black and White Photography Course | Coventry"}]</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
+          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SUP-PHOTOGRAPHY-GIFT-VOUCHERS-DIGITA</t>
+          <t>SUP-PROFESSIONAL-BLACK-AND-WHITE-PHO</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Photography Masterclasses-Learn and improve your photography</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Photography Masterclasses-Learn and improve your photography</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://images.squarespace-cdn.com/content/v1/5013f4b2c4aaa4752ac69b17/1675588273356-8MVS4YXJTH3Y5PRQ36N7/photography-tuition-Package-2.jpg</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.alanranger.com/photography-services-near-me/photography-masterclasses-coventry</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>photography-classes;photography-courses;photography-tuition, coventry</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[{"@type": "Offer", "sku": "SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Photography Masterclasses-Learn and improve your photography"}]</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>150</v>
+      </c>
+      <c r="I52" t="n">
+        <v>150</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SUP-PHOTOGRAPHY-MASTERCLASSES-LEARN-</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>product</t>
         </is>

--- a/csv processed/02 – products_cleaned.xlsx
+++ b/csv processed/02 – products_cleaned.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Tue July 7th - 6:30pm - 8:30pmMacro Photography - Tue Sep 8th - 6:00pm - 8:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
+          <t>Abstract and Macro Photography Workshop . Learn about camera settings, lens use, controlling DoF and composition. Various Dates in Warwickshire | Half DaySummaryLocation: WarwickshireDates: Macro Photography WorkshopsMacro Photography - Sun Aug 23rd - 10:30am - 12:30pmMacro Photography - Tue Sep 8th - 6:00pm - 8:00pmParticipants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: Digital Camera and Tripod, Zoom or Macro LensMacro Photography Workshop Event Details: Macro Photography and AbstractDescription: This Abstract and Macro Photography Workshop takes place at a Warwickshire location and is open to all levels and any camera. Macro is where ordinary surroundings become extraordinary — get close and a tree trunk, a piece of weathered stone or a patch of water reveals shapes, colours, tones and patterns most people walk straight past. The whole session is about learning to see them, and then photograph them with intention.The technical craft matters here — and we'll cover it properly — but it's the floor, not the point. Working around the area together, Alan guides you through the settings that give you control: getting sharp focus and using a macro lens or zoom, controlling depth of field to isolate your subject, and building a composition with real intention. From there the real work begins — training your eye to find the abstract within the ordinary, to read tone, shadow and highlight, and to treat colour as a harmony to compose with rather than a loud effect to chase. The aim is never the obvious close-up everyone takes, but an image that's considered and your own.It's a small group of no more than four, taught personally by an award-winning professional photographer, so every person gets real one-to-one guidance in the field — briefing and set-up, then shooting with reviews and tuition as you go. You'll leave with your own macro and abstract images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph everything afterwards.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue Jul 7th - 6:30pm - 8:30pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8660736", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue Sep 8th - 6:00pm - 8:00pm", "priceSpecification": {"price": "50.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8482281", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun Aug 23rd - 10:30am - 12:30pm"}, {"@type": "Offer", "sku": "SQ8660736", "price": "65.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue Sep 8th - 6:00pm - 8:00pm"}]</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "1 x £3000 = £3000"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0754560", "price": "1200.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £1200 = £1200"}, {"@type": "Offer", "sku": "SQ7502565", "price": "1500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £1500 = £1500"}, {"@type": "Offer", "sku": "SQ1485137", "price": "2000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £2000 = £2000"}, {"@type": "Offer", "sku": "SQ7001156", "price": "2500.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £2500 = £2500"}, {"@type": "Offer", "sku": "SQ2612014", "price": "3000.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "1 x £3000 = £3000"}]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0818501", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7647904", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9436105", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1204772", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9290465", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7375084", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0264308", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9938663", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0693365", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3442432", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8197555", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9853668", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0732756", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6382131", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4533936", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4668363", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 31  Oct 2026 AM - 8am - 11:30am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5203247", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 31 Oct 2026 PM - 12pm - 3:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1249736", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 31 Oct 2026 All Day -8am - 3:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -686,11 +686,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4322859", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Wednesdays - Jul 1 - Jul 15 Coventry"}, {"@type": "Offer", "sku": "SQ5977532", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Mondays - Jul 6 - Jul 20 Coventry"}, {"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}, {"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6482854", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Thursdays - Sep 17 - Oct 1 Coventry"}, {"@type": "Offer", "sku": "SQ1702168", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Tuesdays - Sep 22 - Oct 6 Coventry"}, {"@type": "Offer", "sku": "SQ6875626", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Mondays - Oct 12 - Oct 26 Coventry"}, {"@type": "Offer", "sku": "SQ8844762", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Wednesdays - Oct 14 - Oct 28 Coventry"}, {"@type": "Offer", "sku": "SQ5616379", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Mondays - Nov 9 - Nov 23 Coventry"}, {"@type": "Offer", "sku": "SQ3231903", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Tuesdays - Dec 1 - Dec 15 Coventry"}, {"@type": "Offer", "sku": "SQ5559634", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Wednesdays - Jan 13 - Jan 27 Coventry"}, {"@type": "Offer", "sku": "SQ0659870", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "3wks Thursdays - Jan 28 - Feb 11 Coventry"}]</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
         <v>150</v>
@@ -700,12 +700,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SQ4322859, SQ5977532, SQ6482854, SQ1702168, SQ6875626, SQ8844762, SQ5616379, SQ3231903, SQ5559634, SQ0659870</t>
+          <t>SQ6482854, SQ1702168, SQ6875626, SQ8844762, SQ5616379, SQ3231903, SQ5559634, SQ0659870</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SQ4322859</t>
+          <t>SQ6482854</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beginners Portrait Photography Course - Coventry - 11 Oct 2025</t>
+          <t>Beginners Portrait Photography Course - Coventry 11 Oct -25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2592535", "price": "195.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8599409", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 20 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7560082", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 20 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7443277", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 20 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8437523", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 21 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8685603", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 21 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1561078", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 21 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1660230", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 22 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1568285", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 22 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5411810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 22 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5831738", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3014350", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5312475", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 23 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1318075", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8270632", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ4260038", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sat 24 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6145280", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2267773", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2428415", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun 25 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ6117337", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 26 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8500857", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 26 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1516510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Mon 26 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1102782", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 27 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5885147", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 27 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3102560", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 27 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1465142", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 28 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1264314", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 28 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8706845", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Wed 28 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ7100218", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2446216", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ3086312", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 29 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ1353684", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Apr - 5:45am - 09:45am", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0574386", "price": "99.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Apr - 10:30am - 14:30pm", "priceSpecification": {"price": "99.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2004510", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 30 Apr All day - 5:45am - 14:30pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5650040", "price": "30.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -885,12 +885,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Christmas Photography Seasonal Workshops | Warwickshire</t>
+          <t>Christmas Photography Seasonal Workshops - Warwickshire UK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details: Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
+          <t>Christmas photography workshops. A Leisurely Christmas photography walk and photograph the countryside - Lapworth or the Christmas lights Stratford Upon Avon photography- Warwickshire - Expert Advice GivenSummaryLocation: WarwickshireDates: 2026 DatesThu 10 December 2026 - 18:45 - 20:30 - Stratford Upon Avon Evening ShootTue, 29 December 2026 - 1 day Christmas Photo Walk 09:00 15:00Break for pub lunch around 12:45 - Not includedParticipants: Max 6Fitness: 2. Easy-ModerateExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodChristmas Photography Workshop Event Details Christmas PhotowalkDescription: This Christmas Photography Workshop is the perfect way to escape the heat and fuss of the festive season — swap the wrapping paper for your camera, walk off a little of the overindulgence, and rediscover how much there is to photograph at the most atmospheric time of year. Open to all levels and any camera, it's a relaxed, sociable outing in Warwickshire with expert guidance throughout, and there's a choice of two very different sessions.Stratford-upon-Avon, evening: an after-dark shoot in the heart of the town, photographing the Christmas lights and festive atmosphere. It's a chance to work long exposure, reflections and the warm glow of the season — learning to control exposure in low light and compose a strong frame out of a busy, sparkling scene rather than settling for the obvious snapshot.Lapworth, daytime: the antidote to Christmas. Once the presents are unwrapped, the family politics have peaked and you've eaten your bodyweight in turkey, this leisurely day in the winter countryside is the tonic — a chance to breathe, clear your head and lose yourself in your photography for a few hours. We'll amble through frosty fields, bare woodland and quiet lanes reading the soft, low winter light, with a relaxed lunch in the middle of the day. The whole walk is under five miles at an easy, unhurried pace — gentle enough that the photography, the fresh air and the company are the whole point. The focus stays on seeing: composing with intention, working both intimate detail and wider vista, and reading light, texture and mood to make a picture that's truly yours.It's a small group of no more than six, taught personally and pitched at exactly your level, with one-to-one guidance in the field throughout. Whether you choose the festive lights of Stratford, the crisp countryside of Lapworth, or both, you'll come away with a set of atmospheric seasonal images — and a stronger eye for light, composition and winter colour that carries through long after the decorations come down. For the Lapworth day, a table is reserved in advance at a welcoming country pub, with a festive menu offering both lighter and full festive-meal options to suit every appetite. The lunch itself isn't included in the workshop fee, so you simply pay for what you choose on the day.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8119747", "price": "50.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Thu 10 Dec 18:45- 20:30 - Stratford Upon Avon"}, {"@type": "Offer", "sku": "SQ6178610", "price": "125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Tue 29 Dec 09:00 - 15:00 - Lapworth"}]</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8540187", "price": "1095.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "1095.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ5540434", "price": "875.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ2754105", "price": "925.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ8057321", "price": "575.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "60x40 Canvas Wrap Round"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0105911", "price": "135.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "16x12 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ4206024", "price": "177.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "24x16 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ0781804", "price": "219.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "30x20 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ3982814", "price": "306.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "36x24 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ8209269", "price": "336.65", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "40x30 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7901040", "price": "414.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "48x36 Canvas Wrap Round"}, {"@type": "Offer", "sku": "SQ7260825", "price": "459.95", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "60x40 Canvas Wrap Round"}]</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "60x40 Print"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ4872440", "price": "50.57", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "16x12 Print"}, {"@type": "Offer", "sku": "SQ0453600", "price": "95.78", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "24x16 Print"}, {"@type": "Offer", "sku": "SQ7485354", "price": "138.86", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "30x20 Print"}, {"@type": "Offer", "sku": "SQ0167262", "price": "161.38", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "36x24 Print"}, {"@type": "Offer", "sku": "SQ1664775", "price": "217.23", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "40x30 Print"}, {"@type": "Offer", "sku": "SQ0377820", "price": "305.05", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "48x36 Print"}, {"@type": "Offer", "sku": "SQ8780582", "price": "416.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "60x40 Print"}]</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ1182401", "price": "75.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6583676", "price": "360.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "4 x 2hr sessions - weekday daytime", "priceSpecification": {"price": "360.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "36x24 Print (with Frame 48x36)"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ6825544", "price": "133.85", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "16x12 Print (with Frame 20x16)"}, {"@type": "Offer", "sku": "SQ3786581", "price": "191.50", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "24x16 Print (with Frame 30x20)"}, {"@type": "Offer", "sku": "SQ1355351", "price": "267.43", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "30x20 Print (with Frame 40x30)"}, {"@type": "Offer", "sku": "SQ0156134", "price": "356.90", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "36x24 Print (with Frame 48x36)"}]</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates: DatesSun Jul 12th 2026 - 15:00 - 17:00Sun May 23rd 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
+          <t>Join us for an unforgettable journey into macro and abstract on this garden photography workshop. Secure your spot today and embark on a transformative learning experience in garden photography.SummaryLocation: Coventry - CV4Dates:Sun May 23rd 2027 - 15:00 - 17:00Sun Jul 11th 2027 - 15:00 - 17:00Participants: Max 4Fitness: 1. EasyExperience Level: Beginner to AdvancedEquipment Needed: DSLR or Mirrorless Camera and TripodPhotography Workshop Event Details Garden PhotographyDescription: This Garden Photography Workshop is an intimate afternoon in Alan's own private garden in Coventry — his personal creative studio, a space he knows intimately and tends with a photographer's eye — open to all levels and any camera. A garden is one of the richest and most overlooked subjects there is: get close and the flowers, foliage, structures and borders reveal endless macro, close-up and abstract images, and this relaxed half-day is all about learning to see them, then photograph them with intention.The technical craft is the floor we build on — getting sharp focus, using your lens for macro and close-up detail, and controlling exposure and depth of field — but the real work is learning to look. You'll be given four photography assignments with guidance notes that push you to experiment and vary your approach, from intimate macro to wider garden portraits, training your eye to find the abstract within the planting and to compose with real intention. Throughout, the emphasis is on reading colour, light and texture as a harmony — letting the flowers sing without tipping into the loud, over-saturated shot — so your images feel considered and your own, not the obvious bloom-in-the-middle snap. Image reviews and feedback on a large screen in the gazebo help you see what's working and why.Places are limited to just four, so this is genuinely personal tuition, with Alan on hand for settings, composition and one-to-one guidance the whole time — and tea, coffee and cake served throughout. You'll come away with your own portfolio of garden images, and a sharper, more intentional way of seeing detail, colour and light that changes how you photograph flowers and nature everywhere.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun Jul 12 2026 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ0939451", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun May 23rd 2027 - 15:00 - 17:00"}, {"@type": "Offer", "sku": "SQ3644687", "price": "45.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Sun Jul 11th 2027 - 15:00 - 17:00"}]</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SQ3644687, SQ0939451</t>
+          <t>SQ0939451, SQ3644687</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SQ3644687</t>
+          <t>SQ0939451</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9898707", "price": "400.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "priceSpecification": {"price": "400.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29"}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ7419716", "price": "1595.00", "priceCurrency": "GBP", "availability": "https://schema.org/OutOfStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12"}]</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ9100538", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 18 Sep - 20 Sep - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ5158309", "price": "1075.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 13 Nov - 15 Nov - 3 Days 2026", "priceSpecification": {"price": "1075.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9016326", "price": "975.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 22 Jan - 24 Jan - 3 Days 2027", "priceSpecification": {"price": "975.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ0142956", "price": "1125.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Fri 12 Mar - Sun 14 Mar - 3 Days/2 Nights 2027", "priceSpecification": {"price": "1125.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-06-29", "priceValidUntil": "2027-06-29", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
+          <t>[{"@type": "Offer", "sku": "SQ3794821", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sat 17th Oct  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ8457424", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sun 1st Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ9037810", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sat 7th Nov  2026 09:30am - 4:00pm", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}, {"@type": "Offer", "sku": "SQ2363666", "price": "150.00", "priceCurrency": "GBP", "availability": "https://schema.org/InStock", "validFrom": "2026-08-12", "priceValidUntil": "2027-08-12", "name": "Padley and Bolehill Sat 22nd May 2027 - 09:30 - 16:00", "priceSpecification": {"price": "150.00", "priceCurrency": "GBP"}}]</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1725,7 +1725,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
  